--- a/office/data/实验数据.xlsx
+++ b/office/data/实验数据.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\glplaman.github.io\office\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FBE5B8D-5C8B-42D8-81D3-B3D83044B6D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A514656E-CD3C-4A0C-8532-094E55708E50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{2E5A61E7-CF82-4D7E-B994-D412ADB0B79D}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{2E5A61E7-CF82-4D7E-B994-D412ADB0B79D}"/>
   </bookViews>
   <sheets>
     <sheet name="通信录" sheetId="6" r:id="rId1"/>
@@ -2293,10 +2293,6 @@
       <c r="K2">
         <v>800</v>
       </c>
-      <c r="L2">
-        <f t="shared" ref="L2:L11" si="0">SUM(H2:K2)</f>
-        <v>7103</v>
-      </c>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
@@ -2332,10 +2328,6 @@
       <c r="K3">
         <v>500</v>
       </c>
-      <c r="L3">
-        <f t="shared" si="0"/>
-        <v>4905</v>
-      </c>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
@@ -2371,10 +2363,6 @@
       <c r="K4">
         <v>800</v>
       </c>
-      <c r="L4">
-        <f t="shared" si="0"/>
-        <v>5362</v>
-      </c>
       <c r="P4" t="s">
         <v>130</v>
       </c>
@@ -2416,10 +2404,6 @@
       <c r="K5">
         <v>1000</v>
       </c>
-      <c r="L5">
-        <f t="shared" si="0"/>
-        <v>8095.5</v>
-      </c>
       <c r="P5" t="s">
         <v>129</v>
       </c>
@@ -2461,10 +2445,6 @@
       <c r="K6">
         <v>1000</v>
       </c>
-      <c r="L6">
-        <f t="shared" si="0"/>
-        <v>7100.5</v>
-      </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
@@ -2500,10 +2480,6 @@
       <c r="K7">
         <v>800</v>
       </c>
-      <c r="L7">
-        <f t="shared" si="0"/>
-        <v>5750</v>
-      </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
@@ -2539,10 +2515,6 @@
       <c r="K8">
         <v>480</v>
       </c>
-      <c r="L8">
-        <f t="shared" si="0"/>
-        <v>6390</v>
-      </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
@@ -2578,10 +2550,6 @@
       <c r="K9">
         <v>900</v>
       </c>
-      <c r="L9">
-        <f t="shared" si="0"/>
-        <v>6998.5</v>
-      </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
@@ -2617,10 +2585,6 @@
       <c r="K10">
         <v>600</v>
       </c>
-      <c r="L10">
-        <f t="shared" si="0"/>
-        <v>7354</v>
-      </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
@@ -2655,10 +2619,6 @@
       </c>
       <c r="K11">
         <v>800</v>
-      </c>
-      <c r="L11">
-        <f t="shared" si="0"/>
-        <v>5605</v>
       </c>
     </row>
   </sheetData>

--- a/office/data/实验数据.xlsx
+++ b/office/data/实验数据.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\glplaman.github.io\office\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A514656E-CD3C-4A0C-8532-094E55708E50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F8F94D9-FDB1-403A-98F0-2413BFB90A31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{2E5A61E7-CF82-4D7E-B994-D412ADB0B79D}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{2E5A61E7-CF82-4D7E-B994-D412ADB0B79D}"/>
   </bookViews>
   <sheets>
     <sheet name="通信录" sheetId="6" r:id="rId1"/>
@@ -18,6 +18,7 @@
     <sheet name="销售记录" sheetId="3" r:id="rId3"/>
     <sheet name="工资收入" sheetId="4" r:id="rId4"/>
     <sheet name="高考成绩" sheetId="5" r:id="rId5"/>
+    <sheet name="迷你图" sheetId="7" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">工资收入!$A$1:$L$11</definedName>
@@ -35,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="206">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="221">
   <si>
     <t>学号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -78,15 +79,6 @@
   </si>
   <si>
     <t>排名</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>说明
-1. 五级成绩评定：优、良、中、及格、不及格
-2. 两级成绩评定：及格、不及格
-3. 评语为不及格的单元格红色背景高亮显示
-4. 前3名高亮显示
-5. 百分比保留小数点后2位，其它数字为整数</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -763,6 +755,68 @@
   </si>
   <si>
     <t>副主任</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>筛选实际收入小于8000的教授，结果放在B15</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.先根据总分降序排序，再根据语文降序排序</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2.使用透视表统计语文成绩的分布，结果放在新工作表中，命名为语文成绩分布</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>公司</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>上海</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>广州</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>重庆</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>深圳</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.创建数据</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2.生成柱形图</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3.生成迷你图</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5. 百分比保留小数点后2位，其它数字为整数</t>
+  </si>
+  <si>
+    <t>4. 前3名高亮显示</t>
+  </si>
+  <si>
+    <t>3. 评语为不及格的单元格红色背景高亮显示</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. 两级成绩评定：及格、不及格</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2. 五级成绩评定：优、良、中、及格、不及格</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -810,12 +864,21 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -827,20 +890,23 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="centerContinuous" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="centerContinuous" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1175,40 +1241,40 @@
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
       </c>
       <c r="C1" t="s">
+        <v>140</v>
+      </c>
+      <c r="D1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E1" t="s">
+        <v>151</v>
+      </c>
+      <c r="F1" t="s">
+        <v>139</v>
+      </c>
+      <c r="G1" t="s">
+        <v>149</v>
+      </c>
+      <c r="H1" t="s">
+        <v>138</v>
+      </c>
+      <c r="I1" t="s">
+        <v>150</v>
+      </c>
+      <c r="J1" t="s">
         <v>141</v>
       </c>
-      <c r="D1" t="s">
+      <c r="K1" t="s">
+        <v>152</v>
+      </c>
+      <c r="L1" t="s">
         <v>154</v>
-      </c>
-      <c r="E1" t="s">
-        <v>152</v>
-      </c>
-      <c r="F1" t="s">
-        <v>140</v>
-      </c>
-      <c r="G1" t="s">
-        <v>150</v>
-      </c>
-      <c r="H1" t="s">
-        <v>139</v>
-      </c>
-      <c r="I1" t="s">
-        <v>151</v>
-      </c>
-      <c r="J1" t="s">
-        <v>142</v>
-      </c>
-      <c r="K1" t="s">
-        <v>153</v>
-      </c>
-      <c r="L1" t="s">
-        <v>155</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.2">
@@ -1216,34 +1282,34 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
+        <v>155</v>
+      </c>
+      <c r="C2" t="s">
+        <v>143</v>
+      </c>
+      <c r="D2" s="2">
+        <v>31048</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="F2" t="s">
+        <v>203</v>
+      </c>
+      <c r="G2" t="s">
         <v>156</v>
       </c>
-      <c r="C2" t="s">
-        <v>144</v>
-      </c>
-      <c r="D2" s="4">
-        <v>31048</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="F2" t="s">
-        <v>204</v>
-      </c>
-      <c r="G2" t="s">
-        <v>157</v>
-      </c>
       <c r="H2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="I2">
         <v>65</v>
       </c>
       <c r="K2" t="s">
+        <v>158</v>
+      </c>
+      <c r="L2" t="s">
         <v>159</v>
-      </c>
-      <c r="L2" t="s">
-        <v>160</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.2">
@@ -1251,34 +1317,34 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
+        <v>160</v>
+      </c>
+      <c r="C3" t="s">
+        <v>143</v>
+      </c>
+      <c r="D3" s="2">
+        <v>29254</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="F3" t="s">
+        <v>203</v>
+      </c>
+      <c r="G3" t="s">
         <v>161</v>
       </c>
-      <c r="C3" t="s">
+      <c r="H3" t="s">
         <v>144</v>
-      </c>
-      <c r="D3" s="4">
-        <v>29254</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="F3" t="s">
-        <v>204</v>
-      </c>
-      <c r="G3" t="s">
-        <v>162</v>
-      </c>
-      <c r="H3" t="s">
-        <v>145</v>
       </c>
       <c r="I3">
         <v>60</v>
       </c>
       <c r="K3" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="L3" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.2">
@@ -1286,34 +1352,34 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
+        <v>165</v>
+      </c>
+      <c r="C4" t="s">
+        <v>143</v>
+      </c>
+      <c r="D4" s="2">
+        <v>32183</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="F4" t="s">
+        <v>204</v>
+      </c>
+      <c r="G4" t="s">
         <v>166</v>
       </c>
-      <c r="C4" t="s">
-        <v>144</v>
-      </c>
-      <c r="D4" s="4">
-        <v>32183</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="F4" t="s">
-        <v>205</v>
-      </c>
-      <c r="G4" t="s">
-        <v>167</v>
-      </c>
       <c r="H4" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="I4">
         <v>55</v>
       </c>
       <c r="K4" t="s">
+        <v>168</v>
+      </c>
+      <c r="L4" t="s">
         <v>169</v>
-      </c>
-      <c r="L4" t="s">
-        <v>170</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.2">
@@ -1321,34 +1387,34 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
+        <v>170</v>
+      </c>
+      <c r="C5" t="s">
+        <v>143</v>
+      </c>
+      <c r="D5" s="2">
+        <v>33107</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="F5" t="s">
+        <v>203</v>
+      </c>
+      <c r="G5" t="s">
         <v>171</v>
       </c>
-      <c r="C5" t="s">
-        <v>144</v>
-      </c>
-      <c r="D5" s="4">
-        <v>33107</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="F5" t="s">
-        <v>204</v>
-      </c>
-      <c r="G5" t="s">
-        <v>172</v>
-      </c>
       <c r="H5" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="I5">
         <v>90</v>
       </c>
       <c r="K5" t="s">
+        <v>173</v>
+      </c>
+      <c r="L5" t="s">
         <v>174</v>
-      </c>
-      <c r="L5" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.2">
@@ -1356,31 +1422,31 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
+        <v>175</v>
+      </c>
+      <c r="C6" t="s">
+        <v>143</v>
+      </c>
+      <c r="D6" s="2">
+        <v>33859</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="F6" t="s">
+        <v>199</v>
+      </c>
+      <c r="G6" t="s">
         <v>176</v>
-      </c>
-      <c r="C6" t="s">
-        <v>144</v>
-      </c>
-      <c r="D6" s="4">
-        <v>33859</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="F6" t="s">
-        <v>200</v>
-      </c>
-      <c r="G6" t="s">
-        <v>177</v>
       </c>
       <c r="I6">
         <v>76</v>
       </c>
       <c r="K6" t="s">
+        <v>178</v>
+      </c>
+      <c r="L6" t="s">
         <v>179</v>
-      </c>
-      <c r="L6" t="s">
-        <v>180</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
@@ -1388,29 +1454,29 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
+        <v>180</v>
+      </c>
+      <c r="C7" t="s">
+        <v>146</v>
+      </c>
+      <c r="D7" s="2">
+        <v>32051</v>
+      </c>
+      <c r="E7" s="1"/>
+      <c r="F7" t="s">
+        <v>204</v>
+      </c>
+      <c r="G7" t="s">
         <v>181</v>
-      </c>
-      <c r="C7" t="s">
-        <v>147</v>
-      </c>
-      <c r="D7" s="4">
-        <v>32051</v>
-      </c>
-      <c r="E7" s="3"/>
-      <c r="F7" t="s">
-        <v>205</v>
-      </c>
-      <c r="G7" t="s">
-        <v>182</v>
       </c>
       <c r="I7">
         <v>70</v>
       </c>
       <c r="K7" t="s">
+        <v>182</v>
+      </c>
+      <c r="L7" t="s">
         <v>183</v>
-      </c>
-      <c r="L7" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.2">
@@ -1418,28 +1484,28 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
+        <v>184</v>
+      </c>
+      <c r="C8" t="s">
+        <v>146</v>
+      </c>
+      <c r="D8" s="2">
+        <v>34823</v>
+      </c>
+      <c r="F8" t="s">
+        <v>199</v>
+      </c>
+      <c r="G8" t="s">
         <v>185</v>
-      </c>
-      <c r="C8" t="s">
-        <v>147</v>
-      </c>
-      <c r="D8" s="4">
-        <v>34823</v>
-      </c>
-      <c r="F8" t="s">
-        <v>200</v>
-      </c>
-      <c r="G8" t="s">
-        <v>186</v>
       </c>
       <c r="I8">
         <v>74</v>
       </c>
       <c r="K8" t="s">
+        <v>186</v>
+      </c>
+      <c r="L8" t="s">
         <v>187</v>
-      </c>
-      <c r="L8" t="s">
-        <v>188</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.2">
@@ -1447,31 +1513,31 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
+        <v>188</v>
+      </c>
+      <c r="C9" t="s">
+        <v>146</v>
+      </c>
+      <c r="D9" s="2">
+        <v>34121</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="F9" t="s">
+        <v>200</v>
+      </c>
+      <c r="G9" t="s">
         <v>189</v>
-      </c>
-      <c r="C9" t="s">
-        <v>147</v>
-      </c>
-      <c r="D9" s="4">
-        <v>34121</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>191</v>
-      </c>
-      <c r="F9" t="s">
-        <v>201</v>
-      </c>
-      <c r="G9" t="s">
-        <v>190</v>
       </c>
       <c r="I9">
         <v>85</v>
       </c>
       <c r="K9" t="s">
+        <v>191</v>
+      </c>
+      <c r="L9" t="s">
         <v>192</v>
-      </c>
-      <c r="L9" t="s">
-        <v>193</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.2">
@@ -1479,28 +1545,28 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
+        <v>193</v>
+      </c>
+      <c r="C10" t="s">
+        <v>146</v>
+      </c>
+      <c r="D10" s="2">
+        <v>35278</v>
+      </c>
+      <c r="F10" t="s">
+        <v>199</v>
+      </c>
+      <c r="G10" t="s">
         <v>194</v>
-      </c>
-      <c r="C10" t="s">
-        <v>147</v>
-      </c>
-      <c r="D10" s="4">
-        <v>35278</v>
-      </c>
-      <c r="F10" t="s">
-        <v>200</v>
-      </c>
-      <c r="G10" t="s">
-        <v>195</v>
       </c>
       <c r="I10">
         <v>60</v>
       </c>
       <c r="K10" t="s">
+        <v>195</v>
+      </c>
+      <c r="L10" t="s">
         <v>196</v>
-      </c>
-      <c r="L10" t="s">
-        <v>197</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.2">
@@ -1508,28 +1574,28 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C11" t="s">
-        <v>144</v>
-      </c>
-      <c r="D11" s="4">
+        <v>143</v>
+      </c>
+      <c r="D11" s="2">
         <v>34881</v>
       </c>
       <c r="F11" t="s">
+        <v>200</v>
+      </c>
+      <c r="G11" t="s">
         <v>201</v>
-      </c>
-      <c r="G11" t="s">
-        <v>202</v>
       </c>
       <c r="I11">
         <v>100</v>
       </c>
       <c r="K11" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="L11" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
   </sheetData>
@@ -1548,7 +1614,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DE67399F-CC12-4ABD-9F7C-F6EE52160CF4}">
-  <dimension ref="A1:K27"/>
+  <dimension ref="A1:K33"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.5" bestFit="1" customWidth="1"/>
@@ -1595,10 +1661,10 @@
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C2">
         <v>18</v>
@@ -1615,10 +1681,10 @@
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C3">
         <v>19</v>
@@ -1635,10 +1701,10 @@
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C4">
         <v>18</v>
@@ -1655,10 +1721,10 @@
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B5" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C5">
         <v>20</v>
@@ -1675,10 +1741,10 @@
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C6">
         <v>17</v>
@@ -1695,10 +1761,10 @@
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B7" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C7">
         <v>17</v>
@@ -1715,10 +1781,10 @@
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C8">
         <v>18</v>
@@ -1735,10 +1801,10 @@
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B9" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C9">
         <v>17</v>
@@ -1755,10 +1821,10 @@
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B10" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C10">
         <v>17</v>
@@ -1775,10 +1841,10 @@
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B11" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C11">
         <v>18</v>
@@ -1795,10 +1861,10 @@
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B12" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C12">
         <v>20</v>
@@ -1815,10 +1881,10 @@
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B13" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C13">
         <v>17</v>
@@ -1835,10 +1901,10 @@
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B14" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C14">
         <v>18</v>
@@ -1855,10 +1921,10 @@
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B15" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C15">
         <v>17</v>
@@ -1875,10 +1941,10 @@
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B16" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C16">
         <v>17</v>
@@ -1893,12 +1959,12 @@
         <v>90</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B17" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C17">
         <v>19</v>
@@ -1913,12 +1979,12 @@
         <v>96</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B18" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C18">
         <v>20</v>
@@ -1933,50 +1999,75 @@
         <v>98</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B20" t="s">
+        <v>132</v>
+      </c>
+      <c r="C20" s="3"/>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B21" t="s">
         <v>133</v>
       </c>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="B21" t="s">
+      <c r="C21" s="3"/>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B22" t="s">
         <v>134</v>
       </c>
-    </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="B22" t="s">
+      <c r="C22" s="3"/>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B23" t="s">
         <v>135</v>
       </c>
-    </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="B23" t="s">
+      <c r="C23" s="3"/>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B24" t="s">
         <v>136</v>
       </c>
-    </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="B24" t="s">
+      <c r="C24" s="3"/>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B25" t="s">
         <v>137</v>
       </c>
-    </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="B25" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11" ht="99.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B27" s="1"/>
-      <c r="C27" s="1"/>
-      <c r="D27" s="1"/>
-      <c r="E27" s="1"/>
-      <c r="F27" s="1"/>
-      <c r="G27" s="1"/>
-      <c r="H27" s="1"/>
-      <c r="I27" s="1"/>
-      <c r="J27" s="1"/>
-      <c r="K27" s="1"/>
+      <c r="C25" s="3"/>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C26" s="4"/>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C27" s="4"/>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C28" s="4"/>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A29" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="5" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A31" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A32" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A33" t="s">
+        <v>216</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -1991,7 +2082,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B43A4D9D-2C34-46F9-8998-D6D5D69FC8F7}">
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="2" width="7.5" bestFit="1" customWidth="1"/>
@@ -2001,195 +2092,199 @@
     <col min="16" max="16" width="14.25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B1" t="s">
         <v>36</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D1" t="s">
         <v>37</v>
       </c>
-      <c r="C1" t="s">
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B2" t="s">
         <v>24</v>
       </c>
-      <c r="D1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B2" t="s">
-        <v>25</v>
-      </c>
       <c r="C2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D2">
         <v>2500</v>
       </c>
       <c r="F2" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+        <v>124</v>
+      </c>
+      <c r="G2" s="3"/>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D3">
         <v>150</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D4">
         <v>3000</v>
       </c>
       <c r="F4" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+        <v>125</v>
+      </c>
+      <c r="G4" s="3"/>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D5">
         <v>4000</v>
       </c>
       <c r="F5" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+        <v>126</v>
+      </c>
+      <c r="G5" s="3"/>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D6">
         <v>2700</v>
       </c>
       <c r="F6" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+        <v>127</v>
+      </c>
+      <c r="G6" s="3"/>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B7" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D7">
         <v>600</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B8" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C8" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D8">
         <v>5000</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B9" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C9" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D9">
         <v>3500</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B10" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C10" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D10">
         <v>2600</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C11" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D11">
         <v>700</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C12" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D12">
         <v>1200</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B13" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C13" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D13">
         <v>2200</v>
@@ -2223,63 +2318,63 @@
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B1" t="s">
         <v>42</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
+        <v>113</v>
+      </c>
+      <c r="D1" t="s">
+        <v>116</v>
+      </c>
+      <c r="E1" t="s">
+        <v>115</v>
+      </c>
+      <c r="F1" t="s">
+        <v>114</v>
+      </c>
+      <c r="G1" t="s">
         <v>43</v>
       </c>
-      <c r="C1" t="s">
-        <v>114</v>
-      </c>
-      <c r="D1" t="s">
-        <v>117</v>
-      </c>
-      <c r="E1" t="s">
-        <v>116</v>
-      </c>
-      <c r="F1" t="s">
-        <v>115</v>
-      </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>44</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>45</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>46</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>47</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>48</v>
-      </c>
-      <c r="L1" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B2" t="s">
         <v>50</v>
       </c>
-      <c r="B2" t="s">
-        <v>51</v>
-      </c>
       <c r="C2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E2">
         <v>21925</v>
       </c>
       <c r="F2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="G2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H2">
         <v>4700</v>
@@ -2296,25 +2391,25 @@
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B3" t="s">
         <v>53</v>
       </c>
-      <c r="B3" t="s">
-        <v>54</v>
-      </c>
       <c r="C3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E3">
         <v>25122</v>
       </c>
       <c r="F3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="G3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H3">
         <v>3200</v>
@@ -2328,28 +2423,31 @@
       <c r="K3">
         <v>500</v>
       </c>
+      <c r="P3" t="s">
+        <v>205</v>
+      </c>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
+        <v>55</v>
+      </c>
+      <c r="B4" t="s">
         <v>56</v>
       </c>
-      <c r="B4" t="s">
-        <v>57</v>
-      </c>
       <c r="C4" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D4" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E4">
         <v>20950</v>
       </c>
       <c r="F4" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H4">
         <v>3400</v>
@@ -2364,33 +2462,33 @@
         <v>800</v>
       </c>
       <c r="P4" t="s">
+        <v>129</v>
+      </c>
+      <c r="Q4" t="s">
         <v>130</v>
-      </c>
-      <c r="Q4" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
+        <v>57</v>
+      </c>
+      <c r="B5" t="s">
         <v>58</v>
       </c>
-      <c r="B5" t="s">
-        <v>59</v>
-      </c>
       <c r="C5" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D5" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E5">
         <v>22132</v>
       </c>
       <c r="F5" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="G5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H5">
         <v>5000</v>
@@ -2405,33 +2503,33 @@
         <v>1000</v>
       </c>
       <c r="P5" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="Q5" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
+        <v>60</v>
+      </c>
+      <c r="B6" t="s">
         <v>61</v>
       </c>
-      <c r="B6" t="s">
-        <v>62</v>
-      </c>
       <c r="C6" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D6" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E6">
         <v>21220</v>
       </c>
       <c r="F6" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="G6" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H6">
         <v>4500</v>
@@ -2448,25 +2546,25 @@
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
+        <v>62</v>
+      </c>
+      <c r="B7" t="s">
         <v>63</v>
       </c>
-      <c r="B7" t="s">
-        <v>64</v>
-      </c>
       <c r="C7" t="s">
+        <v>122</v>
+      </c>
+      <c r="D7" t="s">
         <v>123</v>
-      </c>
-      <c r="D7" t="s">
-        <v>124</v>
       </c>
       <c r="E7">
         <v>21248</v>
       </c>
       <c r="F7" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="G7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H7">
         <v>3800</v>
@@ -2483,25 +2581,25 @@
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
+        <v>64</v>
+      </c>
+      <c r="B8" t="s">
         <v>65</v>
       </c>
-      <c r="B8" t="s">
-        <v>66</v>
-      </c>
       <c r="C8" t="s">
+        <v>122</v>
+      </c>
+      <c r="D8" t="s">
         <v>123</v>
-      </c>
-      <c r="D8" t="s">
-        <v>124</v>
       </c>
       <c r="E8">
         <v>22951</v>
       </c>
       <c r="F8" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="G8" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H8">
         <v>4300</v>
@@ -2518,25 +2616,25 @@
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
+        <v>66</v>
+      </c>
+      <c r="B9" t="s">
         <v>67</v>
       </c>
-      <c r="B9" t="s">
-        <v>68</v>
-      </c>
       <c r="C9" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D9" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E9">
         <v>20616</v>
       </c>
       <c r="F9" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G9" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H9">
         <v>4500</v>
@@ -2553,25 +2651,25 @@
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
+        <v>68</v>
+      </c>
+      <c r="B10" t="s">
         <v>69</v>
       </c>
-      <c r="B10" t="s">
-        <v>70</v>
-      </c>
       <c r="C10" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D10" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E10">
         <v>21956</v>
       </c>
       <c r="F10" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G10" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H10">
         <v>4600</v>
@@ -2588,25 +2686,25 @@
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
+        <v>71</v>
+      </c>
+      <c r="B11" t="s">
         <v>72</v>
       </c>
-      <c r="B11" t="s">
-        <v>73</v>
-      </c>
       <c r="C11" t="s">
+        <v>122</v>
+      </c>
+      <c r="D11" t="s">
         <v>123</v>
-      </c>
-      <c r="D11" t="s">
-        <v>124</v>
       </c>
       <c r="E11">
         <v>25851</v>
       </c>
       <c r="F11" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G11" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H11">
         <v>3700</v>
@@ -2629,35 +2727,38 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{91A735B0-C993-4BCF-AB27-DE2EEDBA9C95}">
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:K18"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
+        <v>107</v>
+      </c>
+      <c r="B1" t="s">
         <v>108</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>109</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>110</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>111</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>112</v>
       </c>
-      <c r="F1" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="K1" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C2">
         <v>90</v>
@@ -2672,13 +2773,16 @@
         <f t="shared" ref="F2:F18" si="0">C2+D2+E2</f>
         <v>248</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="K2" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C3">
         <v>96</v>
@@ -2694,12 +2798,12 @@
         <v>285</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C4">
         <v>68</v>
@@ -2715,12 +2819,12 @@
         <v>259</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B5" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C5">
         <v>78</v>
@@ -2736,12 +2840,12 @@
         <v>248</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C6">
         <v>75</v>
@@ -2757,12 +2861,12 @@
         <v>251</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B7" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C7">
         <v>87</v>
@@ -2778,12 +2882,12 @@
         <v>269</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C8">
         <v>85</v>
@@ -2799,12 +2903,12 @@
         <v>270</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B9" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C9">
         <v>75</v>
@@ -2820,12 +2924,12 @@
         <v>244</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B10" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C10">
         <v>88</v>
@@ -2841,12 +2945,12 @@
         <v>256</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B11" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C11">
         <v>96</v>
@@ -2862,12 +2966,12 @@
         <v>275</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B12" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C12">
         <v>95</v>
@@ -2883,12 +2987,12 @@
         <v>274</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B13" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C13">
         <v>90</v>
@@ -2904,12 +3008,12 @@
         <v>267</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B14" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C14">
         <v>86</v>
@@ -2925,12 +3029,12 @@
         <v>262</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B15" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C15">
         <v>86</v>
@@ -2946,12 +3050,12 @@
         <v>258</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B16" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C16">
         <v>98</v>
@@ -2969,10 +3073,10 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B17" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C17">
         <v>97</v>
@@ -2990,10 +3094,10 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B18" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C18">
         <v>96</v>
@@ -3007,6 +3111,57 @@
       <c r="F18">
         <f t="shared" si="0"/>
         <v>287</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6579603A-B2D6-4548-A73D-81A72F0DE6E5}">
+  <dimension ref="A1:A12"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>215</v>
       </c>
     </row>
   </sheetData>

--- a/office/data/实验数据.xlsx
+++ b/office/data/实验数据.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F8F94D9-FDB1-403A-98F0-2413BFB90A31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{2E5A61E7-CF82-4D7E-B994-D412ADB0B79D}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{2E5A61E7-CF82-4D7E-B994-D412ADB0B79D}"/>
   </bookViews>
   <sheets>
     <sheet name="通信录" sheetId="6" r:id="rId1"/>
@@ -890,7 +890,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -901,12 +901,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -2035,22 +2029,13 @@
       </c>
       <c r="C25" s="3"/>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="C26" s="4"/>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="C27" s="4"/>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="C28" s="4"/>
-    </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>219</v>
       </c>
     </row>
-    <row r="30" spans="1:6" s="5" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="5" t="s">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A30" t="s">
         <v>220</v>
       </c>
     </row>

--- a/office/data/实验数据.xlsx
+++ b/office/data/实验数据.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\glplaman.github.io\office\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F8F94D9-FDB1-403A-98F0-2413BFB90A31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C90C20E-F14B-4961-9BAF-D41009B9ADAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{2E5A61E7-CF82-4D7E-B994-D412ADB0B79D}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{2E5A61E7-CF82-4D7E-B994-D412ADB0B79D}"/>
   </bookViews>
   <sheets>
     <sheet name="通信录" sheetId="6" r:id="rId1"/>
@@ -23,6 +23,8 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">工资收入!$A$1:$L$11</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">学生成绩!$A$1:$K$16</definedName>
+    <definedName name="_xlchart.v1.0" hidden="1">高考成绩!$C$2:$C$18</definedName>
+    <definedName name="_xlchart.v1.1" hidden="1">高考成绩!$C$2:$C$18</definedName>
     <definedName name="_xlnm.Criteria" localSheetId="3">工资收入!$P$4:$Q$5</definedName>
     <definedName name="_xlnm.Extract" localSheetId="3">工资收入!$P$13:$AA$13</definedName>
   </definedNames>
@@ -36,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="221">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="222">
   <si>
     <t>学号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -817,6 +819,10 @@
   </si>
   <si>
     <t>2. 五级成绩评定：优、良、中、及格、不及格</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3.使用直方图统计语文成绩的分布</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2782,6 +2788,9 @@
         <f t="shared" si="0"/>
         <v>285</v>
       </c>
+      <c r="K3" t="s">
+        <v>221</v>
+      </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A4" t="s">

--- a/office/data/实验数据.xlsx
+++ b/office/data/实验数据.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\glplaman.github.io\office\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C90C20E-F14B-4961-9BAF-D41009B9ADAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA02B4F1-54F3-43DA-937C-24CB35057382}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{2E5A61E7-CF82-4D7E-B994-D412ADB0B79D}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{2E5A61E7-CF82-4D7E-B994-D412ADB0B79D}"/>
   </bookViews>
   <sheets>
     <sheet name="通信录" sheetId="6" r:id="rId1"/>
@@ -23,8 +23,6 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">工资收入!$A$1:$L$11</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">学生成绩!$A$1:$K$16</definedName>
-    <definedName name="_xlchart.v1.0" hidden="1">高考成绩!$C$2:$C$18</definedName>
-    <definedName name="_xlchart.v1.1" hidden="1">高考成绩!$C$2:$C$18</definedName>
     <definedName name="_xlnm.Criteria" localSheetId="3">工资收入!$P$4:$Q$5</definedName>
     <definedName name="_xlnm.Extract" localSheetId="3">工资收入!$P$13:$AA$13</definedName>
   </definedNames>
@@ -38,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="222">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="317" uniqueCount="225">
   <si>
     <t>学号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -823,6 +821,18 @@
   </si>
   <si>
     <t>3.使用直方图统计语文成绩的分布</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>方案2：使用column(CELL) 求偏差</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>方案1：使用column() 求偏差</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>根据姓名查询多个数据</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -830,7 +840,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -858,6 +868,15 @@
       <color theme="10"/>
       <name val="等线"/>
       <family val="2"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -896,7 +915,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -907,6 +926,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1614,12 +1636,13 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DE67399F-CC12-4ABD-9F7C-F6EE52160CF4}">
-  <dimension ref="A1:K33"/>
+  <dimension ref="A1:N33"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10.5" bestFit="1" customWidth="1"/>
     <col min="3" max="11" width="10.625" customWidth="1"/>
+    <col min="14" max="14" width="30.875" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="7.5" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="7.5" bestFit="1" customWidth="1"/>
   </cols>
@@ -1959,7 +1982,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>105</v>
       </c>
@@ -1979,7 +2002,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>106</v>
       </c>
@@ -1999,58 +2022,81 @@
         <v>98</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="J19" t="s">
+        <v>2</v>
+      </c>
+      <c r="K19" t="s">
+        <v>3</v>
+      </c>
+      <c r="L19" t="s">
+        <v>4</v>
+      </c>
+      <c r="M19" t="s">
+        <v>6</v>
+      </c>
+      <c r="N19" s="4" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B20" t="s">
         <v>132</v>
       </c>
       <c r="C20" s="3"/>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="N20" s="4" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B21" t="s">
         <v>133</v>
       </c>
       <c r="C21" s="3"/>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B22" t="s">
         <v>134</v>
       </c>
       <c r="C22" s="3"/>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B23" t="s">
         <v>135</v>
       </c>
       <c r="C23" s="3"/>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B24" t="s">
         <v>136</v>
       </c>
       <c r="C24" s="3"/>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="N24" s="4" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B25" t="s">
         <v>137</v>
       </c>
       <c r="C25" s="3"/>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>219</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>217</v>
       </c>

--- a/office/data/实验数据.xlsx
+++ b/office/data/实验数据.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\glplaman.github.io\office\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA02B4F1-54F3-43DA-937C-24CB35057382}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9DB2157-016F-4A71-878B-5721DC6B00DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{2E5A61E7-CF82-4D7E-B994-D412ADB0B79D}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{2E5A61E7-CF82-4D7E-B994-D412ADB0B79D}"/>
   </bookViews>
   <sheets>
     <sheet name="通信录" sheetId="6" r:id="rId1"/>
@@ -19,6 +19,7 @@
     <sheet name="工资收入" sheetId="4" r:id="rId4"/>
     <sheet name="高考成绩" sheetId="5" r:id="rId5"/>
     <sheet name="迷你图" sheetId="7" r:id="rId6"/>
+    <sheet name="门店晚间收益" sheetId="8" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">工资收入!$A$1:$L$11</definedName>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="317" uniqueCount="225">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="933" uniqueCount="308">
   <si>
     <t>学号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -833,6 +834,335 @@
   </si>
   <si>
     <t>根据姓名查询多个数据</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>调查ID</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>年龄</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>婚姻状况</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>广告印象</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>光顾次数</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>光顾人数</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>消费金额</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>点过套餐</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>点过面类</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>点过盖浇饭</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>点过甜品</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>点过其他小食</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>点过饮料</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>点过酒类</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>已婚已育</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>无</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>无</t>
+  </si>
+  <si>
+    <t>有</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>已婚未育</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>有</t>
+  </si>
+  <si>
+    <t>11</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>13</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>未婚</t>
+  </si>
+  <si>
+    <t>17</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>26</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>未婚</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>28</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>32</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>36</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>45</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>48</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>53</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>56</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>58</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>62</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>63</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>67</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>69</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>71</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>74</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>75</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>78</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>79</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>83</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>86</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>五</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>88</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>93</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>97</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>103</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>105</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>107</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>110</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>121</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>124</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>128</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>134</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>146</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>152</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>167</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>178</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>185</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>190</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>193</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>197</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>201</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>205</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>209</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>213</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>215</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>217</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>218</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>224</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>226</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>227</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>230</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>231</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>235</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>240</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>出生日期</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -915,7 +1245,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -930,6 +1260,18 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -3208,4 +3550,3083 @@
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{415D4CE3-02B4-414E-8DBB-570449F0C690}">
+  <dimension ref="A1:S61"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="7" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="5.25" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.125" style="8" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="11" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="16.375" bestFit="1" customWidth="1"/>
+    <col min="20" max="26" width="15.625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A1" s="5" t="s">
+        <v>225</v>
+      </c>
+      <c r="B1" t="s">
+        <v>226</v>
+      </c>
+      <c r="C1" t="s">
+        <v>140</v>
+      </c>
+      <c r="D1" t="s">
+        <v>227</v>
+      </c>
+      <c r="E1" t="s">
+        <v>307</v>
+      </c>
+      <c r="F1" t="s">
+        <v>228</v>
+      </c>
+      <c r="G1" t="s">
+        <v>229</v>
+      </c>
+      <c r="H1" t="s">
+        <v>230</v>
+      </c>
+      <c r="I1" t="s">
+        <v>231</v>
+      </c>
+      <c r="J1" t="s">
+        <v>232</v>
+      </c>
+      <c r="K1" t="s">
+        <v>233</v>
+      </c>
+      <c r="L1" t="s">
+        <v>234</v>
+      </c>
+      <c r="M1" t="s">
+        <v>235</v>
+      </c>
+      <c r="N1" t="s">
+        <v>236</v>
+      </c>
+      <c r="O1" t="s">
+        <v>237</v>
+      </c>
+      <c r="P1" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A2" s="5" t="s">
+        <v>239</v>
+      </c>
+      <c r="B2">
+        <v>50</v>
+      </c>
+      <c r="C2" t="s">
+        <v>146</v>
+      </c>
+      <c r="D2" t="s">
+        <v>240</v>
+      </c>
+      <c r="E2" s="7">
+        <v>40945</v>
+      </c>
+      <c r="F2">
+        <v>3</v>
+      </c>
+      <c r="G2">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="I2">
+        <v>48</v>
+      </c>
+      <c r="J2" t="s">
+        <v>241</v>
+      </c>
+      <c r="K2" t="s">
+        <v>242</v>
+      </c>
+      <c r="L2" t="s">
+        <v>243</v>
+      </c>
+      <c r="M2" t="s">
+        <v>242</v>
+      </c>
+      <c r="N2" t="s">
+        <v>242</v>
+      </c>
+      <c r="O2" t="s">
+        <v>242</v>
+      </c>
+      <c r="P2" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A3" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="B3">
+        <v>50</v>
+      </c>
+      <c r="C3" t="s">
+        <v>143</v>
+      </c>
+      <c r="D3" t="s">
+        <v>240</v>
+      </c>
+      <c r="E3" s="7">
+        <v>40085</v>
+      </c>
+      <c r="F3">
+        <v>2</v>
+      </c>
+      <c r="G3">
+        <v>2</v>
+      </c>
+      <c r="H3">
+        <v>2</v>
+      </c>
+      <c r="I3">
+        <v>680</v>
+      </c>
+      <c r="J3" t="s">
+        <v>241</v>
+      </c>
+      <c r="K3" t="s">
+        <v>243</v>
+      </c>
+      <c r="L3" t="s">
+        <v>242</v>
+      </c>
+      <c r="M3" t="s">
+        <v>241</v>
+      </c>
+      <c r="N3" t="s">
+        <v>243</v>
+      </c>
+      <c r="O3" t="s">
+        <v>243</v>
+      </c>
+      <c r="P3" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A4" s="5" t="s">
+        <v>245</v>
+      </c>
+      <c r="B4">
+        <v>27</v>
+      </c>
+      <c r="C4" t="s">
+        <v>143</v>
+      </c>
+      <c r="D4" t="s">
+        <v>246</v>
+      </c>
+      <c r="E4" s="7">
+        <v>42895</v>
+      </c>
+      <c r="F4">
+        <v>3</v>
+      </c>
+      <c r="G4">
+        <v>3</v>
+      </c>
+      <c r="H4">
+        <v>3</v>
+      </c>
+      <c r="I4">
+        <v>260</v>
+      </c>
+      <c r="J4" t="s">
+        <v>242</v>
+      </c>
+      <c r="K4" t="s">
+        <v>242</v>
+      </c>
+      <c r="L4" t="s">
+        <v>247</v>
+      </c>
+      <c r="M4" t="s">
+        <v>242</v>
+      </c>
+      <c r="N4" t="s">
+        <v>247</v>
+      </c>
+      <c r="O4" t="s">
+        <v>241</v>
+      </c>
+      <c r="P4" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A5" s="5" t="s">
+        <v>248</v>
+      </c>
+      <c r="B5">
+        <v>28</v>
+      </c>
+      <c r="C5" t="s">
+        <v>143</v>
+      </c>
+      <c r="D5" t="s">
+        <v>246</v>
+      </c>
+      <c r="E5" s="7">
+        <v>43016</v>
+      </c>
+      <c r="F5">
+        <v>3</v>
+      </c>
+      <c r="G5">
+        <v>3</v>
+      </c>
+      <c r="H5">
+        <v>2</v>
+      </c>
+      <c r="I5">
+        <v>180</v>
+      </c>
+      <c r="J5" t="s">
+        <v>241</v>
+      </c>
+      <c r="K5" t="s">
+        <v>243</v>
+      </c>
+      <c r="L5" t="s">
+        <v>242</v>
+      </c>
+      <c r="M5" t="s">
+        <v>241</v>
+      </c>
+      <c r="N5" t="s">
+        <v>243</v>
+      </c>
+      <c r="O5" t="s">
+        <v>243</v>
+      </c>
+      <c r="P5" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A6" s="5" t="s">
+        <v>249</v>
+      </c>
+      <c r="B6">
+        <v>24</v>
+      </c>
+      <c r="C6" t="s">
+        <v>143</v>
+      </c>
+      <c r="D6" t="s">
+        <v>250</v>
+      </c>
+      <c r="E6" s="7">
+        <v>40146</v>
+      </c>
+      <c r="F6">
+        <v>3</v>
+      </c>
+      <c r="G6">
+        <v>2</v>
+      </c>
+      <c r="H6">
+        <v>3</v>
+      </c>
+      <c r="I6">
+        <v>280</v>
+      </c>
+      <c r="J6" t="s">
+        <v>241</v>
+      </c>
+      <c r="K6" t="s">
+        <v>243</v>
+      </c>
+      <c r="L6" t="s">
+        <v>247</v>
+      </c>
+      <c r="M6" t="s">
+        <v>243</v>
+      </c>
+      <c r="N6" t="s">
+        <v>243</v>
+      </c>
+      <c r="O6" t="s">
+        <v>241</v>
+      </c>
+      <c r="P6" t="s">
+        <v>242</v>
+      </c>
+      <c r="S6" s="2"/>
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A7" s="5" t="s">
+        <v>251</v>
+      </c>
+      <c r="B7">
+        <v>36</v>
+      </c>
+      <c r="C7" t="s">
+        <v>146</v>
+      </c>
+      <c r="D7" t="s">
+        <v>240</v>
+      </c>
+      <c r="E7" s="7">
+        <v>39052</v>
+      </c>
+      <c r="F7">
+        <v>3</v>
+      </c>
+      <c r="G7">
+        <v>2</v>
+      </c>
+      <c r="H7">
+        <v>1</v>
+      </c>
+      <c r="I7">
+        <v>50</v>
+      </c>
+      <c r="J7" t="s">
+        <v>243</v>
+      </c>
+      <c r="K7" t="s">
+        <v>241</v>
+      </c>
+      <c r="L7" t="s">
+        <v>241</v>
+      </c>
+      <c r="M7" t="s">
+        <v>243</v>
+      </c>
+      <c r="N7" t="s">
+        <v>241</v>
+      </c>
+      <c r="O7" t="s">
+        <v>242</v>
+      </c>
+      <c r="P7" t="s">
+        <v>241</v>
+      </c>
+      <c r="S7" s="2"/>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A8" s="5" t="s">
+        <v>252</v>
+      </c>
+      <c r="B8">
+        <v>29</v>
+      </c>
+      <c r="C8" t="s">
+        <v>146</v>
+      </c>
+      <c r="D8" t="s">
+        <v>253</v>
+      </c>
+      <c r="E8" s="7">
+        <v>36677</v>
+      </c>
+      <c r="F8">
+        <v>3</v>
+      </c>
+      <c r="G8">
+        <v>3</v>
+      </c>
+      <c r="H8">
+        <v>1</v>
+      </c>
+      <c r="I8">
+        <v>60</v>
+      </c>
+      <c r="J8" t="s">
+        <v>241</v>
+      </c>
+      <c r="K8" t="s">
+        <v>241</v>
+      </c>
+      <c r="L8" t="s">
+        <v>243</v>
+      </c>
+      <c r="M8" t="s">
+        <v>243</v>
+      </c>
+      <c r="N8" t="s">
+        <v>241</v>
+      </c>
+      <c r="O8" t="s">
+        <v>241</v>
+      </c>
+      <c r="P8" t="s">
+        <v>241</v>
+      </c>
+      <c r="S8" s="2"/>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A9" s="5" t="s">
+        <v>254</v>
+      </c>
+      <c r="B9">
+        <v>53</v>
+      </c>
+      <c r="C9" t="s">
+        <v>143</v>
+      </c>
+      <c r="D9" t="s">
+        <v>240</v>
+      </c>
+      <c r="E9" s="7">
+        <v>39861</v>
+      </c>
+      <c r="F9">
+        <v>3</v>
+      </c>
+      <c r="G9">
+        <v>1</v>
+      </c>
+      <c r="H9">
+        <v>3</v>
+      </c>
+      <c r="I9">
+        <v>870</v>
+      </c>
+      <c r="J9" t="s">
+        <v>241</v>
+      </c>
+      <c r="K9" t="s">
+        <v>243</v>
+      </c>
+      <c r="L9" t="s">
+        <v>241</v>
+      </c>
+      <c r="M9" t="s">
+        <v>243</v>
+      </c>
+      <c r="N9" t="s">
+        <v>243</v>
+      </c>
+      <c r="O9" t="s">
+        <v>241</v>
+      </c>
+      <c r="P9" t="s">
+        <v>243</v>
+      </c>
+      <c r="S9" s="2"/>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A10" s="5" t="s">
+        <v>255</v>
+      </c>
+      <c r="B10">
+        <v>32</v>
+      </c>
+      <c r="C10" t="s">
+        <v>143</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>253</v>
+      </c>
+      <c r="E10" s="7">
+        <v>37867</v>
+      </c>
+      <c r="F10">
+        <v>3</v>
+      </c>
+      <c r="G10">
+        <v>2</v>
+      </c>
+      <c r="H10">
+        <v>1</v>
+      </c>
+      <c r="I10">
+        <v>120</v>
+      </c>
+      <c r="J10" t="s">
+        <v>241</v>
+      </c>
+      <c r="K10" t="s">
+        <v>241</v>
+      </c>
+      <c r="L10" t="s">
+        <v>243</v>
+      </c>
+      <c r="M10" t="s">
+        <v>241</v>
+      </c>
+      <c r="N10" t="s">
+        <v>243</v>
+      </c>
+      <c r="O10" t="s">
+        <v>241</v>
+      </c>
+      <c r="P10" t="s">
+        <v>243</v>
+      </c>
+      <c r="S10" s="2"/>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A11" s="5" t="s">
+        <v>256</v>
+      </c>
+      <c r="B11">
+        <v>45</v>
+      </c>
+      <c r="C11" t="s">
+        <v>146</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>246</v>
+      </c>
+      <c r="E11" s="7">
+        <v>43561</v>
+      </c>
+      <c r="F11">
+        <v>3</v>
+      </c>
+      <c r="G11">
+        <v>3</v>
+      </c>
+      <c r="H11">
+        <v>1</v>
+      </c>
+      <c r="I11">
+        <v>100</v>
+      </c>
+      <c r="J11" t="s">
+        <v>243</v>
+      </c>
+      <c r="K11" t="s">
+        <v>241</v>
+      </c>
+      <c r="L11" t="s">
+        <v>241</v>
+      </c>
+      <c r="M11" t="s">
+        <v>243</v>
+      </c>
+      <c r="N11" t="s">
+        <v>241</v>
+      </c>
+      <c r="O11" t="s">
+        <v>241</v>
+      </c>
+      <c r="P11" t="s">
+        <v>241</v>
+      </c>
+      <c r="S11" s="2"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A12" s="5" t="s">
+        <v>257</v>
+      </c>
+      <c r="B12">
+        <v>20</v>
+      </c>
+      <c r="C12" t="s">
+        <v>146</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>253</v>
+      </c>
+      <c r="E12" s="7">
+        <v>37417</v>
+      </c>
+      <c r="F12">
+        <v>3</v>
+      </c>
+      <c r="G12">
+        <v>2</v>
+      </c>
+      <c r="H12">
+        <v>2</v>
+      </c>
+      <c r="I12">
+        <v>120</v>
+      </c>
+      <c r="J12" t="s">
+        <v>241</v>
+      </c>
+      <c r="K12" t="s">
+        <v>243</v>
+      </c>
+      <c r="L12" t="s">
+        <v>243</v>
+      </c>
+      <c r="M12" t="s">
+        <v>243</v>
+      </c>
+      <c r="N12" t="s">
+        <v>241</v>
+      </c>
+      <c r="O12" t="s">
+        <v>241</v>
+      </c>
+      <c r="P12" t="s">
+        <v>241</v>
+      </c>
+      <c r="S12" s="2"/>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A13" s="5" t="s">
+        <v>258</v>
+      </c>
+      <c r="B13">
+        <v>33</v>
+      </c>
+      <c r="C13" t="s">
+        <v>146</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>246</v>
+      </c>
+      <c r="E13" s="7">
+        <v>41971</v>
+      </c>
+      <c r="F13">
+        <v>3</v>
+      </c>
+      <c r="G13">
+        <v>2</v>
+      </c>
+      <c r="H13">
+        <v>2</v>
+      </c>
+      <c r="I13">
+        <v>150</v>
+      </c>
+      <c r="J13" t="s">
+        <v>241</v>
+      </c>
+      <c r="K13" t="s">
+        <v>241</v>
+      </c>
+      <c r="L13" t="s">
+        <v>243</v>
+      </c>
+      <c r="M13" t="s">
+        <v>243</v>
+      </c>
+      <c r="N13" t="s">
+        <v>243</v>
+      </c>
+      <c r="O13" t="s">
+        <v>241</v>
+      </c>
+      <c r="P13" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A14" s="5" t="s">
+        <v>259</v>
+      </c>
+      <c r="B14">
+        <v>23</v>
+      </c>
+      <c r="C14" t="s">
+        <v>143</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>253</v>
+      </c>
+      <c r="E14" s="7">
+        <v>38717</v>
+      </c>
+      <c r="F14">
+        <v>3</v>
+      </c>
+      <c r="G14">
+        <v>3</v>
+      </c>
+      <c r="H14">
+        <v>2</v>
+      </c>
+      <c r="I14">
+        <v>100</v>
+      </c>
+      <c r="J14" t="s">
+        <v>241</v>
+      </c>
+      <c r="K14" t="s">
+        <v>243</v>
+      </c>
+      <c r="L14" t="s">
+        <v>241</v>
+      </c>
+      <c r="M14" t="s">
+        <v>243</v>
+      </c>
+      <c r="N14" t="s">
+        <v>243</v>
+      </c>
+      <c r="O14" t="s">
+        <v>241</v>
+      </c>
+      <c r="P14" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A15" s="5" t="s">
+        <v>260</v>
+      </c>
+      <c r="B15">
+        <v>40</v>
+      </c>
+      <c r="C15" t="s">
+        <v>143</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>253</v>
+      </c>
+      <c r="E15" s="7">
+        <v>36811</v>
+      </c>
+      <c r="F15">
+        <v>3</v>
+      </c>
+      <c r="G15">
+        <v>1</v>
+      </c>
+      <c r="H15">
+        <v>2</v>
+      </c>
+      <c r="I15">
+        <v>280</v>
+      </c>
+      <c r="J15" t="s">
+        <v>241</v>
+      </c>
+      <c r="K15" t="s">
+        <v>243</v>
+      </c>
+      <c r="L15" t="s">
+        <v>241</v>
+      </c>
+      <c r="M15" t="s">
+        <v>241</v>
+      </c>
+      <c r="N15" t="s">
+        <v>243</v>
+      </c>
+      <c r="O15" t="s">
+        <v>241</v>
+      </c>
+      <c r="P15" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A16" s="5" t="s">
+        <v>261</v>
+      </c>
+      <c r="B16">
+        <v>42</v>
+      </c>
+      <c r="C16" t="s">
+        <v>146</v>
+      </c>
+      <c r="D16" t="s">
+        <v>240</v>
+      </c>
+      <c r="E16" s="7">
+        <v>43610</v>
+      </c>
+      <c r="F16">
+        <v>3</v>
+      </c>
+      <c r="G16">
+        <v>1</v>
+      </c>
+      <c r="H16">
+        <v>2</v>
+      </c>
+      <c r="I16">
+        <v>200</v>
+      </c>
+      <c r="J16" t="s">
+        <v>241</v>
+      </c>
+      <c r="K16" t="s">
+        <v>243</v>
+      </c>
+      <c r="L16" t="s">
+        <v>242</v>
+      </c>
+      <c r="M16" t="s">
+        <v>243</v>
+      </c>
+      <c r="N16" t="s">
+        <v>243</v>
+      </c>
+      <c r="O16" t="s">
+        <v>242</v>
+      </c>
+      <c r="P16" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A17" s="5" t="s">
+        <v>262</v>
+      </c>
+      <c r="B17">
+        <v>46</v>
+      </c>
+      <c r="C17" t="s">
+        <v>143</v>
+      </c>
+      <c r="D17" t="s">
+        <v>246</v>
+      </c>
+      <c r="E17" s="7">
+        <v>43111</v>
+      </c>
+      <c r="F17">
+        <v>2</v>
+      </c>
+      <c r="G17">
+        <v>1</v>
+      </c>
+      <c r="H17">
+        <v>2</v>
+      </c>
+      <c r="I17">
+        <v>380</v>
+      </c>
+      <c r="J17" t="s">
+        <v>241</v>
+      </c>
+      <c r="K17" t="s">
+        <v>243</v>
+      </c>
+      <c r="L17" t="s">
+        <v>242</v>
+      </c>
+      <c r="M17" t="s">
+        <v>241</v>
+      </c>
+      <c r="N17" t="s">
+        <v>243</v>
+      </c>
+      <c r="O17" t="s">
+        <v>241</v>
+      </c>
+      <c r="P17" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A18" s="5" t="s">
+        <v>263</v>
+      </c>
+      <c r="B18">
+        <v>27</v>
+      </c>
+      <c r="C18" t="s">
+        <v>146</v>
+      </c>
+      <c r="D18" t="s">
+        <v>250</v>
+      </c>
+      <c r="E18" s="7">
+        <v>42037</v>
+      </c>
+      <c r="F18">
+        <v>3</v>
+      </c>
+      <c r="G18">
+        <v>3</v>
+      </c>
+      <c r="H18">
+        <v>2</v>
+      </c>
+      <c r="I18">
+        <v>210</v>
+      </c>
+      <c r="J18" t="s">
+        <v>242</v>
+      </c>
+      <c r="K18" t="s">
+        <v>243</v>
+      </c>
+      <c r="L18" t="s">
+        <v>241</v>
+      </c>
+      <c r="M18" t="s">
+        <v>243</v>
+      </c>
+      <c r="N18" t="s">
+        <v>247</v>
+      </c>
+      <c r="O18" t="s">
+        <v>241</v>
+      </c>
+      <c r="P18" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A19" s="5" t="s">
+        <v>264</v>
+      </c>
+      <c r="B19">
+        <v>33</v>
+      </c>
+      <c r="C19" t="s">
+        <v>146</v>
+      </c>
+      <c r="D19" t="s">
+        <v>246</v>
+      </c>
+      <c r="E19" s="7">
+        <v>42820</v>
+      </c>
+      <c r="F19">
+        <v>3</v>
+      </c>
+      <c r="G19">
+        <v>2</v>
+      </c>
+      <c r="H19">
+        <v>1</v>
+      </c>
+      <c r="I19">
+        <v>48</v>
+      </c>
+      <c r="J19" t="s">
+        <v>241</v>
+      </c>
+      <c r="K19" t="s">
+        <v>242</v>
+      </c>
+      <c r="L19" t="s">
+        <v>243</v>
+      </c>
+      <c r="M19" t="s">
+        <v>241</v>
+      </c>
+      <c r="N19" t="s">
+        <v>242</v>
+      </c>
+      <c r="O19" t="s">
+        <v>242</v>
+      </c>
+      <c r="P19" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A20" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="B20">
+        <v>18</v>
+      </c>
+      <c r="C20" t="s">
+        <v>143</v>
+      </c>
+      <c r="D20" t="s">
+        <v>250</v>
+      </c>
+      <c r="E20" s="7">
+        <v>41940</v>
+      </c>
+      <c r="F20">
+        <v>3</v>
+      </c>
+      <c r="G20">
+        <v>2</v>
+      </c>
+      <c r="H20">
+        <v>3</v>
+      </c>
+      <c r="I20">
+        <v>160</v>
+      </c>
+      <c r="J20" t="s">
+        <v>241</v>
+      </c>
+      <c r="K20" t="s">
+        <v>243</v>
+      </c>
+      <c r="L20" t="s">
+        <v>241</v>
+      </c>
+      <c r="M20" t="s">
+        <v>241</v>
+      </c>
+      <c r="N20" t="s">
+        <v>243</v>
+      </c>
+      <c r="O20" t="s">
+        <v>243</v>
+      </c>
+      <c r="P20" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A21" s="5" t="s">
+        <v>266</v>
+      </c>
+      <c r="B21">
+        <v>35</v>
+      </c>
+      <c r="C21" t="s">
+        <v>146</v>
+      </c>
+      <c r="D21" t="s">
+        <v>240</v>
+      </c>
+      <c r="E21" s="7">
+        <v>40444</v>
+      </c>
+      <c r="F21">
+        <v>3</v>
+      </c>
+      <c r="G21">
+        <v>2</v>
+      </c>
+      <c r="H21">
+        <v>1</v>
+      </c>
+      <c r="I21">
+        <v>48</v>
+      </c>
+      <c r="J21" t="s">
+        <v>241</v>
+      </c>
+      <c r="K21" t="s">
+        <v>242</v>
+      </c>
+      <c r="L21" t="s">
+        <v>243</v>
+      </c>
+      <c r="M21" t="s">
+        <v>241</v>
+      </c>
+      <c r="N21" t="s">
+        <v>242</v>
+      </c>
+      <c r="O21" t="s">
+        <v>242</v>
+      </c>
+      <c r="P21" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A22" s="5" t="s">
+        <v>267</v>
+      </c>
+      <c r="B22">
+        <v>17</v>
+      </c>
+      <c r="C22" t="s">
+        <v>146</v>
+      </c>
+      <c r="D22" t="s">
+        <v>253</v>
+      </c>
+      <c r="E22" s="7">
+        <v>36758</v>
+      </c>
+      <c r="F22">
+        <v>3</v>
+      </c>
+      <c r="G22">
+        <v>1</v>
+      </c>
+      <c r="H22">
+        <v>1</v>
+      </c>
+      <c r="I22">
+        <v>48</v>
+      </c>
+      <c r="J22" t="s">
+        <v>241</v>
+      </c>
+      <c r="K22" t="s">
+        <v>241</v>
+      </c>
+      <c r="L22" t="s">
+        <v>243</v>
+      </c>
+      <c r="M22" t="s">
+        <v>241</v>
+      </c>
+      <c r="N22" t="s">
+        <v>241</v>
+      </c>
+      <c r="O22" t="s">
+        <v>241</v>
+      </c>
+      <c r="P22" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A23" s="5" t="s">
+        <v>268</v>
+      </c>
+      <c r="B23">
+        <v>47</v>
+      </c>
+      <c r="C23" t="s">
+        <v>146</v>
+      </c>
+      <c r="D23" t="s">
+        <v>240</v>
+      </c>
+      <c r="E23" s="7">
+        <v>38062</v>
+      </c>
+      <c r="F23">
+        <v>3</v>
+      </c>
+      <c r="G23">
+        <v>1</v>
+      </c>
+      <c r="H23">
+        <v>1</v>
+      </c>
+      <c r="I23">
+        <v>48</v>
+      </c>
+      <c r="J23" t="s">
+        <v>241</v>
+      </c>
+      <c r="K23" t="s">
+        <v>241</v>
+      </c>
+      <c r="L23" t="s">
+        <v>243</v>
+      </c>
+      <c r="M23" t="s">
+        <v>241</v>
+      </c>
+      <c r="N23" t="s">
+        <v>241</v>
+      </c>
+      <c r="O23" t="s">
+        <v>241</v>
+      </c>
+      <c r="P23" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A24" s="5" t="s">
+        <v>269</v>
+      </c>
+      <c r="B24">
+        <v>35</v>
+      </c>
+      <c r="C24" t="s">
+        <v>143</v>
+      </c>
+      <c r="D24" s="6" t="s">
+        <v>240</v>
+      </c>
+      <c r="E24" s="7">
+        <v>37911</v>
+      </c>
+      <c r="F24">
+        <v>3</v>
+      </c>
+      <c r="G24">
+        <v>1</v>
+      </c>
+      <c r="H24">
+        <v>2</v>
+      </c>
+      <c r="I24">
+        <v>280</v>
+      </c>
+      <c r="J24" t="s">
+        <v>241</v>
+      </c>
+      <c r="K24" t="s">
+        <v>243</v>
+      </c>
+      <c r="L24" t="s">
+        <v>241</v>
+      </c>
+      <c r="M24" t="s">
+        <v>241</v>
+      </c>
+      <c r="N24" t="s">
+        <v>243</v>
+      </c>
+      <c r="O24" t="s">
+        <v>241</v>
+      </c>
+      <c r="P24" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="25" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A25" s="5" t="s">
+        <v>270</v>
+      </c>
+      <c r="B25">
+        <v>19</v>
+      </c>
+      <c r="C25" t="s">
+        <v>146</v>
+      </c>
+      <c r="D25" s="6" t="s">
+        <v>253</v>
+      </c>
+      <c r="E25" s="7">
+        <v>42927</v>
+      </c>
+      <c r="F25">
+        <v>3</v>
+      </c>
+      <c r="G25">
+        <v>2</v>
+      </c>
+      <c r="H25">
+        <v>1</v>
+      </c>
+      <c r="I25">
+        <v>68</v>
+      </c>
+      <c r="J25" t="s">
+        <v>241</v>
+      </c>
+      <c r="K25" t="s">
+        <v>241</v>
+      </c>
+      <c r="L25" t="s">
+        <v>243</v>
+      </c>
+      <c r="M25" t="s">
+        <v>243</v>
+      </c>
+      <c r="N25" t="s">
+        <v>241</v>
+      </c>
+      <c r="O25" t="s">
+        <v>241</v>
+      </c>
+      <c r="P25" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="26" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A26" s="5" t="s">
+        <v>271</v>
+      </c>
+      <c r="B26">
+        <v>20</v>
+      </c>
+      <c r="C26" t="s">
+        <v>146</v>
+      </c>
+      <c r="D26" s="6" t="s">
+        <v>253</v>
+      </c>
+      <c r="E26" s="7">
+        <v>41560</v>
+      </c>
+      <c r="F26">
+        <v>3</v>
+      </c>
+      <c r="G26">
+        <v>1</v>
+      </c>
+      <c r="H26">
+        <v>2</v>
+      </c>
+      <c r="I26">
+        <v>100</v>
+      </c>
+      <c r="J26" t="s">
+        <v>241</v>
+      </c>
+      <c r="K26" t="s">
+        <v>243</v>
+      </c>
+      <c r="L26" t="s">
+        <v>241</v>
+      </c>
+      <c r="M26" t="s">
+        <v>243</v>
+      </c>
+      <c r="N26" t="s">
+        <v>241</v>
+      </c>
+      <c r="O26" t="s">
+        <v>241</v>
+      </c>
+      <c r="P26" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="27" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A27" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="B27">
+        <v>33</v>
+      </c>
+      <c r="C27" t="s">
+        <v>143</v>
+      </c>
+      <c r="D27" s="6" t="s">
+        <v>253</v>
+      </c>
+      <c r="E27" s="7">
+        <v>42886</v>
+      </c>
+      <c r="F27">
+        <v>3</v>
+      </c>
+      <c r="G27">
+        <v>1</v>
+      </c>
+      <c r="H27">
+        <v>1</v>
+      </c>
+      <c r="I27">
+        <v>100</v>
+      </c>
+      <c r="J27" t="s">
+        <v>241</v>
+      </c>
+      <c r="K27" t="s">
+        <v>243</v>
+      </c>
+      <c r="L27" t="s">
+        <v>241</v>
+      </c>
+      <c r="M27" t="s">
+        <v>273</v>
+      </c>
+      <c r="N27" t="s">
+        <v>243</v>
+      </c>
+      <c r="O27" t="s">
+        <v>243</v>
+      </c>
+      <c r="P27" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="28" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A28" s="5" t="s">
+        <v>274</v>
+      </c>
+      <c r="B28">
+        <v>23</v>
+      </c>
+      <c r="C28" t="s">
+        <v>143</v>
+      </c>
+      <c r="D28" s="6" t="s">
+        <v>253</v>
+      </c>
+      <c r="E28" s="7">
+        <v>39345</v>
+      </c>
+      <c r="F28">
+        <v>3</v>
+      </c>
+      <c r="G28">
+        <v>1</v>
+      </c>
+      <c r="H28">
+        <v>1</v>
+      </c>
+      <c r="I28">
+        <v>80</v>
+      </c>
+      <c r="J28" t="s">
+        <v>241</v>
+      </c>
+      <c r="K28" t="s">
+        <v>241</v>
+      </c>
+      <c r="L28" t="s">
+        <v>243</v>
+      </c>
+      <c r="M28" t="s">
+        <v>241</v>
+      </c>
+      <c r="N28" t="s">
+        <v>243</v>
+      </c>
+      <c r="O28" t="s">
+        <v>243</v>
+      </c>
+      <c r="P28" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="29" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A29" s="5" t="s">
+        <v>275</v>
+      </c>
+      <c r="B29">
+        <v>57</v>
+      </c>
+      <c r="C29" t="s">
+        <v>146</v>
+      </c>
+      <c r="D29" s="6" t="s">
+        <v>240</v>
+      </c>
+      <c r="E29" s="7">
+        <v>39725</v>
+      </c>
+      <c r="F29">
+        <v>3</v>
+      </c>
+      <c r="G29">
+        <v>1</v>
+      </c>
+      <c r="H29">
+        <v>2</v>
+      </c>
+      <c r="I29">
+        <v>212</v>
+      </c>
+      <c r="J29" t="s">
+        <v>241</v>
+      </c>
+      <c r="K29" t="s">
+        <v>243</v>
+      </c>
+      <c r="L29" t="s">
+        <v>241</v>
+      </c>
+      <c r="M29" t="s">
+        <v>243</v>
+      </c>
+      <c r="N29" t="s">
+        <v>243</v>
+      </c>
+      <c r="O29" t="s">
+        <v>243</v>
+      </c>
+      <c r="P29" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="30" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A30" s="5" t="s">
+        <v>276</v>
+      </c>
+      <c r="B30">
+        <v>37</v>
+      </c>
+      <c r="C30" t="s">
+        <v>143</v>
+      </c>
+      <c r="D30" s="6" t="s">
+        <v>240</v>
+      </c>
+      <c r="E30" s="7">
+        <v>41797</v>
+      </c>
+      <c r="F30">
+        <v>3</v>
+      </c>
+      <c r="G30">
+        <v>1</v>
+      </c>
+      <c r="H30">
+        <v>2</v>
+      </c>
+      <c r="I30">
+        <v>280</v>
+      </c>
+      <c r="J30" t="s">
+        <v>241</v>
+      </c>
+      <c r="K30" t="s">
+        <v>243</v>
+      </c>
+      <c r="L30" t="s">
+        <v>241</v>
+      </c>
+      <c r="M30" t="s">
+        <v>241</v>
+      </c>
+      <c r="N30" t="s">
+        <v>243</v>
+      </c>
+      <c r="O30" t="s">
+        <v>241</v>
+      </c>
+      <c r="P30" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="31" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A31" s="5" t="s">
+        <v>277</v>
+      </c>
+      <c r="B31">
+        <v>48</v>
+      </c>
+      <c r="C31" t="s">
+        <v>143</v>
+      </c>
+      <c r="D31" s="6" t="s">
+        <v>246</v>
+      </c>
+      <c r="E31" s="7">
+        <v>42064</v>
+      </c>
+      <c r="F31">
+        <v>3</v>
+      </c>
+      <c r="G31">
+        <v>2</v>
+      </c>
+      <c r="H31">
+        <v>3</v>
+      </c>
+      <c r="I31">
+        <v>420</v>
+      </c>
+      <c r="J31" t="s">
+        <v>241</v>
+      </c>
+      <c r="K31" t="s">
+        <v>243</v>
+      </c>
+      <c r="L31" t="s">
+        <v>241</v>
+      </c>
+      <c r="M31" t="s">
+        <v>241</v>
+      </c>
+      <c r="N31" t="s">
+        <v>243</v>
+      </c>
+      <c r="O31" t="s">
+        <v>241</v>
+      </c>
+      <c r="P31" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="32" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A32" s="5" t="s">
+        <v>278</v>
+      </c>
+      <c r="B32">
+        <v>54</v>
+      </c>
+      <c r="C32" t="s">
+        <v>146</v>
+      </c>
+      <c r="D32" t="s">
+        <v>240</v>
+      </c>
+      <c r="E32" s="7">
+        <v>36758</v>
+      </c>
+      <c r="F32">
+        <v>3</v>
+      </c>
+      <c r="G32">
+        <v>1</v>
+      </c>
+      <c r="H32">
+        <v>1</v>
+      </c>
+      <c r="I32">
+        <v>48</v>
+      </c>
+      <c r="J32" t="s">
+        <v>241</v>
+      </c>
+      <c r="K32" t="s">
+        <v>242</v>
+      </c>
+      <c r="L32" t="s">
+        <v>243</v>
+      </c>
+      <c r="M32" t="s">
+        <v>242</v>
+      </c>
+      <c r="N32" t="s">
+        <v>242</v>
+      </c>
+      <c r="O32" t="s">
+        <v>242</v>
+      </c>
+      <c r="P32" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="33" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A33" s="5" t="s">
+        <v>279</v>
+      </c>
+      <c r="B33">
+        <v>50</v>
+      </c>
+      <c r="C33" t="s">
+        <v>143</v>
+      </c>
+      <c r="D33" t="s">
+        <v>240</v>
+      </c>
+      <c r="E33" s="7">
+        <v>38062</v>
+      </c>
+      <c r="F33">
+        <v>2</v>
+      </c>
+      <c r="G33">
+        <v>2</v>
+      </c>
+      <c r="H33">
+        <v>1</v>
+      </c>
+      <c r="I33">
+        <v>680</v>
+      </c>
+      <c r="J33" t="s">
+        <v>241</v>
+      </c>
+      <c r="K33" t="s">
+        <v>243</v>
+      </c>
+      <c r="L33" t="s">
+        <v>242</v>
+      </c>
+      <c r="M33" t="s">
+        <v>241</v>
+      </c>
+      <c r="N33" t="s">
+        <v>243</v>
+      </c>
+      <c r="O33" t="s">
+        <v>243</v>
+      </c>
+      <c r="P33" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="34" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A34" s="5" t="s">
+        <v>280</v>
+      </c>
+      <c r="B34">
+        <v>27</v>
+      </c>
+      <c r="C34" t="s">
+        <v>143</v>
+      </c>
+      <c r="D34" t="s">
+        <v>246</v>
+      </c>
+      <c r="E34" s="7">
+        <v>37911</v>
+      </c>
+      <c r="F34">
+        <v>3</v>
+      </c>
+      <c r="G34">
+        <v>3</v>
+      </c>
+      <c r="H34">
+        <v>1</v>
+      </c>
+      <c r="I34">
+        <v>260</v>
+      </c>
+      <c r="J34" t="s">
+        <v>242</v>
+      </c>
+      <c r="K34" t="s">
+        <v>242</v>
+      </c>
+      <c r="L34" t="s">
+        <v>247</v>
+      </c>
+      <c r="M34" t="s">
+        <v>242</v>
+      </c>
+      <c r="N34" t="s">
+        <v>247</v>
+      </c>
+      <c r="O34" t="s">
+        <v>241</v>
+      </c>
+      <c r="P34" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="35" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A35" s="5" t="s">
+        <v>281</v>
+      </c>
+      <c r="B35">
+        <v>28</v>
+      </c>
+      <c r="C35" t="s">
+        <v>143</v>
+      </c>
+      <c r="D35" t="s">
+        <v>246</v>
+      </c>
+      <c r="E35" s="7">
+        <v>42927</v>
+      </c>
+      <c r="F35">
+        <v>3</v>
+      </c>
+      <c r="G35">
+        <v>3</v>
+      </c>
+      <c r="H35">
+        <v>1</v>
+      </c>
+      <c r="I35">
+        <v>180</v>
+      </c>
+      <c r="J35" t="s">
+        <v>241</v>
+      </c>
+      <c r="K35" t="s">
+        <v>243</v>
+      </c>
+      <c r="L35" t="s">
+        <v>242</v>
+      </c>
+      <c r="M35" t="s">
+        <v>241</v>
+      </c>
+      <c r="N35" t="s">
+        <v>243</v>
+      </c>
+      <c r="O35" t="s">
+        <v>243</v>
+      </c>
+      <c r="P35" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="36" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A36" s="5" t="s">
+        <v>282</v>
+      </c>
+      <c r="B36">
+        <v>24</v>
+      </c>
+      <c r="C36" t="s">
+        <v>143</v>
+      </c>
+      <c r="D36" t="s">
+        <v>250</v>
+      </c>
+      <c r="E36" s="7">
+        <v>41560</v>
+      </c>
+      <c r="F36">
+        <v>3</v>
+      </c>
+      <c r="G36">
+        <v>2</v>
+      </c>
+      <c r="H36">
+        <v>1</v>
+      </c>
+      <c r="I36">
+        <v>280</v>
+      </c>
+      <c r="J36" t="s">
+        <v>241</v>
+      </c>
+      <c r="K36" t="s">
+        <v>243</v>
+      </c>
+      <c r="L36" t="s">
+        <v>247</v>
+      </c>
+      <c r="M36" t="s">
+        <v>243</v>
+      </c>
+      <c r="N36" t="s">
+        <v>243</v>
+      </c>
+      <c r="O36" t="s">
+        <v>241</v>
+      </c>
+      <c r="P36" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="37" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A37" s="5" t="s">
+        <v>283</v>
+      </c>
+      <c r="B37">
+        <v>36</v>
+      </c>
+      <c r="C37" t="s">
+        <v>146</v>
+      </c>
+      <c r="D37" t="s">
+        <v>240</v>
+      </c>
+      <c r="E37" s="7">
+        <v>42886</v>
+      </c>
+      <c r="F37">
+        <v>3</v>
+      </c>
+      <c r="G37">
+        <v>2</v>
+      </c>
+      <c r="H37">
+        <v>1</v>
+      </c>
+      <c r="I37">
+        <v>50</v>
+      </c>
+      <c r="J37" t="s">
+        <v>243</v>
+      </c>
+      <c r="K37" t="s">
+        <v>241</v>
+      </c>
+      <c r="L37" t="s">
+        <v>241</v>
+      </c>
+      <c r="M37" t="s">
+        <v>243</v>
+      </c>
+      <c r="N37" t="s">
+        <v>241</v>
+      </c>
+      <c r="O37" t="s">
+        <v>242</v>
+      </c>
+      <c r="P37" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="38" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A38" s="5" t="s">
+        <v>284</v>
+      </c>
+      <c r="B38">
+        <v>29</v>
+      </c>
+      <c r="C38" t="s">
+        <v>146</v>
+      </c>
+      <c r="D38" t="s">
+        <v>253</v>
+      </c>
+      <c r="E38" s="7">
+        <v>39345</v>
+      </c>
+      <c r="F38">
+        <v>3</v>
+      </c>
+      <c r="G38">
+        <v>3</v>
+      </c>
+      <c r="H38">
+        <v>1</v>
+      </c>
+      <c r="I38">
+        <v>60</v>
+      </c>
+      <c r="J38" t="s">
+        <v>241</v>
+      </c>
+      <c r="K38" t="s">
+        <v>241</v>
+      </c>
+      <c r="L38" t="s">
+        <v>243</v>
+      </c>
+      <c r="M38" t="s">
+        <v>243</v>
+      </c>
+      <c r="N38" t="s">
+        <v>241</v>
+      </c>
+      <c r="O38" t="s">
+        <v>241</v>
+      </c>
+      <c r="P38" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="39" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A39" s="5" t="s">
+        <v>285</v>
+      </c>
+      <c r="B39">
+        <v>53</v>
+      </c>
+      <c r="C39" t="s">
+        <v>143</v>
+      </c>
+      <c r="D39" t="s">
+        <v>240</v>
+      </c>
+      <c r="E39" s="7">
+        <v>39725</v>
+      </c>
+      <c r="F39">
+        <v>3</v>
+      </c>
+      <c r="G39">
+        <v>1</v>
+      </c>
+      <c r="H39">
+        <v>2</v>
+      </c>
+      <c r="I39">
+        <v>870</v>
+      </c>
+      <c r="J39" t="s">
+        <v>241</v>
+      </c>
+      <c r="K39" t="s">
+        <v>243</v>
+      </c>
+      <c r="L39" t="s">
+        <v>241</v>
+      </c>
+      <c r="M39" t="s">
+        <v>243</v>
+      </c>
+      <c r="N39" t="s">
+        <v>243</v>
+      </c>
+      <c r="O39" t="s">
+        <v>241</v>
+      </c>
+      <c r="P39" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="40" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A40" s="5" t="s">
+        <v>286</v>
+      </c>
+      <c r="B40">
+        <v>32</v>
+      </c>
+      <c r="C40" t="s">
+        <v>143</v>
+      </c>
+      <c r="D40" s="6" t="s">
+        <v>253</v>
+      </c>
+      <c r="E40" s="7">
+        <v>41797</v>
+      </c>
+      <c r="F40">
+        <v>3</v>
+      </c>
+      <c r="G40">
+        <v>2</v>
+      </c>
+      <c r="H40">
+        <v>2</v>
+      </c>
+      <c r="I40">
+        <v>120</v>
+      </c>
+      <c r="J40" t="s">
+        <v>241</v>
+      </c>
+      <c r="K40" t="s">
+        <v>241</v>
+      </c>
+      <c r="L40" t="s">
+        <v>243</v>
+      </c>
+      <c r="M40" t="s">
+        <v>241</v>
+      </c>
+      <c r="N40" t="s">
+        <v>243</v>
+      </c>
+      <c r="O40" t="s">
+        <v>241</v>
+      </c>
+      <c r="P40" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="41" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A41" s="5" t="s">
+        <v>287</v>
+      </c>
+      <c r="B41">
+        <v>48</v>
+      </c>
+      <c r="C41" t="s">
+        <v>146</v>
+      </c>
+      <c r="D41" s="6" t="s">
+        <v>246</v>
+      </c>
+      <c r="E41" s="7">
+        <v>42064</v>
+      </c>
+      <c r="F41">
+        <v>3</v>
+      </c>
+      <c r="G41">
+        <v>3</v>
+      </c>
+      <c r="H41">
+        <v>1</v>
+      </c>
+      <c r="I41">
+        <v>100</v>
+      </c>
+      <c r="J41" t="s">
+        <v>243</v>
+      </c>
+      <c r="K41" t="s">
+        <v>241</v>
+      </c>
+      <c r="L41" t="s">
+        <v>241</v>
+      </c>
+      <c r="M41" t="s">
+        <v>243</v>
+      </c>
+      <c r="N41" t="s">
+        <v>241</v>
+      </c>
+      <c r="O41" t="s">
+        <v>241</v>
+      </c>
+      <c r="P41" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="42" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A42" s="5" t="s">
+        <v>288</v>
+      </c>
+      <c r="B42">
+        <v>20</v>
+      </c>
+      <c r="C42" t="s">
+        <v>146</v>
+      </c>
+      <c r="D42" s="6" t="s">
+        <v>253</v>
+      </c>
+      <c r="E42" s="7">
+        <v>36758</v>
+      </c>
+      <c r="F42">
+        <v>3</v>
+      </c>
+      <c r="G42">
+        <v>2</v>
+      </c>
+      <c r="H42">
+        <v>1</v>
+      </c>
+      <c r="I42">
+        <v>120</v>
+      </c>
+      <c r="J42" t="s">
+        <v>241</v>
+      </c>
+      <c r="K42" t="s">
+        <v>243</v>
+      </c>
+      <c r="L42" t="s">
+        <v>243</v>
+      </c>
+      <c r="M42" t="s">
+        <v>243</v>
+      </c>
+      <c r="N42" t="s">
+        <v>241</v>
+      </c>
+      <c r="O42" t="s">
+        <v>241</v>
+      </c>
+      <c r="P42" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="43" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A43" s="5" t="s">
+        <v>289</v>
+      </c>
+      <c r="B43">
+        <v>33</v>
+      </c>
+      <c r="C43" t="s">
+        <v>146</v>
+      </c>
+      <c r="D43" s="6" t="s">
+        <v>246</v>
+      </c>
+      <c r="E43" s="7">
+        <v>38062</v>
+      </c>
+      <c r="F43">
+        <v>3</v>
+      </c>
+      <c r="G43">
+        <v>2</v>
+      </c>
+      <c r="H43">
+        <v>1</v>
+      </c>
+      <c r="I43">
+        <v>150</v>
+      </c>
+      <c r="J43" t="s">
+        <v>241</v>
+      </c>
+      <c r="K43" t="s">
+        <v>241</v>
+      </c>
+      <c r="L43" t="s">
+        <v>243</v>
+      </c>
+      <c r="M43" t="s">
+        <v>243</v>
+      </c>
+      <c r="N43" t="s">
+        <v>243</v>
+      </c>
+      <c r="O43" t="s">
+        <v>241</v>
+      </c>
+      <c r="P43" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="44" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A44" s="5" t="s">
+        <v>290</v>
+      </c>
+      <c r="B44">
+        <v>23</v>
+      </c>
+      <c r="C44" t="s">
+        <v>143</v>
+      </c>
+      <c r="D44" s="6" t="s">
+        <v>253</v>
+      </c>
+      <c r="E44" s="7">
+        <v>37911</v>
+      </c>
+      <c r="F44">
+        <v>3</v>
+      </c>
+      <c r="G44">
+        <v>3</v>
+      </c>
+      <c r="H44">
+        <v>1</v>
+      </c>
+      <c r="I44">
+        <v>100</v>
+      </c>
+      <c r="J44" t="s">
+        <v>241</v>
+      </c>
+      <c r="K44" t="s">
+        <v>243</v>
+      </c>
+      <c r="L44" t="s">
+        <v>241</v>
+      </c>
+      <c r="M44" t="s">
+        <v>243</v>
+      </c>
+      <c r="N44" t="s">
+        <v>243</v>
+      </c>
+      <c r="O44" t="s">
+        <v>241</v>
+      </c>
+      <c r="P44" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="45" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A45" s="5" t="s">
+        <v>291</v>
+      </c>
+      <c r="B45">
+        <v>40</v>
+      </c>
+      <c r="C45" t="s">
+        <v>143</v>
+      </c>
+      <c r="D45" s="6" t="s">
+        <v>253</v>
+      </c>
+      <c r="E45" s="7">
+        <v>42927</v>
+      </c>
+      <c r="F45">
+        <v>3</v>
+      </c>
+      <c r="G45">
+        <v>1</v>
+      </c>
+      <c r="H45">
+        <v>1</v>
+      </c>
+      <c r="I45">
+        <v>280</v>
+      </c>
+      <c r="J45" t="s">
+        <v>241</v>
+      </c>
+      <c r="K45" t="s">
+        <v>243</v>
+      </c>
+      <c r="L45" t="s">
+        <v>241</v>
+      </c>
+      <c r="M45" t="s">
+        <v>241</v>
+      </c>
+      <c r="N45" t="s">
+        <v>243</v>
+      </c>
+      <c r="O45" t="s">
+        <v>241</v>
+      </c>
+      <c r="P45" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="46" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A46" s="5" t="s">
+        <v>292</v>
+      </c>
+      <c r="B46">
+        <v>42</v>
+      </c>
+      <c r="C46" t="s">
+        <v>146</v>
+      </c>
+      <c r="D46" t="s">
+        <v>240</v>
+      </c>
+      <c r="E46" s="7">
+        <v>41560</v>
+      </c>
+      <c r="F46">
+        <v>3</v>
+      </c>
+      <c r="G46">
+        <v>1</v>
+      </c>
+      <c r="H46">
+        <v>1</v>
+      </c>
+      <c r="I46">
+        <v>200</v>
+      </c>
+      <c r="J46" t="s">
+        <v>241</v>
+      </c>
+      <c r="K46" t="s">
+        <v>243</v>
+      </c>
+      <c r="L46" t="s">
+        <v>242</v>
+      </c>
+      <c r="M46" t="s">
+        <v>243</v>
+      </c>
+      <c r="N46" t="s">
+        <v>243</v>
+      </c>
+      <c r="O46" t="s">
+        <v>242</v>
+      </c>
+      <c r="P46" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="47" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A47" s="5" t="s">
+        <v>293</v>
+      </c>
+      <c r="B47">
+        <v>46</v>
+      </c>
+      <c r="C47" t="s">
+        <v>143</v>
+      </c>
+      <c r="D47" t="s">
+        <v>246</v>
+      </c>
+      <c r="E47" s="7">
+        <v>42886</v>
+      </c>
+      <c r="F47">
+        <v>2</v>
+      </c>
+      <c r="G47">
+        <v>2</v>
+      </c>
+      <c r="H47">
+        <v>1</v>
+      </c>
+      <c r="I47">
+        <v>380</v>
+      </c>
+      <c r="J47" t="s">
+        <v>241</v>
+      </c>
+      <c r="K47" t="s">
+        <v>243</v>
+      </c>
+      <c r="L47" t="s">
+        <v>242</v>
+      </c>
+      <c r="M47" t="s">
+        <v>241</v>
+      </c>
+      <c r="N47" t="s">
+        <v>243</v>
+      </c>
+      <c r="O47" t="s">
+        <v>241</v>
+      </c>
+      <c r="P47" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="48" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A48" s="5" t="s">
+        <v>294</v>
+      </c>
+      <c r="B48">
+        <v>27</v>
+      </c>
+      <c r="C48" t="s">
+        <v>146</v>
+      </c>
+      <c r="D48" t="s">
+        <v>250</v>
+      </c>
+      <c r="E48" s="7">
+        <v>39345</v>
+      </c>
+      <c r="F48">
+        <v>3</v>
+      </c>
+      <c r="G48">
+        <v>2</v>
+      </c>
+      <c r="H48">
+        <v>1</v>
+      </c>
+      <c r="I48">
+        <v>210</v>
+      </c>
+      <c r="J48" t="s">
+        <v>242</v>
+      </c>
+      <c r="K48" t="s">
+        <v>243</v>
+      </c>
+      <c r="L48" t="s">
+        <v>241</v>
+      </c>
+      <c r="M48" t="s">
+        <v>243</v>
+      </c>
+      <c r="N48" t="s">
+        <v>247</v>
+      </c>
+      <c r="O48" t="s">
+        <v>241</v>
+      </c>
+      <c r="P48" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="49" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A49" s="5" t="s">
+        <v>294</v>
+      </c>
+      <c r="B49">
+        <v>33</v>
+      </c>
+      <c r="C49" t="s">
+        <v>146</v>
+      </c>
+      <c r="D49" t="s">
+        <v>246</v>
+      </c>
+      <c r="E49" s="7">
+        <v>39725</v>
+      </c>
+      <c r="F49">
+        <v>3</v>
+      </c>
+      <c r="G49">
+        <v>2</v>
+      </c>
+      <c r="H49">
+        <v>1</v>
+      </c>
+      <c r="I49">
+        <v>48</v>
+      </c>
+      <c r="J49" t="s">
+        <v>241</v>
+      </c>
+      <c r="K49" t="s">
+        <v>242</v>
+      </c>
+      <c r="L49" t="s">
+        <v>243</v>
+      </c>
+      <c r="M49" t="s">
+        <v>241</v>
+      </c>
+      <c r="N49" t="s">
+        <v>242</v>
+      </c>
+      <c r="O49" t="s">
+        <v>242</v>
+      </c>
+      <c r="P49" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="50" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A50" s="5" t="s">
+        <v>295</v>
+      </c>
+      <c r="B50">
+        <v>18</v>
+      </c>
+      <c r="C50" t="s">
+        <v>143</v>
+      </c>
+      <c r="D50" t="s">
+        <v>250</v>
+      </c>
+      <c r="E50" s="7">
+        <v>41797</v>
+      </c>
+      <c r="F50">
+        <v>3</v>
+      </c>
+      <c r="G50">
+        <v>2</v>
+      </c>
+      <c r="H50">
+        <v>1</v>
+      </c>
+      <c r="I50">
+        <v>160</v>
+      </c>
+      <c r="J50" t="s">
+        <v>241</v>
+      </c>
+      <c r="K50" t="s">
+        <v>243</v>
+      </c>
+      <c r="L50" t="s">
+        <v>241</v>
+      </c>
+      <c r="M50" t="s">
+        <v>241</v>
+      </c>
+      <c r="N50" t="s">
+        <v>243</v>
+      </c>
+      <c r="O50" t="s">
+        <v>243</v>
+      </c>
+      <c r="P50" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="51" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A51" s="5" t="s">
+        <v>296</v>
+      </c>
+      <c r="B51">
+        <v>35</v>
+      </c>
+      <c r="C51" t="s">
+        <v>146</v>
+      </c>
+      <c r="D51" t="s">
+        <v>240</v>
+      </c>
+      <c r="E51" s="7">
+        <v>42064</v>
+      </c>
+      <c r="F51">
+        <v>3</v>
+      </c>
+      <c r="G51">
+        <v>2</v>
+      </c>
+      <c r="H51">
+        <v>1</v>
+      </c>
+      <c r="I51">
+        <v>48</v>
+      </c>
+      <c r="J51" t="s">
+        <v>241</v>
+      </c>
+      <c r="K51" t="s">
+        <v>242</v>
+      </c>
+      <c r="L51" t="s">
+        <v>243</v>
+      </c>
+      <c r="M51" t="s">
+        <v>241</v>
+      </c>
+      <c r="N51" t="s">
+        <v>242</v>
+      </c>
+      <c r="O51" t="s">
+        <v>242</v>
+      </c>
+      <c r="P51" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="52" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A52" s="5" t="s">
+        <v>297</v>
+      </c>
+      <c r="B52">
+        <v>17</v>
+      </c>
+      <c r="C52" t="s">
+        <v>146</v>
+      </c>
+      <c r="D52" t="s">
+        <v>253</v>
+      </c>
+      <c r="E52" s="7">
+        <v>36758</v>
+      </c>
+      <c r="F52">
+        <v>3</v>
+      </c>
+      <c r="G52">
+        <v>1</v>
+      </c>
+      <c r="H52">
+        <v>1</v>
+      </c>
+      <c r="I52">
+        <v>48</v>
+      </c>
+      <c r="J52" t="s">
+        <v>241</v>
+      </c>
+      <c r="K52" t="s">
+        <v>241</v>
+      </c>
+      <c r="L52" t="s">
+        <v>243</v>
+      </c>
+      <c r="M52" t="s">
+        <v>241</v>
+      </c>
+      <c r="N52" t="s">
+        <v>241</v>
+      </c>
+      <c r="O52" t="s">
+        <v>241</v>
+      </c>
+      <c r="P52" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="53" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A53" s="5" t="s">
+        <v>298</v>
+      </c>
+      <c r="B53">
+        <v>50</v>
+      </c>
+      <c r="C53" t="s">
+        <v>146</v>
+      </c>
+      <c r="D53" t="s">
+        <v>240</v>
+      </c>
+      <c r="E53" s="7">
+        <v>38062</v>
+      </c>
+      <c r="F53">
+        <v>3</v>
+      </c>
+      <c r="G53">
+        <v>1</v>
+      </c>
+      <c r="H53">
+        <v>1</v>
+      </c>
+      <c r="I53">
+        <v>48</v>
+      </c>
+      <c r="J53" t="s">
+        <v>241</v>
+      </c>
+      <c r="K53" t="s">
+        <v>241</v>
+      </c>
+      <c r="L53" t="s">
+        <v>243</v>
+      </c>
+      <c r="M53" t="s">
+        <v>241</v>
+      </c>
+      <c r="N53" t="s">
+        <v>241</v>
+      </c>
+      <c r="O53" t="s">
+        <v>241</v>
+      </c>
+      <c r="P53" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="54" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A54" s="5" t="s">
+        <v>299</v>
+      </c>
+      <c r="B54">
+        <v>35</v>
+      </c>
+      <c r="C54" t="s">
+        <v>143</v>
+      </c>
+      <c r="D54" s="6" t="s">
+        <v>240</v>
+      </c>
+      <c r="E54" s="7">
+        <v>37911</v>
+      </c>
+      <c r="F54">
+        <v>3</v>
+      </c>
+      <c r="G54">
+        <v>1</v>
+      </c>
+      <c r="H54">
+        <v>1</v>
+      </c>
+      <c r="I54">
+        <v>280</v>
+      </c>
+      <c r="J54" t="s">
+        <v>241</v>
+      </c>
+      <c r="K54" t="s">
+        <v>243</v>
+      </c>
+      <c r="L54" t="s">
+        <v>241</v>
+      </c>
+      <c r="M54" t="s">
+        <v>241</v>
+      </c>
+      <c r="N54" t="s">
+        <v>243</v>
+      </c>
+      <c r="O54" t="s">
+        <v>241</v>
+      </c>
+      <c r="P54" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="55" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A55" s="5" t="s">
+        <v>300</v>
+      </c>
+      <c r="B55">
+        <v>19</v>
+      </c>
+      <c r="C55" t="s">
+        <v>146</v>
+      </c>
+      <c r="D55" s="6" t="s">
+        <v>253</v>
+      </c>
+      <c r="E55" s="7">
+        <v>42927</v>
+      </c>
+      <c r="F55">
+        <v>3</v>
+      </c>
+      <c r="G55">
+        <v>2</v>
+      </c>
+      <c r="H55">
+        <v>1</v>
+      </c>
+      <c r="I55">
+        <v>68</v>
+      </c>
+      <c r="J55" t="s">
+        <v>241</v>
+      </c>
+      <c r="K55" t="s">
+        <v>241</v>
+      </c>
+      <c r="L55" t="s">
+        <v>243</v>
+      </c>
+      <c r="M55" t="s">
+        <v>243</v>
+      </c>
+      <c r="N55" t="s">
+        <v>241</v>
+      </c>
+      <c r="O55" t="s">
+        <v>241</v>
+      </c>
+      <c r="P55" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="56" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A56" s="5" t="s">
+        <v>301</v>
+      </c>
+      <c r="B56">
+        <v>20</v>
+      </c>
+      <c r="C56" t="s">
+        <v>146</v>
+      </c>
+      <c r="D56" s="6" t="s">
+        <v>253</v>
+      </c>
+      <c r="E56" s="7">
+        <v>41560</v>
+      </c>
+      <c r="F56">
+        <v>3</v>
+      </c>
+      <c r="G56">
+        <v>1</v>
+      </c>
+      <c r="H56">
+        <v>1</v>
+      </c>
+      <c r="I56">
+        <v>100</v>
+      </c>
+      <c r="J56" t="s">
+        <v>241</v>
+      </c>
+      <c r="K56" t="s">
+        <v>243</v>
+      </c>
+      <c r="L56" t="s">
+        <v>241</v>
+      </c>
+      <c r="M56" t="s">
+        <v>243</v>
+      </c>
+      <c r="N56" t="s">
+        <v>241</v>
+      </c>
+      <c r="O56" t="s">
+        <v>241</v>
+      </c>
+      <c r="P56" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="57" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A57" s="5" t="s">
+        <v>302</v>
+      </c>
+      <c r="B57">
+        <v>33</v>
+      </c>
+      <c r="C57" t="s">
+        <v>143</v>
+      </c>
+      <c r="D57" s="6" t="s">
+        <v>253</v>
+      </c>
+      <c r="E57" s="7">
+        <v>42886</v>
+      </c>
+      <c r="F57">
+        <v>3</v>
+      </c>
+      <c r="G57">
+        <v>1</v>
+      </c>
+      <c r="H57">
+        <v>1</v>
+      </c>
+      <c r="I57">
+        <v>100</v>
+      </c>
+      <c r="J57" t="s">
+        <v>241</v>
+      </c>
+      <c r="K57" t="s">
+        <v>243</v>
+      </c>
+      <c r="L57" t="s">
+        <v>241</v>
+      </c>
+      <c r="M57" t="s">
+        <v>273</v>
+      </c>
+      <c r="N57" t="s">
+        <v>243</v>
+      </c>
+      <c r="O57" t="s">
+        <v>243</v>
+      </c>
+      <c r="P57" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="58" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A58" s="5" t="s">
+        <v>303</v>
+      </c>
+      <c r="B58">
+        <v>23</v>
+      </c>
+      <c r="C58" t="s">
+        <v>143</v>
+      </c>
+      <c r="D58" s="6" t="s">
+        <v>253</v>
+      </c>
+      <c r="E58" s="7">
+        <v>39345</v>
+      </c>
+      <c r="F58">
+        <v>3</v>
+      </c>
+      <c r="G58">
+        <v>1</v>
+      </c>
+      <c r="H58">
+        <v>1</v>
+      </c>
+      <c r="I58">
+        <v>80</v>
+      </c>
+      <c r="J58" t="s">
+        <v>241</v>
+      </c>
+      <c r="K58" t="s">
+        <v>241</v>
+      </c>
+      <c r="L58" t="s">
+        <v>243</v>
+      </c>
+      <c r="M58" t="s">
+        <v>241</v>
+      </c>
+      <c r="N58" t="s">
+        <v>243</v>
+      </c>
+      <c r="O58" t="s">
+        <v>243</v>
+      </c>
+      <c r="P58" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="59" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A59" s="5" t="s">
+        <v>304</v>
+      </c>
+      <c r="B59">
+        <v>50</v>
+      </c>
+      <c r="C59" t="s">
+        <v>146</v>
+      </c>
+      <c r="D59" s="6" t="s">
+        <v>240</v>
+      </c>
+      <c r="E59" s="7">
+        <v>39725</v>
+      </c>
+      <c r="F59">
+        <v>3</v>
+      </c>
+      <c r="G59">
+        <v>1</v>
+      </c>
+      <c r="H59">
+        <v>1</v>
+      </c>
+      <c r="I59">
+        <v>212</v>
+      </c>
+      <c r="J59" t="s">
+        <v>241</v>
+      </c>
+      <c r="K59" t="s">
+        <v>243</v>
+      </c>
+      <c r="L59" t="s">
+        <v>241</v>
+      </c>
+      <c r="M59" t="s">
+        <v>243</v>
+      </c>
+      <c r="N59" t="s">
+        <v>243</v>
+      </c>
+      <c r="O59" t="s">
+        <v>243</v>
+      </c>
+      <c r="P59" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="60" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A60" s="5" t="s">
+        <v>305</v>
+      </c>
+      <c r="B60">
+        <v>37</v>
+      </c>
+      <c r="C60" t="s">
+        <v>143</v>
+      </c>
+      <c r="D60" s="6" t="s">
+        <v>240</v>
+      </c>
+      <c r="E60" s="7">
+        <v>41797</v>
+      </c>
+      <c r="F60">
+        <v>3</v>
+      </c>
+      <c r="G60">
+        <v>2</v>
+      </c>
+      <c r="H60">
+        <v>1</v>
+      </c>
+      <c r="I60">
+        <v>280</v>
+      </c>
+      <c r="J60" t="s">
+        <v>241</v>
+      </c>
+      <c r="K60" t="s">
+        <v>243</v>
+      </c>
+      <c r="L60" t="s">
+        <v>241</v>
+      </c>
+      <c r="M60" t="s">
+        <v>241</v>
+      </c>
+      <c r="N60" t="s">
+        <v>243</v>
+      </c>
+      <c r="O60" t="s">
+        <v>241</v>
+      </c>
+      <c r="P60" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="61" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A61" s="5" t="s">
+        <v>306</v>
+      </c>
+      <c r="B61">
+        <v>48</v>
+      </c>
+      <c r="C61" t="s">
+        <v>143</v>
+      </c>
+      <c r="D61" s="6" t="s">
+        <v>246</v>
+      </c>
+      <c r="E61" s="7">
+        <v>42064</v>
+      </c>
+      <c r="F61">
+        <v>3</v>
+      </c>
+      <c r="G61">
+        <v>2</v>
+      </c>
+      <c r="H61">
+        <v>1</v>
+      </c>
+      <c r="I61">
+        <v>420</v>
+      </c>
+      <c r="J61" t="s">
+        <v>241</v>
+      </c>
+      <c r="K61" t="s">
+        <v>243</v>
+      </c>
+      <c r="L61" t="s">
+        <v>241</v>
+      </c>
+      <c r="M61" t="s">
+        <v>241</v>
+      </c>
+      <c r="N61" t="s">
+        <v>243</v>
+      </c>
+      <c r="O61" t="s">
+        <v>241</v>
+      </c>
+      <c r="P61" t="s">
+        <v>243</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>
--- a/office/data/实验数据.xlsx
+++ b/office/data/实验数据.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\glplaman.github.io\office\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9DB2157-016F-4A71-878B-5721DC6B00DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E85A1D8-A8AD-4856-94AA-8B2D842E884B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{2E5A61E7-CF82-4D7E-B994-D412ADB0B79D}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{2E5A61E7-CF82-4D7E-B994-D412ADB0B79D}"/>
   </bookViews>
   <sheets>
     <sheet name="通信录" sheetId="6" r:id="rId1"/>
@@ -23,6 +23,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">工资收入!$A$1:$L$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">门店晚间收益!$A$1:$P$61</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">学生成绩!$A$1:$K$16</definedName>
     <definedName name="_xlnm.Criteria" localSheetId="3">工资收入!$P$4:$Q$5</definedName>
     <definedName name="_xlnm.Extract" localSheetId="3">工资收入!$P$13:$AA$13</definedName>
@@ -1170,7 +1171,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1202,9 +1203,34 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
@@ -1245,33 +1271,42 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1591,374 +1626,377 @@
   <dimension ref="A1:L11"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="5.25" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.25" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="17.25" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="7.125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="23.5" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="5.25" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9.375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="5.25" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.125" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.25" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.25" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9" style="4"/>
+    <col min="7" max="7" width="7.125" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="23.5" style="4" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="5.25" style="4" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9" style="4"/>
+    <col min="11" max="11" width="11" style="4" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.375" style="4" bestFit="1" customWidth="1"/>
+    <col min="13" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
+      <c r="A1" s="4" t="s">
         <v>148</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="4" t="s">
         <v>153</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="4" t="s">
         <v>151</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="4" t="s">
         <v>139</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="4" t="s">
         <v>149</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="4" t="s">
         <v>150</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="4" t="s">
         <v>141</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="4" t="s">
         <v>152</v>
       </c>
-      <c r="L1" t="s">
+      <c r="L1" s="4" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A2">
+      <c r="A2" s="4">
         <v>1</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="4" t="s">
         <v>155</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="4" t="s">
         <v>143</v>
       </c>
-      <c r="D2" s="2">
+      <c r="D2" s="5">
         <v>31048</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" s="6" t="s">
         <v>157</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F2" s="4" t="s">
         <v>203</v>
       </c>
-      <c r="G2" t="s">
+      <c r="G2" s="4" t="s">
         <v>156</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" s="4" t="s">
         <v>142</v>
       </c>
-      <c r="I2">
+      <c r="I2" s="4">
         <v>65</v>
       </c>
-      <c r="K2" t="s">
+      <c r="K2" s="4" t="s">
         <v>158</v>
       </c>
-      <c r="L2" t="s">
+      <c r="L2" s="4" t="s">
         <v>159</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A3">
+      <c r="A3" s="4">
         <v>2</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="4" t="s">
         <v>160</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="4" t="s">
         <v>143</v>
       </c>
-      <c r="D3" s="2">
+      <c r="D3" s="5">
         <v>29254</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="E3" s="6" t="s">
         <v>162</v>
       </c>
-      <c r="F3" t="s">
+      <c r="F3" s="4" t="s">
         <v>203</v>
       </c>
-      <c r="G3" t="s">
+      <c r="G3" s="4" t="s">
         <v>161</v>
       </c>
-      <c r="H3" t="s">
+      <c r="H3" s="4" t="s">
         <v>144</v>
       </c>
-      <c r="I3">
+      <c r="I3" s="4">
         <v>60</v>
       </c>
-      <c r="K3" t="s">
+      <c r="K3" s="4" t="s">
         <v>202</v>
       </c>
-      <c r="L3" t="s">
+      <c r="L3" s="4" t="s">
         <v>164</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
+      <c r="A4" s="4">
+        <v>3</v>
+      </c>
+      <c r="B4" s="4" t="s">
         <v>165</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="4" t="s">
         <v>143</v>
       </c>
-      <c r="D4" s="2">
+      <c r="D4" s="5">
         <v>32183</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="E4" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="F4" t="s">
+      <c r="F4" s="4" t="s">
         <v>204</v>
       </c>
-      <c r="G4" t="s">
+      <c r="G4" s="4" t="s">
         <v>166</v>
       </c>
-      <c r="H4" t="s">
+      <c r="H4" s="4" t="s">
         <v>145</v>
       </c>
-      <c r="I4">
+      <c r="I4" s="4">
         <v>55</v>
       </c>
-      <c r="K4" t="s">
+      <c r="K4" s="4" t="s">
         <v>168</v>
       </c>
-      <c r="L4" t="s">
+      <c r="L4" s="4" t="s">
         <v>169</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A5">
+      <c r="A5" s="4">
         <v>4</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="4" t="s">
         <v>170</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="4" t="s">
         <v>143</v>
       </c>
-      <c r="D5" s="2">
+      <c r="D5" s="5">
         <v>33107</v>
       </c>
-      <c r="E5" s="1" t="s">
+      <c r="E5" s="6" t="s">
         <v>172</v>
       </c>
-      <c r="F5" t="s">
+      <c r="F5" s="4" t="s">
         <v>203</v>
       </c>
-      <c r="G5" t="s">
+      <c r="G5" s="4" t="s">
         <v>171</v>
       </c>
-      <c r="H5" t="s">
+      <c r="H5" s="4" t="s">
         <v>147</v>
       </c>
-      <c r="I5">
+      <c r="I5" s="4">
         <v>90</v>
       </c>
-      <c r="K5" t="s">
+      <c r="K5" s="4" t="s">
         <v>173</v>
       </c>
-      <c r="L5" t="s">
+      <c r="L5" s="4" t="s">
         <v>174</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A6">
+      <c r="A6" s="4">
         <v>5</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="4" t="s">
         <v>175</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="4" t="s">
         <v>143</v>
       </c>
-      <c r="D6" s="2">
+      <c r="D6" s="5">
         <v>33859</v>
       </c>
-      <c r="E6" s="1" t="s">
+      <c r="E6" s="6" t="s">
         <v>177</v>
       </c>
-      <c r="F6" t="s">
+      <c r="F6" s="4" t="s">
         <v>199</v>
       </c>
-      <c r="G6" t="s">
+      <c r="G6" s="4" t="s">
         <v>176</v>
       </c>
-      <c r="I6">
+      <c r="I6" s="4">
         <v>76</v>
       </c>
-      <c r="K6" t="s">
+      <c r="K6" s="4" t="s">
         <v>178</v>
       </c>
-      <c r="L6" t="s">
+      <c r="L6" s="4" t="s">
         <v>179</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A7">
+      <c r="A7" s="4">
         <v>6</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="4" t="s">
         <v>180</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" s="4" t="s">
         <v>146</v>
       </c>
-      <c r="D7" s="2">
+      <c r="D7" s="5">
         <v>32051</v>
       </c>
-      <c r="E7" s="1"/>
-      <c r="F7" t="s">
+      <c r="E7" s="6"/>
+      <c r="F7" s="4" t="s">
         <v>204</v>
       </c>
-      <c r="G7" t="s">
+      <c r="G7" s="4" t="s">
         <v>181</v>
       </c>
-      <c r="I7">
+      <c r="I7" s="4">
         <v>70</v>
       </c>
-      <c r="K7" t="s">
+      <c r="K7" s="4" t="s">
         <v>182</v>
       </c>
-      <c r="L7" t="s">
+      <c r="L7" s="4" t="s">
         <v>183</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A8">
+      <c r="A8" s="4">
         <v>7</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="4" t="s">
         <v>184</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C8" s="4" t="s">
         <v>146</v>
       </c>
-      <c r="D8" s="2">
+      <c r="D8" s="5">
         <v>34823</v>
       </c>
-      <c r="F8" t="s">
+      <c r="F8" s="4" t="s">
         <v>199</v>
       </c>
-      <c r="G8" t="s">
+      <c r="G8" s="4" t="s">
         <v>185</v>
       </c>
-      <c r="I8">
+      <c r="I8" s="4">
         <v>74</v>
       </c>
-      <c r="K8" t="s">
+      <c r="K8" s="4" t="s">
         <v>186</v>
       </c>
-      <c r="L8" t="s">
+      <c r="L8" s="4" t="s">
         <v>187</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A9">
+      <c r="A9" s="4">
         <v>8</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="4" t="s">
         <v>188</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C9" s="4" t="s">
         <v>146</v>
       </c>
-      <c r="D9" s="2">
+      <c r="D9" s="5">
         <v>34121</v>
       </c>
-      <c r="E9" s="1" t="s">
+      <c r="E9" s="6" t="s">
         <v>190</v>
       </c>
-      <c r="F9" t="s">
+      <c r="F9" s="4" t="s">
         <v>200</v>
       </c>
-      <c r="G9" t="s">
+      <c r="G9" s="4" t="s">
         <v>189</v>
       </c>
-      <c r="I9">
+      <c r="I9" s="4">
         <v>85</v>
       </c>
-      <c r="K9" t="s">
+      <c r="K9" s="4" t="s">
         <v>191</v>
       </c>
-      <c r="L9" t="s">
+      <c r="L9" s="4" t="s">
         <v>192</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A10">
+      <c r="A10" s="4">
         <v>9</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" s="4" t="s">
         <v>193</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C10" s="4" t="s">
         <v>146</v>
       </c>
-      <c r="D10" s="2">
+      <c r="D10" s="5">
         <v>35278</v>
       </c>
-      <c r="F10" t="s">
+      <c r="F10" s="4" t="s">
         <v>199</v>
       </c>
-      <c r="G10" t="s">
+      <c r="G10" s="4" t="s">
         <v>194</v>
       </c>
-      <c r="I10">
+      <c r="I10" s="4">
         <v>60</v>
       </c>
-      <c r="K10" t="s">
+      <c r="K10" s="4" t="s">
         <v>195</v>
       </c>
-      <c r="L10" t="s">
+      <c r="L10" s="4" t="s">
         <v>196</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A11">
+      <c r="A11" s="4">
         <v>10</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11" s="4" t="s">
         <v>197</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C11" s="4" t="s">
         <v>143</v>
       </c>
-      <c r="D11" s="2">
+      <c r="D11" s="5">
         <v>34881</v>
       </c>
-      <c r="F11" t="s">
+      <c r="F11" s="4" t="s">
         <v>200</v>
       </c>
-      <c r="G11" t="s">
+      <c r="G11" s="4" t="s">
         <v>201</v>
       </c>
-      <c r="I11">
+      <c r="I11" s="4">
         <v>100</v>
       </c>
-      <c r="K11" t="s">
+      <c r="K11" s="4" t="s">
         <v>163</v>
       </c>
-      <c r="L11" t="s">
+      <c r="L11" s="4" t="s">
         <v>198</v>
       </c>
     </row>
@@ -1979,472 +2017,475 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DE67399F-CC12-4ABD-9F7C-F6EE52160CF4}">
   <dimension ref="A1:N33"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="12" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9.5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.5" bestFit="1" customWidth="1"/>
-    <col min="3" max="11" width="10.625" customWidth="1"/>
-    <col min="14" max="14" width="30.875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="7.5" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="7.5" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="11" width="10.625" style="1" customWidth="1"/>
+    <col min="12" max="13" width="9" style="1"/>
+    <col min="14" max="14" width="30.875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="7.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="9" style="1"/>
+    <col min="18" max="18" width="7.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
+      <c r="A2" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="C2">
+      <c r="C2" s="1">
         <v>18</v>
       </c>
-      <c r="D2">
+      <c r="D2" s="1">
         <v>50</v>
       </c>
-      <c r="E2">
+      <c r="E2" s="1">
         <v>50</v>
       </c>
-      <c r="F2">
+      <c r="F2" s="1">
         <v>50</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
+      <c r="A3" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="C3">
+      <c r="C3" s="1">
         <v>19</v>
       </c>
-      <c r="D3">
+      <c r="D3" s="1">
         <v>79</v>
       </c>
-      <c r="E3">
+      <c r="E3" s="1">
         <v>68</v>
       </c>
-      <c r="F3">
+      <c r="F3" s="1">
         <v>85</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
+      <c r="A4" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="C4">
+      <c r="C4" s="1">
         <v>18</v>
       </c>
-      <c r="D4">
+      <c r="D4" s="1">
         <v>89</v>
       </c>
-      <c r="E4">
+      <c r="E4" s="1">
         <v>78</v>
       </c>
-      <c r="F4">
+      <c r="F4" s="1">
         <v>60</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
+      <c r="A5" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="C5">
+      <c r="C5" s="1">
         <v>20</v>
       </c>
-      <c r="D5">
+      <c r="D5" s="1">
         <v>88</v>
       </c>
-      <c r="E5">
+      <c r="E5" s="1">
         <v>84</v>
       </c>
-      <c r="F5">
+      <c r="F5" s="1">
         <v>90</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
+      <c r="A6" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="C6">
+      <c r="C6" s="1">
         <v>17</v>
       </c>
-      <c r="D6">
+      <c r="D6" s="1">
         <v>62</v>
       </c>
-      <c r="E6">
+      <c r="E6" s="1">
         <v>68</v>
       </c>
-      <c r="F6">
+      <c r="F6" s="1">
         <v>88</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
+      <c r="A7" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="C7">
+      <c r="C7" s="1">
         <v>17</v>
       </c>
-      <c r="D7">
+      <c r="D7" s="1">
         <v>74</v>
       </c>
-      <c r="E7">
+      <c r="E7" s="1">
         <v>77</v>
       </c>
-      <c r="F7">
+      <c r="F7" s="1">
         <v>100</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
+      <c r="A8" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="C8">
+      <c r="C8" s="1">
         <v>18</v>
       </c>
-      <c r="D8">
+      <c r="D8" s="1">
         <v>98</v>
       </c>
-      <c r="E8">
+      <c r="E8" s="1">
         <v>71</v>
       </c>
-      <c r="F8">
+      <c r="F8" s="1">
         <v>99</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
+      <c r="A9" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="C9">
+      <c r="C9" s="1">
         <v>17</v>
       </c>
-      <c r="D9">
+      <c r="D9" s="1">
         <v>67</v>
       </c>
-      <c r="E9">
+      <c r="E9" s="1">
         <v>93</v>
       </c>
-      <c r="F9">
+      <c r="F9" s="1">
         <v>91</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
+      <c r="A10" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="C10">
+      <c r="C10" s="1">
         <v>17</v>
       </c>
-      <c r="D10">
+      <c r="D10" s="1">
         <v>81</v>
       </c>
-      <c r="E10">
+      <c r="E10" s="1">
         <v>72</v>
       </c>
-      <c r="F10">
+      <c r="F10" s="1">
         <v>77</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A11" t="s">
+      <c r="A11" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="C11">
+      <c r="C11" s="1">
         <v>18</v>
       </c>
-      <c r="D11">
+      <c r="D11" s="1">
         <v>87</v>
       </c>
-      <c r="E11">
+      <c r="E11" s="1">
         <v>76</v>
       </c>
-      <c r="F11">
+      <c r="F11" s="1">
         <v>89</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A12" t="s">
+      <c r="A12" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B12" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="C12">
+      <c r="C12" s="1">
         <v>20</v>
       </c>
-      <c r="D12">
+      <c r="D12" s="1">
         <v>78</v>
       </c>
-      <c r="E12">
+      <c r="E12" s="1">
         <v>62</v>
       </c>
-      <c r="F12">
+      <c r="F12" s="1">
         <v>81</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A13" t="s">
+      <c r="A13" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B13" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="C13">
+      <c r="C13" s="1">
         <v>17</v>
       </c>
-      <c r="D13">
+      <c r="D13" s="1">
         <v>67</v>
       </c>
-      <c r="E13">
+      <c r="E13" s="1">
         <v>95</v>
       </c>
-      <c r="F13">
+      <c r="F13" s="1">
         <v>69</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A14" t="s">
+      <c r="A14" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B14" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="C14">
+      <c r="C14" s="1">
         <v>18</v>
       </c>
-      <c r="D14">
+      <c r="D14" s="1">
         <v>98</v>
       </c>
-      <c r="E14">
+      <c r="E14" s="1">
         <v>64</v>
       </c>
-      <c r="F14">
+      <c r="F14" s="1">
         <v>91</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A15" t="s">
+      <c r="A15" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B15" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="C15">
+      <c r="C15" s="1">
         <v>17</v>
       </c>
-      <c r="D15">
+      <c r="D15" s="1">
         <v>66</v>
       </c>
-      <c r="E15">
+      <c r="E15" s="1">
         <v>69</v>
       </c>
-      <c r="F15">
+      <c r="F15" s="1">
         <v>79</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A16" t="s">
+      <c r="A16" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B16" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="C16">
+      <c r="C16" s="1">
         <v>17</v>
       </c>
-      <c r="D16">
+      <c r="D16" s="1">
         <v>78</v>
       </c>
-      <c r="E16">
+      <c r="E16" s="1">
         <v>80</v>
       </c>
-      <c r="F16">
+      <c r="F16" s="1">
         <v>90</v>
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A17" t="s">
+      <c r="A17" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B17" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="C17">
+      <c r="C17" s="1">
         <v>19</v>
       </c>
-      <c r="D17">
+      <c r="D17" s="1">
         <v>97</v>
       </c>
-      <c r="E17">
+      <c r="E17" s="1">
         <v>94</v>
       </c>
-      <c r="F17">
+      <c r="F17" s="1">
         <v>96</v>
       </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A18" t="s">
+      <c r="A18" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B18" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="C18">
+      <c r="C18" s="1">
         <v>20</v>
       </c>
-      <c r="D18">
+      <c r="D18" s="1">
         <v>96</v>
       </c>
-      <c r="E18">
+      <c r="E18" s="1">
         <v>93</v>
       </c>
-      <c r="F18">
+      <c r="F18" s="1">
         <v>98</v>
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="J19" t="s">
+      <c r="J19" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="K19" t="s">
-        <v>3</v>
-      </c>
-      <c r="L19" t="s">
+      <c r="K19" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="L19" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="M19" t="s">
+      <c r="M19" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="N19" s="4" t="s">
+      <c r="N19" s="3" t="s">
         <v>224</v>
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B20" t="s">
+      <c r="B20" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="C20" s="3"/>
-      <c r="N20" s="4" t="s">
+      <c r="C20" s="2"/>
+      <c r="N20" s="3" t="s">
         <v>223</v>
       </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B21" t="s">
+      <c r="B21" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="C21" s="3"/>
+      <c r="C21" s="2"/>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B22" t="s">
+      <c r="B22" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="C22" s="3"/>
+      <c r="C22" s="2"/>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B23" t="s">
+      <c r="B23" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="C23" s="3"/>
+      <c r="C23" s="2"/>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B24" t="s">
+      <c r="B24" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="C24" s="3"/>
-      <c r="N24" s="4" t="s">
+      <c r="C24" s="2"/>
+      <c r="N24" s="3" t="s">
         <v>222</v>
       </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B25" t="s">
+      <c r="B25" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="C25" s="3"/>
+      <c r="C25" s="2"/>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A29" t="s">
+      <c r="A29" s="1" t="s">
         <v>219</v>
       </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A30" t="s">
+      <c r="A30" s="1" t="s">
         <v>220</v>
       </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A31" t="s">
+      <c r="A31" s="1" t="s">
         <v>218</v>
       </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A32" t="s">
+      <c r="A32" s="1" t="s">
         <v>217</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A33" t="s">
+      <c r="A33" s="1" t="s">
         <v>216</v>
       </c>
     </row>
@@ -2464,208 +2505,211 @@
   <dimension ref="A1:G13"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="2" width="7.5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.5" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.25" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="7.5" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.5" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9" style="4"/>
+    <col min="6" max="6" width="13.875" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="15" width="9" style="4"/>
+    <col min="16" max="16" width="14.25" style="4" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
+      <c r="A1" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="4" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
+      <c r="A2" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D2">
+      <c r="D2" s="4">
         <v>2500</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F2" s="4" t="s">
         <v>124</v>
       </c>
-      <c r="G2" s="3"/>
+      <c r="G2" s="11"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
+      <c r="A3" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D3">
+      <c r="D3" s="4">
         <v>150</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
+      <c r="A4" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D4">
+      <c r="D4" s="4">
         <v>3000</v>
       </c>
-      <c r="F4" t="s">
+      <c r="F4" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="G4" s="3"/>
+      <c r="G4" s="11"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
+      <c r="A5" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="D5">
+      <c r="D5" s="4">
         <v>4000</v>
       </c>
-      <c r="F5" t="s">
+      <c r="F5" s="4" t="s">
         <v>126</v>
       </c>
-      <c r="G5" s="3"/>
+      <c r="G5" s="11"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
+      <c r="A6" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="D6">
+      <c r="D6" s="4">
         <v>2700</v>
       </c>
-      <c r="F6" t="s">
+      <c r="F6" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="G6" s="3"/>
+      <c r="G6" s="11"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
+      <c r="A7" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="D7">
+      <c r="D7" s="4">
         <v>600</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
+      <c r="A8" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C8" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="D8">
+      <c r="D8" s="4">
         <v>5000</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
+      <c r="A9" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C9" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="D9">
+      <c r="D9" s="4">
         <v>3500</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
+      <c r="A10" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C10" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="D10">
+      <c r="D10" s="4">
         <v>2600</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A11" t="s">
+      <c r="A11" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C11" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="D11">
+      <c r="D11" s="4">
         <v>700</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A12" t="s">
+      <c r="A12" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B12" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="C12" t="s">
+      <c r="C12" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="D12">
+      <c r="D12" s="4">
         <v>1200</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A13" t="s">
+      <c r="A13" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B13" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="C13" t="s">
+      <c r="C13" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="D13">
+      <c r="D13" s="4">
         <v>2200</v>
       </c>
     </row>
@@ -2683,418 +2727,419 @@
   <dimension ref="A1:Q11"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="2" width="9.5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="5.5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="7.5" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="9.5" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="7.5" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="5.5" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="9.5" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.5" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.875" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.125" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5.5" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="7.5" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="9.5" style="4" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7.5" style="4" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="5.5" style="4" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.5" style="4" bestFit="1" customWidth="1"/>
+    <col min="13" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
+      <c r="A1" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="4" t="s">
         <v>115</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="L1" t="s">
+      <c r="L1" s="4" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
+      <c r="A2" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="E2">
+      <c r="E2" s="4">
         <v>21925</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F2" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="G2" t="s">
+      <c r="G2" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="H2">
+      <c r="H2" s="4">
         <v>4700</v>
       </c>
-      <c r="I2">
+      <c r="I2" s="4">
         <v>1500</v>
       </c>
-      <c r="J2">
+      <c r="J2" s="4">
         <v>103</v>
       </c>
-      <c r="K2">
+      <c r="K2" s="4">
         <v>800</v>
       </c>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
+      <c r="A3" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="E3">
+      <c r="E3" s="4">
         <v>25122</v>
       </c>
-      <c r="F3" t="s">
+      <c r="F3" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="G3" t="s">
+      <c r="G3" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="H3">
+      <c r="H3" s="4">
         <v>3200</v>
       </c>
-      <c r="I3">
+      <c r="I3" s="4">
         <v>1000</v>
       </c>
-      <c r="J3">
+      <c r="J3" s="4">
         <v>205</v>
       </c>
-      <c r="K3">
+      <c r="K3" s="4">
         <v>500</v>
       </c>
-      <c r="P3" t="s">
+      <c r="P3" s="4" t="s">
         <v>205</v>
       </c>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
+      <c r="A4" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="E4">
+      <c r="E4" s="4">
         <v>20950</v>
       </c>
-      <c r="F4" t="s">
+      <c r="F4" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="G4" t="s">
+      <c r="G4" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="H4">
+      <c r="H4" s="4">
         <v>3400</v>
       </c>
-      <c r="I4">
+      <c r="I4" s="4">
         <v>1000</v>
       </c>
-      <c r="J4">
+      <c r="J4" s="4">
         <v>162</v>
       </c>
-      <c r="K4">
+      <c r="K4" s="4">
         <v>800</v>
       </c>
-      <c r="P4" t="s">
+      <c r="P4" s="4" t="s">
         <v>129</v>
       </c>
-      <c r="Q4" t="s">
+      <c r="Q4" s="4" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
+      <c r="A5" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D5" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="E5">
+      <c r="E5" s="4">
         <v>22132</v>
       </c>
-      <c r="F5" t="s">
+      <c r="F5" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="G5" t="s">
+      <c r="G5" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="H5">
+      <c r="H5" s="4">
         <v>5000</v>
       </c>
-      <c r="I5">
+      <c r="I5" s="4">
         <v>2000</v>
       </c>
-      <c r="J5">
+      <c r="J5" s="4">
         <v>95.5</v>
       </c>
-      <c r="K5">
+      <c r="K5" s="4">
         <v>1000</v>
       </c>
-      <c r="P5" t="s">
+      <c r="P5" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="Q5" t="s">
+      <c r="Q5" s="4" t="s">
         <v>131</v>
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
+      <c r="A6" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D6" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="E6">
+      <c r="E6" s="4">
         <v>21220</v>
       </c>
-      <c r="F6" t="s">
+      <c r="F6" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="G6" t="s">
+      <c r="G6" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="H6">
+      <c r="H6" s="4">
         <v>4500</v>
       </c>
-      <c r="I6">
+      <c r="I6" s="4">
         <v>1500</v>
       </c>
-      <c r="J6">
+      <c r="J6" s="4">
         <v>100.5</v>
       </c>
-      <c r="K6">
+      <c r="K6" s="4">
         <v>1000</v>
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
+      <c r="A7" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="D7" t="s">
+      <c r="D7" s="4" t="s">
         <v>123</v>
       </c>
-      <c r="E7">
+      <c r="E7" s="4">
         <v>21248</v>
       </c>
-      <c r="F7" t="s">
+      <c r="F7" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="G7" t="s">
+      <c r="G7" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="H7">
+      <c r="H7" s="4">
         <v>3800</v>
       </c>
-      <c r="I7">
+      <c r="I7" s="4">
         <v>1000</v>
       </c>
-      <c r="J7">
+      <c r="J7" s="4">
         <v>150</v>
       </c>
-      <c r="K7">
+      <c r="K7" s="4">
         <v>800</v>
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
+      <c r="A8" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C8" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="D8" t="s">
+      <c r="D8" s="4" t="s">
         <v>123</v>
       </c>
-      <c r="E8">
+      <c r="E8" s="4">
         <v>22951</v>
       </c>
-      <c r="F8" t="s">
+      <c r="F8" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="G8" t="s">
+      <c r="G8" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="H8">
+      <c r="H8" s="4">
         <v>4300</v>
       </c>
-      <c r="I8">
+      <c r="I8" s="4">
         <v>1500</v>
       </c>
-      <c r="J8">
+      <c r="J8" s="4">
         <v>110</v>
       </c>
-      <c r="K8">
+      <c r="K8" s="4">
         <v>480</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
+      <c r="A9" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C9" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="D9" t="s">
+      <c r="D9" s="4" t="s">
         <v>123</v>
       </c>
-      <c r="E9">
+      <c r="E9" s="4">
         <v>20616</v>
       </c>
-      <c r="F9" t="s">
+      <c r="F9" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="G9" t="s">
+      <c r="G9" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="H9">
+      <c r="H9" s="4">
         <v>4500</v>
       </c>
-      <c r="I9">
+      <c r="I9" s="4">
         <v>1500</v>
       </c>
-      <c r="J9">
+      <c r="J9" s="4">
         <v>98.5</v>
       </c>
-      <c r="K9">
+      <c r="K9" s="4">
         <v>900</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
+      <c r="A10" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C10" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="D10" t="s">
+      <c r="D10" s="4" t="s">
         <v>123</v>
       </c>
-      <c r="E10">
+      <c r="E10" s="4">
         <v>21956</v>
       </c>
-      <c r="F10" t="s">
+      <c r="F10" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="G10" t="s">
+      <c r="G10" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="H10">
+      <c r="H10" s="4">
         <v>4600</v>
       </c>
-      <c r="I10">
+      <c r="I10" s="4">
         <v>2000</v>
       </c>
-      <c r="J10">
+      <c r="J10" s="4">
         <v>154</v>
       </c>
-      <c r="K10">
+      <c r="K10" s="4">
         <v>600</v>
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A11" t="s">
+      <c r="A11" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C11" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="D11" t="s">
+      <c r="D11" s="4" t="s">
         <v>123</v>
       </c>
-      <c r="E11">
+      <c r="E11" s="4">
         <v>25851</v>
       </c>
-      <c r="F11" t="s">
+      <c r="F11" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="G11" t="s">
+      <c r="G11" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="H11">
+      <c r="H11" s="4">
         <v>3700</v>
       </c>
-      <c r="I11">
+      <c r="I11" s="4">
         <v>1000</v>
       </c>
-      <c r="J11">
+      <c r="J11" s="4">
         <v>105</v>
       </c>
-      <c r="K11">
+      <c r="K11" s="4">
         <v>800</v>
       </c>
     </row>
@@ -3108,6 +3153,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{91A735B0-C993-4BCF-AB27-DE2EEDBA9C95}">
   <dimension ref="A1:K18"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="5" width="9" style="4"/>
+    <col min="6" max="6" width="9.375" style="4" customWidth="1"/>
+    <col min="7" max="16384" width="9" style="4"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
@@ -3128,7 +3178,7 @@
       <c r="F1" t="s">
         <v>112</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="4" t="s">
         <v>206</v>
       </c>
     </row>
@@ -3152,7 +3202,7 @@
         <f t="shared" ref="F2:F18" si="0">C2+D2+E2</f>
         <v>248</v>
       </c>
-      <c r="K2" t="s">
+      <c r="K2" s="4" t="s">
         <v>207</v>
       </c>
     </row>
@@ -3176,7 +3226,7 @@
         <f t="shared" si="0"/>
         <v>285</v>
       </c>
-      <c r="K3" t="s">
+      <c r="K3" s="4" t="s">
         <v>221</v>
       </c>
     </row>
@@ -3505,44 +3555,47 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6579603A-B2D6-4548-A73D-81A72F0DE6E5}">
   <dimension ref="A1:A12"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="16384" width="9" style="4"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
+      <c r="A1" s="4" t="s">
         <v>208</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
+      <c r="A2" s="4" t="s">
         <v>211</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
+      <c r="A3" s="4" t="s">
         <v>212</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
+      <c r="A4" s="4" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
+      <c r="A5" s="4" t="s">
         <v>210</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
+      <c r="A10" s="4" t="s">
         <v>213</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A11" t="s">
+      <c r="A11" s="4" t="s">
         <v>214</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A12" t="s">
+      <c r="A12" s="4" t="s">
         <v>215</v>
       </c>
     </row>
@@ -3557,3070 +3610,3075 @@
   <dimension ref="A1:S61"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="7" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="5.25" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.125" style="8" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="11" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="16.375" bestFit="1" customWidth="1"/>
-    <col min="20" max="26" width="15.625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="5.25" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9" style="4"/>
+    <col min="5" max="5" width="11.125" style="10" bestFit="1" customWidth="1"/>
+    <col min="6" max="11" width="9" style="4"/>
+    <col min="12" max="12" width="11" style="4" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9" style="4"/>
+    <col min="14" max="14" width="13" style="4" bestFit="1" customWidth="1"/>
+    <col min="15" max="17" width="9" style="4"/>
+    <col min="18" max="18" width="11" style="4" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="16.375" style="4" bestFit="1" customWidth="1"/>
+    <col min="20" max="26" width="15.625" style="4" bestFit="1" customWidth="1"/>
+    <col min="27" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="7" t="s">
         <v>225</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="4" t="s">
         <v>226</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="4" t="s">
         <v>227</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="4" t="s">
         <v>307</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="4" t="s">
         <v>228</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="4" t="s">
         <v>229</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="4" t="s">
         <v>230</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="4" t="s">
         <v>231</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="4" t="s">
         <v>232</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="4" t="s">
         <v>233</v>
       </c>
-      <c r="L1" t="s">
+      <c r="L1" s="4" t="s">
         <v>234</v>
       </c>
-      <c r="M1" t="s">
+      <c r="M1" s="4" t="s">
         <v>235</v>
       </c>
-      <c r="N1" t="s">
+      <c r="N1" s="4" t="s">
         <v>236</v>
       </c>
-      <c r="O1" t="s">
+      <c r="O1" s="4" t="s">
         <v>237</v>
       </c>
-      <c r="P1" t="s">
+      <c r="P1" s="4" t="s">
         <v>238</v>
       </c>
     </row>
     <row r="2" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="7" t="s">
         <v>239</v>
       </c>
-      <c r="B2">
+      <c r="B2" s="4">
         <v>50</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="4" t="s">
         <v>146</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="4" t="s">
         <v>240</v>
       </c>
-      <c r="E2" s="7">
+      <c r="E2" s="8">
         <v>40945</v>
       </c>
-      <c r="F2">
-        <v>3</v>
-      </c>
-      <c r="G2">
+      <c r="F2" s="4">
+        <v>3</v>
+      </c>
+      <c r="G2" s="4">
         <v>1</v>
       </c>
-      <c r="H2">
+      <c r="H2" s="4">
         <v>1</v>
       </c>
-      <c r="I2">
+      <c r="I2" s="4">
         <v>48</v>
       </c>
-      <c r="J2" t="s">
-        <v>241</v>
-      </c>
-      <c r="K2" t="s">
+      <c r="J2" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="K2" s="4" t="s">
         <v>242</v>
       </c>
-      <c r="L2" t="s">
-        <v>243</v>
-      </c>
-      <c r="M2" t="s">
+      <c r="L2" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="M2" s="4" t="s">
         <v>242</v>
       </c>
-      <c r="N2" t="s">
+      <c r="N2" s="4" t="s">
         <v>242</v>
       </c>
-      <c r="O2" t="s">
+      <c r="O2" s="4" t="s">
         <v>242</v>
       </c>
-      <c r="P2" t="s">
+      <c r="P2" s="4" t="s">
         <v>242</v>
       </c>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="7" t="s">
         <v>244</v>
       </c>
-      <c r="B3">
+      <c r="B3" s="4">
         <v>50</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="4" t="s">
         <v>143</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="4" t="s">
         <v>240</v>
       </c>
-      <c r="E3" s="7">
+      <c r="E3" s="8">
         <v>40085</v>
       </c>
-      <c r="F3">
+      <c r="F3" s="4">
         <v>2</v>
       </c>
-      <c r="G3">
+      <c r="G3" s="4">
         <v>2</v>
       </c>
-      <c r="H3">
+      <c r="H3" s="4">
         <v>2</v>
       </c>
-      <c r="I3">
+      <c r="I3" s="4">
         <v>680</v>
       </c>
-      <c r="J3" t="s">
-        <v>241</v>
-      </c>
-      <c r="K3" t="s">
-        <v>243</v>
-      </c>
-      <c r="L3" t="s">
+      <c r="J3" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="K3" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="L3" s="4" t="s">
         <v>242</v>
       </c>
-      <c r="M3" t="s">
-        <v>241</v>
-      </c>
-      <c r="N3" t="s">
-        <v>243</v>
-      </c>
-      <c r="O3" t="s">
-        <v>243</v>
-      </c>
-      <c r="P3" t="s">
+      <c r="M3" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="N3" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="O3" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="P3" s="4" t="s">
         <v>243</v>
       </c>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="7" t="s">
         <v>245</v>
       </c>
-      <c r="B4">
+      <c r="B4" s="4">
         <v>27</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="4" t="s">
         <v>143</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" s="4" t="s">
         <v>246</v>
       </c>
-      <c r="E4" s="7">
+      <c r="E4" s="8">
         <v>42895</v>
       </c>
-      <c r="F4">
-        <v>3</v>
-      </c>
-      <c r="G4">
-        <v>3</v>
-      </c>
-      <c r="H4">
-        <v>3</v>
-      </c>
-      <c r="I4">
+      <c r="F4" s="4">
+        <v>3</v>
+      </c>
+      <c r="G4" s="4">
+        <v>3</v>
+      </c>
+      <c r="H4" s="4">
+        <v>3</v>
+      </c>
+      <c r="I4" s="4">
         <v>260</v>
       </c>
-      <c r="J4" t="s">
+      <c r="J4" s="4" t="s">
         <v>242</v>
       </c>
-      <c r="K4" t="s">
+      <c r="K4" s="4" t="s">
         <v>242</v>
       </c>
-      <c r="L4" t="s">
+      <c r="L4" s="4" t="s">
         <v>247</v>
       </c>
-      <c r="M4" t="s">
+      <c r="M4" s="4" t="s">
         <v>242</v>
       </c>
-      <c r="N4" t="s">
+      <c r="N4" s="4" t="s">
         <v>247</v>
       </c>
-      <c r="O4" t="s">
-        <v>241</v>
-      </c>
-      <c r="P4" t="s">
+      <c r="O4" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="P4" s="4" t="s">
         <v>243</v>
       </c>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="7" t="s">
         <v>248</v>
       </c>
-      <c r="B5">
+      <c r="B5" s="4">
         <v>28</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="4" t="s">
         <v>143</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D5" s="4" t="s">
         <v>246</v>
       </c>
-      <c r="E5" s="7">
+      <c r="E5" s="8">
         <v>43016</v>
       </c>
-      <c r="F5">
-        <v>3</v>
-      </c>
-      <c r="G5">
-        <v>3</v>
-      </c>
-      <c r="H5">
+      <c r="F5" s="4">
+        <v>3</v>
+      </c>
+      <c r="G5" s="4">
+        <v>3</v>
+      </c>
+      <c r="H5" s="4">
         <v>2</v>
       </c>
-      <c r="I5">
+      <c r="I5" s="4">
         <v>180</v>
       </c>
-      <c r="J5" t="s">
-        <v>241</v>
-      </c>
-      <c r="K5" t="s">
-        <v>243</v>
-      </c>
-      <c r="L5" t="s">
+      <c r="J5" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="K5" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="L5" s="4" t="s">
         <v>242</v>
       </c>
-      <c r="M5" t="s">
-        <v>241</v>
-      </c>
-      <c r="N5" t="s">
-        <v>243</v>
-      </c>
-      <c r="O5" t="s">
-        <v>243</v>
-      </c>
-      <c r="P5" t="s">
+      <c r="M5" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="N5" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="O5" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="P5" s="4" t="s">
         <v>242</v>
       </c>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="7" t="s">
         <v>249</v>
       </c>
-      <c r="B6">
+      <c r="B6" s="4">
         <v>24</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="4" t="s">
         <v>143</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D6" s="4" t="s">
         <v>250</v>
       </c>
-      <c r="E6" s="7">
+      <c r="E6" s="8">
         <v>40146</v>
       </c>
-      <c r="F6">
-        <v>3</v>
-      </c>
-      <c r="G6">
+      <c r="F6" s="4">
+        <v>3</v>
+      </c>
+      <c r="G6" s="4">
         <v>2</v>
       </c>
-      <c r="H6">
-        <v>3</v>
-      </c>
-      <c r="I6">
+      <c r="H6" s="4">
+        <v>3</v>
+      </c>
+      <c r="I6" s="4">
         <v>280</v>
       </c>
-      <c r="J6" t="s">
-        <v>241</v>
-      </c>
-      <c r="K6" t="s">
-        <v>243</v>
-      </c>
-      <c r="L6" t="s">
+      <c r="J6" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="K6" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="L6" s="4" t="s">
         <v>247</v>
       </c>
-      <c r="M6" t="s">
-        <v>243</v>
-      </c>
-      <c r="N6" t="s">
-        <v>243</v>
-      </c>
-      <c r="O6" t="s">
-        <v>241</v>
-      </c>
-      <c r="P6" t="s">
+      <c r="M6" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="N6" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="O6" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="P6" s="4" t="s">
         <v>242</v>
       </c>
-      <c r="S6" s="2"/>
+      <c r="S6" s="5"/>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="7" t="s">
         <v>251</v>
       </c>
-      <c r="B7">
+      <c r="B7" s="4">
         <v>36</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" s="4" t="s">
         <v>146</v>
       </c>
-      <c r="D7" t="s">
+      <c r="D7" s="4" t="s">
         <v>240</v>
       </c>
-      <c r="E7" s="7">
+      <c r="E7" s="8">
         <v>39052</v>
       </c>
-      <c r="F7">
-        <v>3</v>
-      </c>
-      <c r="G7">
+      <c r="F7" s="4">
+        <v>3</v>
+      </c>
+      <c r="G7" s="4">
         <v>2</v>
       </c>
-      <c r="H7">
+      <c r="H7" s="4">
         <v>1</v>
       </c>
-      <c r="I7">
+      <c r="I7" s="4">
         <v>50</v>
       </c>
-      <c r="J7" t="s">
-        <v>243</v>
-      </c>
-      <c r="K7" t="s">
-        <v>241</v>
-      </c>
-      <c r="L7" t="s">
-        <v>241</v>
-      </c>
-      <c r="M7" t="s">
-        <v>243</v>
-      </c>
-      <c r="N7" t="s">
-        <v>241</v>
-      </c>
-      <c r="O7" t="s">
+      <c r="J7" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="K7" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="L7" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="M7" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="N7" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="O7" s="4" t="s">
         <v>242</v>
       </c>
-      <c r="P7" t="s">
-        <v>241</v>
-      </c>
-      <c r="S7" s="2"/>
+      <c r="P7" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="S7" s="5"/>
     </row>
     <row r="8" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="7" t="s">
         <v>252</v>
       </c>
-      <c r="B8">
+      <c r="B8" s="4">
         <v>29</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C8" s="4" t="s">
         <v>146</v>
       </c>
-      <c r="D8" t="s">
+      <c r="D8" s="4" t="s">
         <v>253</v>
       </c>
-      <c r="E8" s="7">
+      <c r="E8" s="8">
         <v>36677</v>
       </c>
-      <c r="F8">
-        <v>3</v>
-      </c>
-      <c r="G8">
-        <v>3</v>
-      </c>
-      <c r="H8">
+      <c r="F8" s="4">
+        <v>3</v>
+      </c>
+      <c r="G8" s="4">
+        <v>3</v>
+      </c>
+      <c r="H8" s="4">
         <v>1</v>
       </c>
-      <c r="I8">
+      <c r="I8" s="4">
         <v>60</v>
       </c>
-      <c r="J8" t="s">
-        <v>241</v>
-      </c>
-      <c r="K8" t="s">
-        <v>241</v>
-      </c>
-      <c r="L8" t="s">
-        <v>243</v>
-      </c>
-      <c r="M8" t="s">
-        <v>243</v>
-      </c>
-      <c r="N8" t="s">
-        <v>241</v>
-      </c>
-      <c r="O8" t="s">
-        <v>241</v>
-      </c>
-      <c r="P8" t="s">
-        <v>241</v>
-      </c>
-      <c r="S8" s="2"/>
+      <c r="J8" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="K8" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="L8" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="M8" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="N8" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="O8" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="P8" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="S8" s="5"/>
     </row>
     <row r="9" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A9" s="5" t="s">
+      <c r="A9" s="7" t="s">
         <v>254</v>
       </c>
-      <c r="B9">
+      <c r="B9" s="4">
         <v>53</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C9" s="4" t="s">
         <v>143</v>
       </c>
-      <c r="D9" t="s">
+      <c r="D9" s="4" t="s">
         <v>240</v>
       </c>
-      <c r="E9" s="7">
+      <c r="E9" s="8">
         <v>39861</v>
       </c>
-      <c r="F9">
-        <v>3</v>
-      </c>
-      <c r="G9">
+      <c r="F9" s="4">
+        <v>3</v>
+      </c>
+      <c r="G9" s="4">
         <v>1</v>
       </c>
-      <c r="H9">
-        <v>3</v>
-      </c>
-      <c r="I9">
+      <c r="H9" s="4">
+        <v>3</v>
+      </c>
+      <c r="I9" s="4">
         <v>870</v>
       </c>
-      <c r="J9" t="s">
-        <v>241</v>
-      </c>
-      <c r="K9" t="s">
-        <v>243</v>
-      </c>
-      <c r="L9" t="s">
-        <v>241</v>
-      </c>
-      <c r="M9" t="s">
-        <v>243</v>
-      </c>
-      <c r="N9" t="s">
-        <v>243</v>
-      </c>
-      <c r="O9" t="s">
-        <v>241</v>
-      </c>
-      <c r="P9" t="s">
-        <v>243</v>
-      </c>
-      <c r="S9" s="2"/>
+      <c r="J9" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="K9" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="L9" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="M9" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="N9" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="O9" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="P9" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="S9" s="5"/>
     </row>
     <row r="10" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A10" s="5" t="s">
+      <c r="A10" s="7" t="s">
         <v>255</v>
       </c>
-      <c r="B10">
+      <c r="B10" s="4">
         <v>32</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C10" s="4" t="s">
         <v>143</v>
       </c>
-      <c r="D10" s="6" t="s">
+      <c r="D10" s="9" t="s">
         <v>253</v>
       </c>
-      <c r="E10" s="7">
+      <c r="E10" s="8">
         <v>37867</v>
       </c>
-      <c r="F10">
-        <v>3</v>
-      </c>
-      <c r="G10">
+      <c r="F10" s="4">
+        <v>3</v>
+      </c>
+      <c r="G10" s="4">
         <v>2</v>
       </c>
-      <c r="H10">
+      <c r="H10" s="4">
         <v>1</v>
       </c>
-      <c r="I10">
+      <c r="I10" s="4">
         <v>120</v>
       </c>
-      <c r="J10" t="s">
-        <v>241</v>
-      </c>
-      <c r="K10" t="s">
-        <v>241</v>
-      </c>
-      <c r="L10" t="s">
-        <v>243</v>
-      </c>
-      <c r="M10" t="s">
-        <v>241</v>
-      </c>
-      <c r="N10" t="s">
-        <v>243</v>
-      </c>
-      <c r="O10" t="s">
-        <v>241</v>
-      </c>
-      <c r="P10" t="s">
-        <v>243</v>
-      </c>
-      <c r="S10" s="2"/>
+      <c r="J10" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="K10" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="L10" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="M10" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="N10" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="O10" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="P10" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="S10" s="5"/>
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A11" s="5" t="s">
+      <c r="A11" s="7" t="s">
         <v>256</v>
       </c>
-      <c r="B11">
+      <c r="B11" s="4">
         <v>45</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C11" s="4" t="s">
         <v>146</v>
       </c>
-      <c r="D11" s="6" t="s">
+      <c r="D11" s="9" t="s">
         <v>246</v>
       </c>
-      <c r="E11" s="7">
+      <c r="E11" s="8">
         <v>43561</v>
       </c>
-      <c r="F11">
-        <v>3</v>
-      </c>
-      <c r="G11">
-        <v>3</v>
-      </c>
-      <c r="H11">
+      <c r="F11" s="4">
+        <v>3</v>
+      </c>
+      <c r="G11" s="4">
+        <v>3</v>
+      </c>
+      <c r="H11" s="4">
         <v>1</v>
       </c>
-      <c r="I11">
+      <c r="I11" s="4">
         <v>100</v>
       </c>
-      <c r="J11" t="s">
-        <v>243</v>
-      </c>
-      <c r="K11" t="s">
-        <v>241</v>
-      </c>
-      <c r="L11" t="s">
-        <v>241</v>
-      </c>
-      <c r="M11" t="s">
-        <v>243</v>
-      </c>
-      <c r="N11" t="s">
-        <v>241</v>
-      </c>
-      <c r="O11" t="s">
-        <v>241</v>
-      </c>
-      <c r="P11" t="s">
-        <v>241</v>
-      </c>
-      <c r="S11" s="2"/>
+      <c r="J11" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="K11" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="L11" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="M11" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="N11" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="O11" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="P11" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="S11" s="5"/>
     </row>
     <row r="12" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A12" s="5" t="s">
+      <c r="A12" s="7" t="s">
         <v>257</v>
       </c>
-      <c r="B12">
+      <c r="B12" s="4">
         <v>20</v>
       </c>
-      <c r="C12" t="s">
+      <c r="C12" s="4" t="s">
         <v>146</v>
       </c>
-      <c r="D12" s="6" t="s">
+      <c r="D12" s="9" t="s">
         <v>253</v>
       </c>
-      <c r="E12" s="7">
+      <c r="E12" s="8">
         <v>37417</v>
       </c>
-      <c r="F12">
-        <v>3</v>
-      </c>
-      <c r="G12">
+      <c r="F12" s="4">
+        <v>3</v>
+      </c>
+      <c r="G12" s="4">
         <v>2</v>
       </c>
-      <c r="H12">
+      <c r="H12" s="4">
         <v>2</v>
       </c>
-      <c r="I12">
+      <c r="I12" s="4">
         <v>120</v>
       </c>
-      <c r="J12" t="s">
-        <v>241</v>
-      </c>
-      <c r="K12" t="s">
-        <v>243</v>
-      </c>
-      <c r="L12" t="s">
-        <v>243</v>
-      </c>
-      <c r="M12" t="s">
-        <v>243</v>
-      </c>
-      <c r="N12" t="s">
-        <v>241</v>
-      </c>
-      <c r="O12" t="s">
-        <v>241</v>
-      </c>
-      <c r="P12" t="s">
-        <v>241</v>
-      </c>
-      <c r="S12" s="2"/>
+      <c r="J12" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="K12" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="L12" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="M12" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="N12" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="O12" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="P12" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="S12" s="5"/>
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A13" s="5" t="s">
+      <c r="A13" s="7" t="s">
         <v>258</v>
       </c>
-      <c r="B13">
+      <c r="B13" s="4">
         <v>33</v>
       </c>
-      <c r="C13" t="s">
+      <c r="C13" s="4" t="s">
         <v>146</v>
       </c>
-      <c r="D13" s="6" t="s">
+      <c r="D13" s="9" t="s">
         <v>246</v>
       </c>
-      <c r="E13" s="7">
+      <c r="E13" s="8">
         <v>41971</v>
       </c>
-      <c r="F13">
-        <v>3</v>
-      </c>
-      <c r="G13">
+      <c r="F13" s="4">
+        <v>3</v>
+      </c>
+      <c r="G13" s="4">
         <v>2</v>
       </c>
-      <c r="H13">
+      <c r="H13" s="4">
         <v>2</v>
       </c>
-      <c r="I13">
+      <c r="I13" s="4">
         <v>150</v>
       </c>
-      <c r="J13" t="s">
-        <v>241</v>
-      </c>
-      <c r="K13" t="s">
-        <v>241</v>
-      </c>
-      <c r="L13" t="s">
-        <v>243</v>
-      </c>
-      <c r="M13" t="s">
-        <v>243</v>
-      </c>
-      <c r="N13" t="s">
-        <v>243</v>
-      </c>
-      <c r="O13" t="s">
-        <v>241</v>
-      </c>
-      <c r="P13" t="s">
+      <c r="J13" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="K13" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="L13" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="M13" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="N13" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="O13" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="P13" s="4" t="s">
         <v>241</v>
       </c>
     </row>
     <row r="14" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A14" s="5" t="s">
+      <c r="A14" s="7" t="s">
         <v>259</v>
       </c>
-      <c r="B14">
+      <c r="B14" s="4">
         <v>23</v>
       </c>
-      <c r="C14" t="s">
+      <c r="C14" s="4" t="s">
         <v>143</v>
       </c>
-      <c r="D14" s="6" t="s">
+      <c r="D14" s="9" t="s">
         <v>253</v>
       </c>
-      <c r="E14" s="7">
+      <c r="E14" s="8">
         <v>38717</v>
       </c>
-      <c r="F14">
-        <v>3</v>
-      </c>
-      <c r="G14">
-        <v>3</v>
-      </c>
-      <c r="H14">
+      <c r="F14" s="4">
+        <v>3</v>
+      </c>
+      <c r="G14" s="4">
+        <v>3</v>
+      </c>
+      <c r="H14" s="4">
         <v>2</v>
       </c>
-      <c r="I14">
+      <c r="I14" s="4">
         <v>100</v>
       </c>
-      <c r="J14" t="s">
-        <v>241</v>
-      </c>
-      <c r="K14" t="s">
-        <v>243</v>
-      </c>
-      <c r="L14" t="s">
-        <v>241</v>
-      </c>
-      <c r="M14" t="s">
-        <v>243</v>
-      </c>
-      <c r="N14" t="s">
-        <v>243</v>
-      </c>
-      <c r="O14" t="s">
-        <v>241</v>
-      </c>
-      <c r="P14" t="s">
+      <c r="J14" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="K14" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="L14" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="M14" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="N14" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="O14" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="P14" s="4" t="s">
         <v>241</v>
       </c>
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A15" s="5" t="s">
+      <c r="A15" s="7" t="s">
         <v>260</v>
       </c>
-      <c r="B15">
+      <c r="B15" s="4">
         <v>40</v>
       </c>
-      <c r="C15" t="s">
+      <c r="C15" s="4" t="s">
         <v>143</v>
       </c>
-      <c r="D15" s="6" t="s">
+      <c r="D15" s="9" t="s">
         <v>253</v>
       </c>
-      <c r="E15" s="7">
+      <c r="E15" s="8">
         <v>36811</v>
       </c>
-      <c r="F15">
-        <v>3</v>
-      </c>
-      <c r="G15">
+      <c r="F15" s="4">
+        <v>3</v>
+      </c>
+      <c r="G15" s="4">
         <v>1</v>
       </c>
-      <c r="H15">
+      <c r="H15" s="4">
         <v>2</v>
       </c>
-      <c r="I15">
+      <c r="I15" s="4">
         <v>280</v>
       </c>
-      <c r="J15" t="s">
-        <v>241</v>
-      </c>
-      <c r="K15" t="s">
-        <v>243</v>
-      </c>
-      <c r="L15" t="s">
-        <v>241</v>
-      </c>
-      <c r="M15" t="s">
-        <v>241</v>
-      </c>
-      <c r="N15" t="s">
-        <v>243</v>
-      </c>
-      <c r="O15" t="s">
-        <v>241</v>
-      </c>
-      <c r="P15" t="s">
+      <c r="J15" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="K15" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="L15" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="M15" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="N15" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="O15" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="P15" s="4" t="s">
         <v>243</v>
       </c>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A16" s="5" t="s">
+      <c r="A16" s="7" t="s">
         <v>261</v>
       </c>
-      <c r="B16">
+      <c r="B16" s="4">
         <v>42</v>
       </c>
-      <c r="C16" t="s">
+      <c r="C16" s="4" t="s">
         <v>146</v>
       </c>
-      <c r="D16" t="s">
+      <c r="D16" s="4" t="s">
         <v>240</v>
       </c>
-      <c r="E16" s="7">
+      <c r="E16" s="8">
         <v>43610</v>
       </c>
-      <c r="F16">
-        <v>3</v>
-      </c>
-      <c r="G16">
+      <c r="F16" s="4">
+        <v>3</v>
+      </c>
+      <c r="G16" s="4">
         <v>1</v>
       </c>
-      <c r="H16">
+      <c r="H16" s="4">
         <v>2</v>
       </c>
-      <c r="I16">
+      <c r="I16" s="4">
         <v>200</v>
       </c>
-      <c r="J16" t="s">
-        <v>241</v>
-      </c>
-      <c r="K16" t="s">
-        <v>243</v>
-      </c>
-      <c r="L16" t="s">
+      <c r="J16" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="K16" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="L16" s="4" t="s">
         <v>242</v>
       </c>
-      <c r="M16" t="s">
-        <v>243</v>
-      </c>
-      <c r="N16" t="s">
-        <v>243</v>
-      </c>
-      <c r="O16" t="s">
+      <c r="M16" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="N16" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="O16" s="4" t="s">
         <v>242</v>
       </c>
-      <c r="P16" t="s">
+      <c r="P16" s="4" t="s">
         <v>242</v>
       </c>
     </row>
     <row r="17" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A17" s="5" t="s">
+      <c r="A17" s="7" t="s">
         <v>262</v>
       </c>
-      <c r="B17">
+      <c r="B17" s="4">
         <v>46</v>
       </c>
-      <c r="C17" t="s">
+      <c r="C17" s="4" t="s">
         <v>143</v>
       </c>
-      <c r="D17" t="s">
+      <c r="D17" s="4" t="s">
         <v>246</v>
       </c>
-      <c r="E17" s="7">
+      <c r="E17" s="8">
         <v>43111</v>
       </c>
-      <c r="F17">
+      <c r="F17" s="4">
         <v>2</v>
       </c>
-      <c r="G17">
+      <c r="G17" s="4">
         <v>1</v>
       </c>
-      <c r="H17">
+      <c r="H17" s="4">
         <v>2</v>
       </c>
-      <c r="I17">
+      <c r="I17" s="4">
         <v>380</v>
       </c>
-      <c r="J17" t="s">
-        <v>241</v>
-      </c>
-      <c r="K17" t="s">
-        <v>243</v>
-      </c>
-      <c r="L17" t="s">
+      <c r="J17" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="K17" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="L17" s="4" t="s">
         <v>242</v>
       </c>
-      <c r="M17" t="s">
-        <v>241</v>
-      </c>
-      <c r="N17" t="s">
-        <v>243</v>
-      </c>
-      <c r="O17" t="s">
-        <v>241</v>
-      </c>
-      <c r="P17" t="s">
+      <c r="M17" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="N17" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="O17" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="P17" s="4" t="s">
         <v>243</v>
       </c>
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A18" s="5" t="s">
+      <c r="A18" s="7" t="s">
         <v>263</v>
       </c>
-      <c r="B18">
+      <c r="B18" s="4">
         <v>27</v>
       </c>
-      <c r="C18" t="s">
+      <c r="C18" s="4" t="s">
         <v>146</v>
       </c>
-      <c r="D18" t="s">
+      <c r="D18" s="4" t="s">
         <v>250</v>
       </c>
-      <c r="E18" s="7">
+      <c r="E18" s="8">
         <v>42037</v>
       </c>
-      <c r="F18">
-        <v>3</v>
-      </c>
-      <c r="G18">
-        <v>3</v>
-      </c>
-      <c r="H18">
+      <c r="F18" s="4">
+        <v>3</v>
+      </c>
+      <c r="G18" s="4">
+        <v>3</v>
+      </c>
+      <c r="H18" s="4">
         <v>2</v>
       </c>
-      <c r="I18">
+      <c r="I18" s="4">
         <v>210</v>
       </c>
-      <c r="J18" t="s">
+      <c r="J18" s="4" t="s">
         <v>242</v>
       </c>
-      <c r="K18" t="s">
-        <v>243</v>
-      </c>
-      <c r="L18" t="s">
-        <v>241</v>
-      </c>
-      <c r="M18" t="s">
-        <v>243</v>
-      </c>
-      <c r="N18" t="s">
+      <c r="K18" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="L18" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="M18" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="N18" s="4" t="s">
         <v>247</v>
       </c>
-      <c r="O18" t="s">
-        <v>241</v>
-      </c>
-      <c r="P18" t="s">
+      <c r="O18" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="P18" s="4" t="s">
         <v>242</v>
       </c>
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A19" s="5" t="s">
+      <c r="A19" s="7" t="s">
         <v>264</v>
       </c>
-      <c r="B19">
+      <c r="B19" s="4">
         <v>33</v>
       </c>
-      <c r="C19" t="s">
+      <c r="C19" s="4" t="s">
         <v>146</v>
       </c>
-      <c r="D19" t="s">
+      <c r="D19" s="4" t="s">
         <v>246</v>
       </c>
-      <c r="E19" s="7">
+      <c r="E19" s="8">
         <v>42820</v>
       </c>
-      <c r="F19">
-        <v>3</v>
-      </c>
-      <c r="G19">
+      <c r="F19" s="4">
+        <v>3</v>
+      </c>
+      <c r="G19" s="4">
         <v>2</v>
       </c>
-      <c r="H19">
+      <c r="H19" s="4">
         <v>1</v>
       </c>
-      <c r="I19">
+      <c r="I19" s="4">
         <v>48</v>
       </c>
-      <c r="J19" t="s">
-        <v>241</v>
-      </c>
-      <c r="K19" t="s">
+      <c r="J19" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="K19" s="4" t="s">
         <v>242</v>
       </c>
-      <c r="L19" t="s">
-        <v>243</v>
-      </c>
-      <c r="M19" t="s">
-        <v>241</v>
-      </c>
-      <c r="N19" t="s">
+      <c r="L19" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="M19" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="N19" s="4" t="s">
         <v>242</v>
       </c>
-      <c r="O19" t="s">
+      <c r="O19" s="4" t="s">
         <v>242</v>
       </c>
-      <c r="P19" t="s">
+      <c r="P19" s="4" t="s">
         <v>242</v>
       </c>
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A20" s="5" t="s">
+      <c r="A20" s="7" t="s">
         <v>265</v>
       </c>
-      <c r="B20">
+      <c r="B20" s="4">
         <v>18</v>
       </c>
-      <c r="C20" t="s">
+      <c r="C20" s="4" t="s">
         <v>143</v>
       </c>
-      <c r="D20" t="s">
+      <c r="D20" s="4" t="s">
         <v>250</v>
       </c>
-      <c r="E20" s="7">
+      <c r="E20" s="8">
         <v>41940</v>
       </c>
-      <c r="F20">
-        <v>3</v>
-      </c>
-      <c r="G20">
+      <c r="F20" s="4">
+        <v>3</v>
+      </c>
+      <c r="G20" s="4">
         <v>2</v>
       </c>
-      <c r="H20">
-        <v>3</v>
-      </c>
-      <c r="I20">
+      <c r="H20" s="4">
+        <v>3</v>
+      </c>
+      <c r="I20" s="4">
         <v>160</v>
       </c>
-      <c r="J20" t="s">
-        <v>241</v>
-      </c>
-      <c r="K20" t="s">
-        <v>243</v>
-      </c>
-      <c r="L20" t="s">
-        <v>241</v>
-      </c>
-      <c r="M20" t="s">
-        <v>241</v>
-      </c>
-      <c r="N20" t="s">
-        <v>243</v>
-      </c>
-      <c r="O20" t="s">
-        <v>243</v>
-      </c>
-      <c r="P20" t="s">
+      <c r="J20" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="K20" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="L20" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="M20" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="N20" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="O20" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="P20" s="4" t="s">
         <v>242</v>
       </c>
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A21" s="5" t="s">
+      <c r="A21" s="7" t="s">
         <v>266</v>
       </c>
-      <c r="B21">
+      <c r="B21" s="4">
         <v>35</v>
       </c>
-      <c r="C21" t="s">
+      <c r="C21" s="4" t="s">
         <v>146</v>
       </c>
-      <c r="D21" t="s">
+      <c r="D21" s="4" t="s">
         <v>240</v>
       </c>
-      <c r="E21" s="7">
+      <c r="E21" s="8">
         <v>40444</v>
       </c>
-      <c r="F21">
-        <v>3</v>
-      </c>
-      <c r="G21">
+      <c r="F21" s="4">
+        <v>3</v>
+      </c>
+      <c r="G21" s="4">
         <v>2</v>
       </c>
-      <c r="H21">
+      <c r="H21" s="4">
         <v>1</v>
       </c>
-      <c r="I21">
+      <c r="I21" s="4">
         <v>48</v>
       </c>
-      <c r="J21" t="s">
-        <v>241</v>
-      </c>
-      <c r="K21" t="s">
+      <c r="J21" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="K21" s="4" t="s">
         <v>242</v>
       </c>
-      <c r="L21" t="s">
-        <v>243</v>
-      </c>
-      <c r="M21" t="s">
-        <v>241</v>
-      </c>
-      <c r="N21" t="s">
+      <c r="L21" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="M21" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="N21" s="4" t="s">
         <v>242</v>
       </c>
-      <c r="O21" t="s">
+      <c r="O21" s="4" t="s">
         <v>242</v>
       </c>
-      <c r="P21" t="s">
+      <c r="P21" s="4" t="s">
         <v>241</v>
       </c>
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A22" s="5" t="s">
+      <c r="A22" s="7" t="s">
         <v>267</v>
       </c>
-      <c r="B22">
+      <c r="B22" s="4">
         <v>17</v>
       </c>
-      <c r="C22" t="s">
+      <c r="C22" s="4" t="s">
         <v>146</v>
       </c>
-      <c r="D22" t="s">
+      <c r="D22" s="4" t="s">
         <v>253</v>
       </c>
-      <c r="E22" s="7">
+      <c r="E22" s="8">
         <v>36758</v>
       </c>
-      <c r="F22">
-        <v>3</v>
-      </c>
-      <c r="G22">
+      <c r="F22" s="4">
+        <v>3</v>
+      </c>
+      <c r="G22" s="4">
         <v>1</v>
       </c>
-      <c r="H22">
+      <c r="H22" s="4">
         <v>1</v>
       </c>
-      <c r="I22">
+      <c r="I22" s="4">
         <v>48</v>
       </c>
-      <c r="J22" t="s">
-        <v>241</v>
-      </c>
-      <c r="K22" t="s">
-        <v>241</v>
-      </c>
-      <c r="L22" t="s">
-        <v>243</v>
-      </c>
-      <c r="M22" t="s">
-        <v>241</v>
-      </c>
-      <c r="N22" t="s">
-        <v>241</v>
-      </c>
-      <c r="O22" t="s">
-        <v>241</v>
-      </c>
-      <c r="P22" t="s">
+      <c r="J22" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="K22" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="L22" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="M22" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="N22" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="O22" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="P22" s="4" t="s">
         <v>241</v>
       </c>
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A23" s="5" t="s">
+      <c r="A23" s="7" t="s">
         <v>268</v>
       </c>
-      <c r="B23">
+      <c r="B23" s="4">
         <v>47</v>
       </c>
-      <c r="C23" t="s">
+      <c r="C23" s="4" t="s">
         <v>146</v>
       </c>
-      <c r="D23" t="s">
+      <c r="D23" s="4" t="s">
         <v>240</v>
       </c>
-      <c r="E23" s="7">
+      <c r="E23" s="8">
         <v>38062</v>
       </c>
-      <c r="F23">
-        <v>3</v>
-      </c>
-      <c r="G23">
+      <c r="F23" s="4">
+        <v>3</v>
+      </c>
+      <c r="G23" s="4">
         <v>1</v>
       </c>
-      <c r="H23">
+      <c r="H23" s="4">
         <v>1</v>
       </c>
-      <c r="I23">
+      <c r="I23" s="4">
         <v>48</v>
       </c>
-      <c r="J23" t="s">
-        <v>241</v>
-      </c>
-      <c r="K23" t="s">
-        <v>241</v>
-      </c>
-      <c r="L23" t="s">
-        <v>243</v>
-      </c>
-      <c r="M23" t="s">
-        <v>241</v>
-      </c>
-      <c r="N23" t="s">
-        <v>241</v>
-      </c>
-      <c r="O23" t="s">
-        <v>241</v>
-      </c>
-      <c r="P23" t="s">
+      <c r="J23" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="K23" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="L23" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="M23" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="N23" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="O23" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="P23" s="4" t="s">
         <v>241</v>
       </c>
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A24" s="5" t="s">
+      <c r="A24" s="7" t="s">
         <v>269</v>
       </c>
-      <c r="B24">
+      <c r="B24" s="4">
         <v>35</v>
       </c>
-      <c r="C24" t="s">
+      <c r="C24" s="4" t="s">
         <v>143</v>
       </c>
-      <c r="D24" s="6" t="s">
+      <c r="D24" s="9" t="s">
         <v>240</v>
       </c>
-      <c r="E24" s="7">
+      <c r="E24" s="8">
         <v>37911</v>
       </c>
-      <c r="F24">
-        <v>3</v>
-      </c>
-      <c r="G24">
+      <c r="F24" s="4">
+        <v>3</v>
+      </c>
+      <c r="G24" s="4">
         <v>1</v>
       </c>
-      <c r="H24">
+      <c r="H24" s="4">
         <v>2</v>
       </c>
-      <c r="I24">
+      <c r="I24" s="4">
         <v>280</v>
       </c>
-      <c r="J24" t="s">
-        <v>241</v>
-      </c>
-      <c r="K24" t="s">
-        <v>243</v>
-      </c>
-      <c r="L24" t="s">
-        <v>241</v>
-      </c>
-      <c r="M24" t="s">
-        <v>241</v>
-      </c>
-      <c r="N24" t="s">
-        <v>243</v>
-      </c>
-      <c r="O24" t="s">
-        <v>241</v>
-      </c>
-      <c r="P24" t="s">
+      <c r="J24" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="K24" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="L24" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="M24" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="N24" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="O24" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="P24" s="4" t="s">
         <v>243</v>
       </c>
     </row>
     <row r="25" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A25" s="5" t="s">
+      <c r="A25" s="7" t="s">
         <v>270</v>
       </c>
-      <c r="B25">
+      <c r="B25" s="4">
         <v>19</v>
       </c>
-      <c r="C25" t="s">
+      <c r="C25" s="4" t="s">
         <v>146</v>
       </c>
-      <c r="D25" s="6" t="s">
+      <c r="D25" s="9" t="s">
         <v>253</v>
       </c>
-      <c r="E25" s="7">
+      <c r="E25" s="8">
         <v>42927</v>
       </c>
-      <c r="F25">
-        <v>3</v>
-      </c>
-      <c r="G25">
+      <c r="F25" s="4">
+        <v>3</v>
+      </c>
+      <c r="G25" s="4">
         <v>2</v>
       </c>
-      <c r="H25">
+      <c r="H25" s="4">
         <v>1</v>
       </c>
-      <c r="I25">
+      <c r="I25" s="4">
         <v>68</v>
       </c>
-      <c r="J25" t="s">
-        <v>241</v>
-      </c>
-      <c r="K25" t="s">
-        <v>241</v>
-      </c>
-      <c r="L25" t="s">
-        <v>243</v>
-      </c>
-      <c r="M25" t="s">
-        <v>243</v>
-      </c>
-      <c r="N25" t="s">
-        <v>241</v>
-      </c>
-      <c r="O25" t="s">
-        <v>241</v>
-      </c>
-      <c r="P25" t="s">
+      <c r="J25" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="K25" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="L25" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="M25" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="N25" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="O25" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="P25" s="4" t="s">
         <v>241</v>
       </c>
     </row>
     <row r="26" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A26" s="5" t="s">
+      <c r="A26" s="7" t="s">
         <v>271</v>
       </c>
-      <c r="B26">
+      <c r="B26" s="4">
         <v>20</v>
       </c>
-      <c r="C26" t="s">
+      <c r="C26" s="4" t="s">
         <v>146</v>
       </c>
-      <c r="D26" s="6" t="s">
+      <c r="D26" s="9" t="s">
         <v>253</v>
       </c>
-      <c r="E26" s="7">
+      <c r="E26" s="8">
         <v>41560</v>
       </c>
-      <c r="F26">
-        <v>3</v>
-      </c>
-      <c r="G26">
+      <c r="F26" s="4">
+        <v>3</v>
+      </c>
+      <c r="G26" s="4">
         <v>1</v>
       </c>
-      <c r="H26">
+      <c r="H26" s="4">
         <v>2</v>
       </c>
-      <c r="I26">
+      <c r="I26" s="4">
         <v>100</v>
       </c>
-      <c r="J26" t="s">
-        <v>241</v>
-      </c>
-      <c r="K26" t="s">
-        <v>243</v>
-      </c>
-      <c r="L26" t="s">
-        <v>241</v>
-      </c>
-      <c r="M26" t="s">
-        <v>243</v>
-      </c>
-      <c r="N26" t="s">
-        <v>241</v>
-      </c>
-      <c r="O26" t="s">
-        <v>241</v>
-      </c>
-      <c r="P26" t="s">
+      <c r="J26" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="K26" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="L26" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="M26" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="N26" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="O26" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="P26" s="4" t="s">
         <v>241</v>
       </c>
     </row>
     <row r="27" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A27" s="5" t="s">
+      <c r="A27" s="7" t="s">
         <v>272</v>
       </c>
-      <c r="B27">
+      <c r="B27" s="4">
         <v>33</v>
       </c>
-      <c r="C27" t="s">
+      <c r="C27" s="4" t="s">
         <v>143</v>
       </c>
-      <c r="D27" s="6" t="s">
+      <c r="D27" s="9" t="s">
         <v>253</v>
       </c>
-      <c r="E27" s="7">
+      <c r="E27" s="8">
         <v>42886</v>
       </c>
-      <c r="F27">
-        <v>3</v>
-      </c>
-      <c r="G27">
+      <c r="F27" s="4">
+        <v>3</v>
+      </c>
+      <c r="G27" s="4">
         <v>1</v>
       </c>
-      <c r="H27">
+      <c r="H27" s="4">
         <v>1</v>
       </c>
-      <c r="I27">
+      <c r="I27" s="4">
         <v>100</v>
       </c>
-      <c r="J27" t="s">
-        <v>241</v>
-      </c>
-      <c r="K27" t="s">
-        <v>243</v>
-      </c>
-      <c r="L27" t="s">
-        <v>241</v>
-      </c>
-      <c r="M27" t="s">
+      <c r="J27" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="K27" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="L27" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="M27" s="4" t="s">
         <v>273</v>
       </c>
-      <c r="N27" t="s">
-        <v>243</v>
-      </c>
-      <c r="O27" t="s">
-        <v>243</v>
-      </c>
-      <c r="P27" t="s">
+      <c r="N27" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="O27" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="P27" s="4" t="s">
         <v>241</v>
       </c>
     </row>
     <row r="28" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A28" s="5" t="s">
+      <c r="A28" s="7" t="s">
         <v>274</v>
       </c>
-      <c r="B28">
+      <c r="B28" s="4">
         <v>23</v>
       </c>
-      <c r="C28" t="s">
+      <c r="C28" s="4" t="s">
         <v>143</v>
       </c>
-      <c r="D28" s="6" t="s">
+      <c r="D28" s="9" t="s">
         <v>253</v>
       </c>
-      <c r="E28" s="7">
+      <c r="E28" s="8">
         <v>39345</v>
       </c>
-      <c r="F28">
-        <v>3</v>
-      </c>
-      <c r="G28">
+      <c r="F28" s="4">
+        <v>3</v>
+      </c>
+      <c r="G28" s="4">
         <v>1</v>
       </c>
-      <c r="H28">
+      <c r="H28" s="4">
         <v>1</v>
       </c>
-      <c r="I28">
+      <c r="I28" s="4">
         <v>80</v>
       </c>
-      <c r="J28" t="s">
-        <v>241</v>
-      </c>
-      <c r="K28" t="s">
-        <v>241</v>
-      </c>
-      <c r="L28" t="s">
-        <v>243</v>
-      </c>
-      <c r="M28" t="s">
-        <v>241</v>
-      </c>
-      <c r="N28" t="s">
-        <v>243</v>
-      </c>
-      <c r="O28" t="s">
-        <v>243</v>
-      </c>
-      <c r="P28" t="s">
+      <c r="J28" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="K28" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="L28" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="M28" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="N28" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="O28" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="P28" s="4" t="s">
         <v>241</v>
       </c>
     </row>
     <row r="29" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A29" s="5" t="s">
+      <c r="A29" s="7" t="s">
         <v>275</v>
       </c>
-      <c r="B29">
+      <c r="B29" s="4">
         <v>57</v>
       </c>
-      <c r="C29" t="s">
+      <c r="C29" s="4" t="s">
         <v>146</v>
       </c>
-      <c r="D29" s="6" t="s">
+      <c r="D29" s="9" t="s">
         <v>240</v>
       </c>
-      <c r="E29" s="7">
+      <c r="E29" s="8">
         <v>39725</v>
       </c>
-      <c r="F29">
-        <v>3</v>
-      </c>
-      <c r="G29">
+      <c r="F29" s="4">
+        <v>3</v>
+      </c>
+      <c r="G29" s="4">
         <v>1</v>
       </c>
-      <c r="H29">
+      <c r="H29" s="4">
         <v>2</v>
       </c>
-      <c r="I29">
+      <c r="I29" s="4">
         <v>212</v>
       </c>
-      <c r="J29" t="s">
-        <v>241</v>
-      </c>
-      <c r="K29" t="s">
-        <v>243</v>
-      </c>
-      <c r="L29" t="s">
-        <v>241</v>
-      </c>
-      <c r="M29" t="s">
-        <v>243</v>
-      </c>
-      <c r="N29" t="s">
-        <v>243</v>
-      </c>
-      <c r="O29" t="s">
-        <v>243</v>
-      </c>
-      <c r="P29" t="s">
+      <c r="J29" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="K29" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="L29" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="M29" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="N29" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="O29" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="P29" s="4" t="s">
         <v>241</v>
       </c>
     </row>
     <row r="30" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A30" s="5" t="s">
+      <c r="A30" s="7" t="s">
         <v>276</v>
       </c>
-      <c r="B30">
+      <c r="B30" s="4">
         <v>37</v>
       </c>
-      <c r="C30" t="s">
+      <c r="C30" s="4" t="s">
         <v>143</v>
       </c>
-      <c r="D30" s="6" t="s">
+      <c r="D30" s="9" t="s">
         <v>240</v>
       </c>
-      <c r="E30" s="7">
+      <c r="E30" s="8">
         <v>41797</v>
       </c>
-      <c r="F30">
-        <v>3</v>
-      </c>
-      <c r="G30">
+      <c r="F30" s="4">
+        <v>3</v>
+      </c>
+      <c r="G30" s="4">
         <v>1</v>
       </c>
-      <c r="H30">
+      <c r="H30" s="4">
         <v>2</v>
       </c>
-      <c r="I30">
+      <c r="I30" s="4">
         <v>280</v>
       </c>
-      <c r="J30" t="s">
-        <v>241</v>
-      </c>
-      <c r="K30" t="s">
-        <v>243</v>
-      </c>
-      <c r="L30" t="s">
-        <v>241</v>
-      </c>
-      <c r="M30" t="s">
-        <v>241</v>
-      </c>
-      <c r="N30" t="s">
-        <v>243</v>
-      </c>
-      <c r="O30" t="s">
-        <v>241</v>
-      </c>
-      <c r="P30" t="s">
+      <c r="J30" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="K30" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="L30" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="M30" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="N30" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="O30" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="P30" s="4" t="s">
         <v>243</v>
       </c>
     </row>
     <row r="31" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A31" s="5" t="s">
+      <c r="A31" s="7" t="s">
         <v>277</v>
       </c>
-      <c r="B31">
+      <c r="B31" s="4">
         <v>48</v>
       </c>
-      <c r="C31" t="s">
+      <c r="C31" s="4" t="s">
         <v>143</v>
       </c>
-      <c r="D31" s="6" t="s">
+      <c r="D31" s="9" t="s">
         <v>246</v>
       </c>
-      <c r="E31" s="7">
+      <c r="E31" s="8">
         <v>42064</v>
       </c>
-      <c r="F31">
-        <v>3</v>
-      </c>
-      <c r="G31">
+      <c r="F31" s="4">
+        <v>3</v>
+      </c>
+      <c r="G31" s="4">
         <v>2</v>
       </c>
-      <c r="H31">
-        <v>3</v>
-      </c>
-      <c r="I31">
+      <c r="H31" s="4">
+        <v>3</v>
+      </c>
+      <c r="I31" s="4">
         <v>420</v>
       </c>
-      <c r="J31" t="s">
-        <v>241</v>
-      </c>
-      <c r="K31" t="s">
-        <v>243</v>
-      </c>
-      <c r="L31" t="s">
-        <v>241</v>
-      </c>
-      <c r="M31" t="s">
-        <v>241</v>
-      </c>
-      <c r="N31" t="s">
-        <v>243</v>
-      </c>
-      <c r="O31" t="s">
-        <v>241</v>
-      </c>
-      <c r="P31" t="s">
+      <c r="J31" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="K31" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="L31" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="M31" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="N31" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="O31" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="P31" s="4" t="s">
         <v>243</v>
       </c>
     </row>
     <row r="32" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A32" s="5" t="s">
+      <c r="A32" s="7" t="s">
         <v>278</v>
       </c>
-      <c r="B32">
+      <c r="B32" s="4">
         <v>54</v>
       </c>
-      <c r="C32" t="s">
+      <c r="C32" s="4" t="s">
         <v>146</v>
       </c>
-      <c r="D32" t="s">
+      <c r="D32" s="4" t="s">
         <v>240</v>
       </c>
-      <c r="E32" s="7">
+      <c r="E32" s="8">
         <v>36758</v>
       </c>
-      <c r="F32">
-        <v>3</v>
-      </c>
-      <c r="G32">
+      <c r="F32" s="4">
+        <v>3</v>
+      </c>
+      <c r="G32" s="4">
         <v>1</v>
       </c>
-      <c r="H32">
+      <c r="H32" s="4">
         <v>1</v>
       </c>
-      <c r="I32">
+      <c r="I32" s="4">
         <v>48</v>
       </c>
-      <c r="J32" t="s">
-        <v>241</v>
-      </c>
-      <c r="K32" t="s">
+      <c r="J32" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="K32" s="4" t="s">
         <v>242</v>
       </c>
-      <c r="L32" t="s">
-        <v>243</v>
-      </c>
-      <c r="M32" t="s">
+      <c r="L32" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="M32" s="4" t="s">
         <v>242</v>
       </c>
-      <c r="N32" t="s">
+      <c r="N32" s="4" t="s">
         <v>242</v>
       </c>
-      <c r="O32" t="s">
+      <c r="O32" s="4" t="s">
         <v>242</v>
       </c>
-      <c r="P32" t="s">
+      <c r="P32" s="4" t="s">
         <v>242</v>
       </c>
     </row>
     <row r="33" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A33" s="5" t="s">
+      <c r="A33" s="7" t="s">
         <v>279</v>
       </c>
-      <c r="B33">
+      <c r="B33" s="4">
         <v>50</v>
       </c>
-      <c r="C33" t="s">
+      <c r="C33" s="4" t="s">
         <v>143</v>
       </c>
-      <c r="D33" t="s">
+      <c r="D33" s="4" t="s">
         <v>240</v>
       </c>
-      <c r="E33" s="7">
+      <c r="E33" s="8">
         <v>38062</v>
       </c>
-      <c r="F33">
+      <c r="F33" s="4">
         <v>2</v>
       </c>
-      <c r="G33">
+      <c r="G33" s="4">
         <v>2</v>
       </c>
-      <c r="H33">
+      <c r="H33" s="4">
         <v>1</v>
       </c>
-      <c r="I33">
+      <c r="I33" s="4">
         <v>680</v>
       </c>
-      <c r="J33" t="s">
-        <v>241</v>
-      </c>
-      <c r="K33" t="s">
-        <v>243</v>
-      </c>
-      <c r="L33" t="s">
+      <c r="J33" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="K33" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="L33" s="4" t="s">
         <v>242</v>
       </c>
-      <c r="M33" t="s">
-        <v>241</v>
-      </c>
-      <c r="N33" t="s">
-        <v>243</v>
-      </c>
-      <c r="O33" t="s">
-        <v>243</v>
-      </c>
-      <c r="P33" t="s">
+      <c r="M33" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="N33" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="O33" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="P33" s="4" t="s">
         <v>243</v>
       </c>
     </row>
     <row r="34" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A34" s="5" t="s">
+      <c r="A34" s="7" t="s">
         <v>280</v>
       </c>
-      <c r="B34">
+      <c r="B34" s="4">
         <v>27</v>
       </c>
-      <c r="C34" t="s">
+      <c r="C34" s="4" t="s">
         <v>143</v>
       </c>
-      <c r="D34" t="s">
+      <c r="D34" s="4" t="s">
         <v>246</v>
       </c>
-      <c r="E34" s="7">
+      <c r="E34" s="8">
         <v>37911</v>
       </c>
-      <c r="F34">
-        <v>3</v>
-      </c>
-      <c r="G34">
-        <v>3</v>
-      </c>
-      <c r="H34">
+      <c r="F34" s="4">
+        <v>3</v>
+      </c>
+      <c r="G34" s="4">
+        <v>3</v>
+      </c>
+      <c r="H34" s="4">
         <v>1</v>
       </c>
-      <c r="I34">
+      <c r="I34" s="4">
         <v>260</v>
       </c>
-      <c r="J34" t="s">
+      <c r="J34" s="4" t="s">
         <v>242</v>
       </c>
-      <c r="K34" t="s">
+      <c r="K34" s="4" t="s">
         <v>242</v>
       </c>
-      <c r="L34" t="s">
+      <c r="L34" s="4" t="s">
         <v>247</v>
       </c>
-      <c r="M34" t="s">
+      <c r="M34" s="4" t="s">
         <v>242</v>
       </c>
-      <c r="N34" t="s">
+      <c r="N34" s="4" t="s">
         <v>247</v>
       </c>
-      <c r="O34" t="s">
-        <v>241</v>
-      </c>
-      <c r="P34" t="s">
+      <c r="O34" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="P34" s="4" t="s">
         <v>243</v>
       </c>
     </row>
     <row r="35" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A35" s="5" t="s">
+      <c r="A35" s="7" t="s">
         <v>281</v>
       </c>
-      <c r="B35">
+      <c r="B35" s="4">
         <v>28</v>
       </c>
-      <c r="C35" t="s">
+      <c r="C35" s="4" t="s">
         <v>143</v>
       </c>
-      <c r="D35" t="s">
+      <c r="D35" s="4" t="s">
         <v>246</v>
       </c>
-      <c r="E35" s="7">
+      <c r="E35" s="8">
         <v>42927</v>
       </c>
-      <c r="F35">
-        <v>3</v>
-      </c>
-      <c r="G35">
-        <v>3</v>
-      </c>
-      <c r="H35">
+      <c r="F35" s="4">
+        <v>3</v>
+      </c>
+      <c r="G35" s="4">
+        <v>3</v>
+      </c>
+      <c r="H35" s="4">
         <v>1</v>
       </c>
-      <c r="I35">
+      <c r="I35" s="4">
         <v>180</v>
       </c>
-      <c r="J35" t="s">
-        <v>241</v>
-      </c>
-      <c r="K35" t="s">
-        <v>243</v>
-      </c>
-      <c r="L35" t="s">
+      <c r="J35" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="K35" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="L35" s="4" t="s">
         <v>242</v>
       </c>
-      <c r="M35" t="s">
-        <v>241</v>
-      </c>
-      <c r="N35" t="s">
-        <v>243</v>
-      </c>
-      <c r="O35" t="s">
-        <v>243</v>
-      </c>
-      <c r="P35" t="s">
+      <c r="M35" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="N35" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="O35" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="P35" s="4" t="s">
         <v>242</v>
       </c>
     </row>
     <row r="36" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A36" s="5" t="s">
+      <c r="A36" s="7" t="s">
         <v>282</v>
       </c>
-      <c r="B36">
+      <c r="B36" s="4">
         <v>24</v>
       </c>
-      <c r="C36" t="s">
+      <c r="C36" s="4" t="s">
         <v>143</v>
       </c>
-      <c r="D36" t="s">
+      <c r="D36" s="4" t="s">
         <v>250</v>
       </c>
-      <c r="E36" s="7">
+      <c r="E36" s="8">
         <v>41560</v>
       </c>
-      <c r="F36">
-        <v>3</v>
-      </c>
-      <c r="G36">
+      <c r="F36" s="4">
+        <v>3</v>
+      </c>
+      <c r="G36" s="4">
         <v>2</v>
       </c>
-      <c r="H36">
+      <c r="H36" s="4">
         <v>1</v>
       </c>
-      <c r="I36">
+      <c r="I36" s="4">
         <v>280</v>
       </c>
-      <c r="J36" t="s">
-        <v>241</v>
-      </c>
-      <c r="K36" t="s">
-        <v>243</v>
-      </c>
-      <c r="L36" t="s">
+      <c r="J36" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="K36" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="L36" s="4" t="s">
         <v>247</v>
       </c>
-      <c r="M36" t="s">
-        <v>243</v>
-      </c>
-      <c r="N36" t="s">
-        <v>243</v>
-      </c>
-      <c r="O36" t="s">
-        <v>241</v>
-      </c>
-      <c r="P36" t="s">
+      <c r="M36" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="N36" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="O36" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="P36" s="4" t="s">
         <v>242</v>
       </c>
     </row>
     <row r="37" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A37" s="5" t="s">
+      <c r="A37" s="7" t="s">
         <v>283</v>
       </c>
-      <c r="B37">
+      <c r="B37" s="4">
         <v>36</v>
       </c>
-      <c r="C37" t="s">
+      <c r="C37" s="4" t="s">
         <v>146</v>
       </c>
-      <c r="D37" t="s">
+      <c r="D37" s="4" t="s">
         <v>240</v>
       </c>
-      <c r="E37" s="7">
+      <c r="E37" s="8">
         <v>42886</v>
       </c>
-      <c r="F37">
-        <v>3</v>
-      </c>
-      <c r="G37">
+      <c r="F37" s="4">
+        <v>3</v>
+      </c>
+      <c r="G37" s="4">
         <v>2</v>
       </c>
-      <c r="H37">
+      <c r="H37" s="4">
         <v>1</v>
       </c>
-      <c r="I37">
+      <c r="I37" s="4">
         <v>50</v>
       </c>
-      <c r="J37" t="s">
-        <v>243</v>
-      </c>
-      <c r="K37" t="s">
-        <v>241</v>
-      </c>
-      <c r="L37" t="s">
-        <v>241</v>
-      </c>
-      <c r="M37" t="s">
-        <v>243</v>
-      </c>
-      <c r="N37" t="s">
-        <v>241</v>
-      </c>
-      <c r="O37" t="s">
+      <c r="J37" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="K37" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="L37" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="M37" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="N37" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="O37" s="4" t="s">
         <v>242</v>
       </c>
-      <c r="P37" t="s">
+      <c r="P37" s="4" t="s">
         <v>241</v>
       </c>
     </row>
     <row r="38" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A38" s="5" t="s">
+      <c r="A38" s="7" t="s">
         <v>284</v>
       </c>
-      <c r="B38">
+      <c r="B38" s="4">
         <v>29</v>
       </c>
-      <c r="C38" t="s">
+      <c r="C38" s="4" t="s">
         <v>146</v>
       </c>
-      <c r="D38" t="s">
+      <c r="D38" s="4" t="s">
         <v>253</v>
       </c>
-      <c r="E38" s="7">
+      <c r="E38" s="8">
         <v>39345</v>
       </c>
-      <c r="F38">
-        <v>3</v>
-      </c>
-      <c r="G38">
-        <v>3</v>
-      </c>
-      <c r="H38">
+      <c r="F38" s="4">
+        <v>3</v>
+      </c>
+      <c r="G38" s="4">
+        <v>3</v>
+      </c>
+      <c r="H38" s="4">
         <v>1</v>
       </c>
-      <c r="I38">
+      <c r="I38" s="4">
         <v>60</v>
       </c>
-      <c r="J38" t="s">
-        <v>241</v>
-      </c>
-      <c r="K38" t="s">
-        <v>241</v>
-      </c>
-      <c r="L38" t="s">
-        <v>243</v>
-      </c>
-      <c r="M38" t="s">
-        <v>243</v>
-      </c>
-      <c r="N38" t="s">
-        <v>241</v>
-      </c>
-      <c r="O38" t="s">
-        <v>241</v>
-      </c>
-      <c r="P38" t="s">
+      <c r="J38" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="K38" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="L38" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="M38" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="N38" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="O38" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="P38" s="4" t="s">
         <v>241</v>
       </c>
     </row>
     <row r="39" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A39" s="5" t="s">
+      <c r="A39" s="7" t="s">
         <v>285</v>
       </c>
-      <c r="B39">
+      <c r="B39" s="4">
         <v>53</v>
       </c>
-      <c r="C39" t="s">
+      <c r="C39" s="4" t="s">
         <v>143</v>
       </c>
-      <c r="D39" t="s">
+      <c r="D39" s="4" t="s">
         <v>240</v>
       </c>
-      <c r="E39" s="7">
+      <c r="E39" s="8">
         <v>39725</v>
       </c>
-      <c r="F39">
-        <v>3</v>
-      </c>
-      <c r="G39">
+      <c r="F39" s="4">
+        <v>3</v>
+      </c>
+      <c r="G39" s="4">
         <v>1</v>
       </c>
-      <c r="H39">
+      <c r="H39" s="4">
         <v>2</v>
       </c>
-      <c r="I39">
+      <c r="I39" s="4">
         <v>870</v>
       </c>
-      <c r="J39" t="s">
-        <v>241</v>
-      </c>
-      <c r="K39" t="s">
-        <v>243</v>
-      </c>
-      <c r="L39" t="s">
-        <v>241</v>
-      </c>
-      <c r="M39" t="s">
-        <v>243</v>
-      </c>
-      <c r="N39" t="s">
-        <v>243</v>
-      </c>
-      <c r="O39" t="s">
-        <v>241</v>
-      </c>
-      <c r="P39" t="s">
+      <c r="J39" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="K39" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="L39" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="M39" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="N39" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="O39" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="P39" s="4" t="s">
         <v>243</v>
       </c>
     </row>
     <row r="40" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A40" s="5" t="s">
+      <c r="A40" s="7" t="s">
         <v>286</v>
       </c>
-      <c r="B40">
+      <c r="B40" s="4">
         <v>32</v>
       </c>
-      <c r="C40" t="s">
+      <c r="C40" s="4" t="s">
         <v>143</v>
       </c>
-      <c r="D40" s="6" t="s">
+      <c r="D40" s="9" t="s">
         <v>253</v>
       </c>
-      <c r="E40" s="7">
+      <c r="E40" s="8">
         <v>41797</v>
       </c>
-      <c r="F40">
-        <v>3</v>
-      </c>
-      <c r="G40">
+      <c r="F40" s="4">
+        <v>3</v>
+      </c>
+      <c r="G40" s="4">
         <v>2</v>
       </c>
-      <c r="H40">
+      <c r="H40" s="4">
         <v>2</v>
       </c>
-      <c r="I40">
+      <c r="I40" s="4">
         <v>120</v>
       </c>
-      <c r="J40" t="s">
-        <v>241</v>
-      </c>
-      <c r="K40" t="s">
-        <v>241</v>
-      </c>
-      <c r="L40" t="s">
-        <v>243</v>
-      </c>
-      <c r="M40" t="s">
-        <v>241</v>
-      </c>
-      <c r="N40" t="s">
-        <v>243</v>
-      </c>
-      <c r="O40" t="s">
-        <v>241</v>
-      </c>
-      <c r="P40" t="s">
+      <c r="J40" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="K40" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="L40" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="M40" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="N40" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="O40" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="P40" s="4" t="s">
         <v>243</v>
       </c>
     </row>
     <row r="41" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A41" s="5" t="s">
+      <c r="A41" s="7" t="s">
         <v>287</v>
       </c>
-      <c r="B41">
+      <c r="B41" s="4">
         <v>48</v>
       </c>
-      <c r="C41" t="s">
+      <c r="C41" s="4" t="s">
         <v>146</v>
       </c>
-      <c r="D41" s="6" t="s">
+      <c r="D41" s="9" t="s">
         <v>246</v>
       </c>
-      <c r="E41" s="7">
+      <c r="E41" s="8">
         <v>42064</v>
       </c>
-      <c r="F41">
-        <v>3</v>
-      </c>
-      <c r="G41">
-        <v>3</v>
-      </c>
-      <c r="H41">
+      <c r="F41" s="4">
+        <v>3</v>
+      </c>
+      <c r="G41" s="4">
+        <v>3</v>
+      </c>
+      <c r="H41" s="4">
         <v>1</v>
       </c>
-      <c r="I41">
+      <c r="I41" s="4">
         <v>100</v>
       </c>
-      <c r="J41" t="s">
-        <v>243</v>
-      </c>
-      <c r="K41" t="s">
-        <v>241</v>
-      </c>
-      <c r="L41" t="s">
-        <v>241</v>
-      </c>
-      <c r="M41" t="s">
-        <v>243</v>
-      </c>
-      <c r="N41" t="s">
-        <v>241</v>
-      </c>
-      <c r="O41" t="s">
-        <v>241</v>
-      </c>
-      <c r="P41" t="s">
+      <c r="J41" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="K41" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="L41" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="M41" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="N41" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="O41" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="P41" s="4" t="s">
         <v>241</v>
       </c>
     </row>
     <row r="42" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A42" s="5" t="s">
+      <c r="A42" s="7" t="s">
         <v>288</v>
       </c>
-      <c r="B42">
+      <c r="B42" s="4">
         <v>20</v>
       </c>
-      <c r="C42" t="s">
+      <c r="C42" s="4" t="s">
         <v>146</v>
       </c>
-      <c r="D42" s="6" t="s">
+      <c r="D42" s="9" t="s">
         <v>253</v>
       </c>
-      <c r="E42" s="7">
+      <c r="E42" s="8">
         <v>36758</v>
       </c>
-      <c r="F42">
-        <v>3</v>
-      </c>
-      <c r="G42">
+      <c r="F42" s="4">
+        <v>3</v>
+      </c>
+      <c r="G42" s="4">
         <v>2</v>
       </c>
-      <c r="H42">
+      <c r="H42" s="4">
         <v>1</v>
       </c>
-      <c r="I42">
+      <c r="I42" s="4">
         <v>120</v>
       </c>
-      <c r="J42" t="s">
-        <v>241</v>
-      </c>
-      <c r="K42" t="s">
-        <v>243</v>
-      </c>
-      <c r="L42" t="s">
-        <v>243</v>
-      </c>
-      <c r="M42" t="s">
-        <v>243</v>
-      </c>
-      <c r="N42" t="s">
-        <v>241</v>
-      </c>
-      <c r="O42" t="s">
-        <v>241</v>
-      </c>
-      <c r="P42" t="s">
+      <c r="J42" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="K42" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="L42" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="M42" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="N42" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="O42" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="P42" s="4" t="s">
         <v>241</v>
       </c>
     </row>
     <row r="43" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A43" s="5" t="s">
+      <c r="A43" s="7" t="s">
         <v>289</v>
       </c>
-      <c r="B43">
+      <c r="B43" s="4">
         <v>33</v>
       </c>
-      <c r="C43" t="s">
+      <c r="C43" s="4" t="s">
         <v>146</v>
       </c>
-      <c r="D43" s="6" t="s">
+      <c r="D43" s="9" t="s">
         <v>246</v>
       </c>
-      <c r="E43" s="7">
+      <c r="E43" s="8">
         <v>38062</v>
       </c>
-      <c r="F43">
-        <v>3</v>
-      </c>
-      <c r="G43">
+      <c r="F43" s="4">
+        <v>3</v>
+      </c>
+      <c r="G43" s="4">
         <v>2</v>
       </c>
-      <c r="H43">
+      <c r="H43" s="4">
         <v>1</v>
       </c>
-      <c r="I43">
+      <c r="I43" s="4">
         <v>150</v>
       </c>
-      <c r="J43" t="s">
-        <v>241</v>
-      </c>
-      <c r="K43" t="s">
-        <v>241</v>
-      </c>
-      <c r="L43" t="s">
-        <v>243</v>
-      </c>
-      <c r="M43" t="s">
-        <v>243</v>
-      </c>
-      <c r="N43" t="s">
-        <v>243</v>
-      </c>
-      <c r="O43" t="s">
-        <v>241</v>
-      </c>
-      <c r="P43" t="s">
+      <c r="J43" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="K43" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="L43" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="M43" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="N43" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="O43" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="P43" s="4" t="s">
         <v>241</v>
       </c>
     </row>
     <row r="44" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A44" s="5" t="s">
+      <c r="A44" s="7" t="s">
         <v>290</v>
       </c>
-      <c r="B44">
+      <c r="B44" s="4">
         <v>23</v>
       </c>
-      <c r="C44" t="s">
+      <c r="C44" s="4" t="s">
         <v>143</v>
       </c>
-      <c r="D44" s="6" t="s">
+      <c r="D44" s="9" t="s">
         <v>253</v>
       </c>
-      <c r="E44" s="7">
+      <c r="E44" s="8">
         <v>37911</v>
       </c>
-      <c r="F44">
-        <v>3</v>
-      </c>
-      <c r="G44">
-        <v>3</v>
-      </c>
-      <c r="H44">
+      <c r="F44" s="4">
+        <v>3</v>
+      </c>
+      <c r="G44" s="4">
+        <v>3</v>
+      </c>
+      <c r="H44" s="4">
         <v>1</v>
       </c>
-      <c r="I44">
+      <c r="I44" s="4">
         <v>100</v>
       </c>
-      <c r="J44" t="s">
-        <v>241</v>
-      </c>
-      <c r="K44" t="s">
-        <v>243</v>
-      </c>
-      <c r="L44" t="s">
-        <v>241</v>
-      </c>
-      <c r="M44" t="s">
-        <v>243</v>
-      </c>
-      <c r="N44" t="s">
-        <v>243</v>
-      </c>
-      <c r="O44" t="s">
-        <v>241</v>
-      </c>
-      <c r="P44" t="s">
+      <c r="J44" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="K44" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="L44" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="M44" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="N44" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="O44" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="P44" s="4" t="s">
         <v>241</v>
       </c>
     </row>
     <row r="45" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A45" s="5" t="s">
+      <c r="A45" s="7" t="s">
         <v>291</v>
       </c>
-      <c r="B45">
+      <c r="B45" s="4">
         <v>40</v>
       </c>
-      <c r="C45" t="s">
+      <c r="C45" s="4" t="s">
         <v>143</v>
       </c>
-      <c r="D45" s="6" t="s">
+      <c r="D45" s="9" t="s">
         <v>253</v>
       </c>
-      <c r="E45" s="7">
+      <c r="E45" s="8">
         <v>42927</v>
       </c>
-      <c r="F45">
-        <v>3</v>
-      </c>
-      <c r="G45">
+      <c r="F45" s="4">
+        <v>3</v>
+      </c>
+      <c r="G45" s="4">
         <v>1</v>
       </c>
-      <c r="H45">
+      <c r="H45" s="4">
         <v>1</v>
       </c>
-      <c r="I45">
+      <c r="I45" s="4">
         <v>280</v>
       </c>
-      <c r="J45" t="s">
-        <v>241</v>
-      </c>
-      <c r="K45" t="s">
-        <v>243</v>
-      </c>
-      <c r="L45" t="s">
-        <v>241</v>
-      </c>
-      <c r="M45" t="s">
-        <v>241</v>
-      </c>
-      <c r="N45" t="s">
-        <v>243</v>
-      </c>
-      <c r="O45" t="s">
-        <v>241</v>
-      </c>
-      <c r="P45" t="s">
+      <c r="J45" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="K45" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="L45" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="M45" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="N45" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="O45" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="P45" s="4" t="s">
         <v>243</v>
       </c>
     </row>
     <row r="46" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A46" s="5" t="s">
+      <c r="A46" s="7" t="s">
         <v>292</v>
       </c>
-      <c r="B46">
+      <c r="B46" s="4">
         <v>42</v>
       </c>
-      <c r="C46" t="s">
+      <c r="C46" s="4" t="s">
         <v>146</v>
       </c>
-      <c r="D46" t="s">
+      <c r="D46" s="4" t="s">
         <v>240</v>
       </c>
-      <c r="E46" s="7">
+      <c r="E46" s="8">
         <v>41560</v>
       </c>
-      <c r="F46">
-        <v>3</v>
-      </c>
-      <c r="G46">
+      <c r="F46" s="4">
+        <v>3</v>
+      </c>
+      <c r="G46" s="4">
         <v>1</v>
       </c>
-      <c r="H46">
+      <c r="H46" s="4">
         <v>1</v>
       </c>
-      <c r="I46">
+      <c r="I46" s="4">
         <v>200</v>
       </c>
-      <c r="J46" t="s">
-        <v>241</v>
-      </c>
-      <c r="K46" t="s">
-        <v>243</v>
-      </c>
-      <c r="L46" t="s">
+      <c r="J46" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="K46" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="L46" s="4" t="s">
         <v>242</v>
       </c>
-      <c r="M46" t="s">
-        <v>243</v>
-      </c>
-      <c r="N46" t="s">
-        <v>243</v>
-      </c>
-      <c r="O46" t="s">
+      <c r="M46" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="N46" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="O46" s="4" t="s">
         <v>242</v>
       </c>
-      <c r="P46" t="s">
+      <c r="P46" s="4" t="s">
         <v>242</v>
       </c>
     </row>
     <row r="47" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A47" s="5" t="s">
+      <c r="A47" s="7" t="s">
         <v>293</v>
       </c>
-      <c r="B47">
+      <c r="B47" s="4">
         <v>46</v>
       </c>
-      <c r="C47" t="s">
+      <c r="C47" s="4" t="s">
         <v>143</v>
       </c>
-      <c r="D47" t="s">
+      <c r="D47" s="4" t="s">
         <v>246</v>
       </c>
-      <c r="E47" s="7">
+      <c r="E47" s="8">
         <v>42886</v>
       </c>
-      <c r="F47">
+      <c r="F47" s="4">
         <v>2</v>
       </c>
-      <c r="G47">
+      <c r="G47" s="4">
         <v>2</v>
       </c>
-      <c r="H47">
+      <c r="H47" s="4">
         <v>1</v>
       </c>
-      <c r="I47">
+      <c r="I47" s="4">
         <v>380</v>
       </c>
-      <c r="J47" t="s">
-        <v>241</v>
-      </c>
-      <c r="K47" t="s">
-        <v>243</v>
-      </c>
-      <c r="L47" t="s">
+      <c r="J47" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="K47" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="L47" s="4" t="s">
         <v>242</v>
       </c>
-      <c r="M47" t="s">
-        <v>241</v>
-      </c>
-      <c r="N47" t="s">
-        <v>243</v>
-      </c>
-      <c r="O47" t="s">
-        <v>241</v>
-      </c>
-      <c r="P47" t="s">
+      <c r="M47" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="N47" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="O47" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="P47" s="4" t="s">
         <v>243</v>
       </c>
     </row>
     <row r="48" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A48" s="5" t="s">
+      <c r="A48" s="7" t="s">
         <v>294</v>
       </c>
-      <c r="B48">
+      <c r="B48" s="4">
         <v>27</v>
       </c>
-      <c r="C48" t="s">
+      <c r="C48" s="4" t="s">
         <v>146</v>
       </c>
-      <c r="D48" t="s">
+      <c r="D48" s="4" t="s">
         <v>250</v>
       </c>
-      <c r="E48" s="7">
+      <c r="E48" s="8">
         <v>39345</v>
       </c>
-      <c r="F48">
-        <v>3</v>
-      </c>
-      <c r="G48">
+      <c r="F48" s="4">
+        <v>3</v>
+      </c>
+      <c r="G48" s="4">
         <v>2</v>
       </c>
-      <c r="H48">
+      <c r="H48" s="4">
         <v>1</v>
       </c>
-      <c r="I48">
+      <c r="I48" s="4">
         <v>210</v>
       </c>
-      <c r="J48" t="s">
+      <c r="J48" s="4" t="s">
         <v>242</v>
       </c>
-      <c r="K48" t="s">
-        <v>243</v>
-      </c>
-      <c r="L48" t="s">
-        <v>241</v>
-      </c>
-      <c r="M48" t="s">
-        <v>243</v>
-      </c>
-      <c r="N48" t="s">
+      <c r="K48" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="L48" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="M48" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="N48" s="4" t="s">
         <v>247</v>
       </c>
-      <c r="O48" t="s">
-        <v>241</v>
-      </c>
-      <c r="P48" t="s">
+      <c r="O48" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="P48" s="4" t="s">
         <v>242</v>
       </c>
     </row>
     <row r="49" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A49" s="5" t="s">
+      <c r="A49" s="7" t="s">
         <v>294</v>
       </c>
-      <c r="B49">
+      <c r="B49" s="4">
         <v>33</v>
       </c>
-      <c r="C49" t="s">
+      <c r="C49" s="4" t="s">
         <v>146</v>
       </c>
-      <c r="D49" t="s">
+      <c r="D49" s="4" t="s">
         <v>246</v>
       </c>
-      <c r="E49" s="7">
+      <c r="E49" s="8">
         <v>39725</v>
       </c>
-      <c r="F49">
-        <v>3</v>
-      </c>
-      <c r="G49">
+      <c r="F49" s="4">
+        <v>3</v>
+      </c>
+      <c r="G49" s="4">
         <v>2</v>
       </c>
-      <c r="H49">
+      <c r="H49" s="4">
         <v>1</v>
       </c>
-      <c r="I49">
+      <c r="I49" s="4">
         <v>48</v>
       </c>
-      <c r="J49" t="s">
-        <v>241</v>
-      </c>
-      <c r="K49" t="s">
+      <c r="J49" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="K49" s="4" t="s">
         <v>242</v>
       </c>
-      <c r="L49" t="s">
-        <v>243</v>
-      </c>
-      <c r="M49" t="s">
-        <v>241</v>
-      </c>
-      <c r="N49" t="s">
+      <c r="L49" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="M49" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="N49" s="4" t="s">
         <v>242</v>
       </c>
-      <c r="O49" t="s">
+      <c r="O49" s="4" t="s">
         <v>242</v>
       </c>
-      <c r="P49" t="s">
+      <c r="P49" s="4" t="s">
         <v>242</v>
       </c>
     </row>
     <row r="50" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A50" s="5" t="s">
+      <c r="A50" s="7" t="s">
         <v>295</v>
       </c>
-      <c r="B50">
+      <c r="B50" s="4">
         <v>18</v>
       </c>
-      <c r="C50" t="s">
+      <c r="C50" s="4" t="s">
         <v>143</v>
       </c>
-      <c r="D50" t="s">
+      <c r="D50" s="4" t="s">
         <v>250</v>
       </c>
-      <c r="E50" s="7">
+      <c r="E50" s="8">
         <v>41797</v>
       </c>
-      <c r="F50">
-        <v>3</v>
-      </c>
-      <c r="G50">
+      <c r="F50" s="4">
+        <v>3</v>
+      </c>
+      <c r="G50" s="4">
         <v>2</v>
       </c>
-      <c r="H50">
+      <c r="H50" s="4">
         <v>1</v>
       </c>
-      <c r="I50">
+      <c r="I50" s="4">
         <v>160</v>
       </c>
-      <c r="J50" t="s">
-        <v>241</v>
-      </c>
-      <c r="K50" t="s">
-        <v>243</v>
-      </c>
-      <c r="L50" t="s">
-        <v>241</v>
-      </c>
-      <c r="M50" t="s">
-        <v>241</v>
-      </c>
-      <c r="N50" t="s">
-        <v>243</v>
-      </c>
-      <c r="O50" t="s">
-        <v>243</v>
-      </c>
-      <c r="P50" t="s">
+      <c r="J50" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="K50" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="L50" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="M50" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="N50" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="O50" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="P50" s="4" t="s">
         <v>242</v>
       </c>
     </row>
     <row r="51" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A51" s="5" t="s">
+      <c r="A51" s="7" t="s">
         <v>296</v>
       </c>
-      <c r="B51">
+      <c r="B51" s="4">
         <v>35</v>
       </c>
-      <c r="C51" t="s">
+      <c r="C51" s="4" t="s">
         <v>146</v>
       </c>
-      <c r="D51" t="s">
+      <c r="D51" s="4" t="s">
         <v>240</v>
       </c>
-      <c r="E51" s="7">
+      <c r="E51" s="8">
         <v>42064</v>
       </c>
-      <c r="F51">
-        <v>3</v>
-      </c>
-      <c r="G51">
+      <c r="F51" s="4">
+        <v>3</v>
+      </c>
+      <c r="G51" s="4">
         <v>2</v>
       </c>
-      <c r="H51">
+      <c r="H51" s="4">
         <v>1</v>
       </c>
-      <c r="I51">
+      <c r="I51" s="4">
         <v>48</v>
       </c>
-      <c r="J51" t="s">
-        <v>241</v>
-      </c>
-      <c r="K51" t="s">
+      <c r="J51" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="K51" s="4" t="s">
         <v>242</v>
       </c>
-      <c r="L51" t="s">
-        <v>243</v>
-      </c>
-      <c r="M51" t="s">
-        <v>241</v>
-      </c>
-      <c r="N51" t="s">
+      <c r="L51" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="M51" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="N51" s="4" t="s">
         <v>242</v>
       </c>
-      <c r="O51" t="s">
+      <c r="O51" s="4" t="s">
         <v>242</v>
       </c>
-      <c r="P51" t="s">
+      <c r="P51" s="4" t="s">
         <v>241</v>
       </c>
     </row>
     <row r="52" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A52" s="5" t="s">
+      <c r="A52" s="7" t="s">
         <v>297</v>
       </c>
-      <c r="B52">
+      <c r="B52" s="4">
         <v>17</v>
       </c>
-      <c r="C52" t="s">
+      <c r="C52" s="4" t="s">
         <v>146</v>
       </c>
-      <c r="D52" t="s">
+      <c r="D52" s="4" t="s">
         <v>253</v>
       </c>
-      <c r="E52" s="7">
+      <c r="E52" s="8">
         <v>36758</v>
       </c>
-      <c r="F52">
-        <v>3</v>
-      </c>
-      <c r="G52">
+      <c r="F52" s="4">
+        <v>3</v>
+      </c>
+      <c r="G52" s="4">
         <v>1</v>
       </c>
-      <c r="H52">
+      <c r="H52" s="4">
         <v>1</v>
       </c>
-      <c r="I52">
+      <c r="I52" s="4">
         <v>48</v>
       </c>
-      <c r="J52" t="s">
-        <v>241</v>
-      </c>
-      <c r="K52" t="s">
-        <v>241</v>
-      </c>
-      <c r="L52" t="s">
-        <v>243</v>
-      </c>
-      <c r="M52" t="s">
-        <v>241</v>
-      </c>
-      <c r="N52" t="s">
-        <v>241</v>
-      </c>
-      <c r="O52" t="s">
-        <v>241</v>
-      </c>
-      <c r="P52" t="s">
+      <c r="J52" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="K52" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="L52" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="M52" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="N52" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="O52" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="P52" s="4" t="s">
         <v>241</v>
       </c>
     </row>
     <row r="53" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A53" s="5" t="s">
+      <c r="A53" s="7" t="s">
         <v>298</v>
       </c>
-      <c r="B53">
+      <c r="B53" s="4">
         <v>50</v>
       </c>
-      <c r="C53" t="s">
+      <c r="C53" s="4" t="s">
         <v>146</v>
       </c>
-      <c r="D53" t="s">
+      <c r="D53" s="4" t="s">
         <v>240</v>
       </c>
-      <c r="E53" s="7">
+      <c r="E53" s="8">
         <v>38062</v>
       </c>
-      <c r="F53">
-        <v>3</v>
-      </c>
-      <c r="G53">
+      <c r="F53" s="4">
+        <v>3</v>
+      </c>
+      <c r="G53" s="4">
         <v>1</v>
       </c>
-      <c r="H53">
+      <c r="H53" s="4">
         <v>1</v>
       </c>
-      <c r="I53">
+      <c r="I53" s="4">
         <v>48</v>
       </c>
-      <c r="J53" t="s">
-        <v>241</v>
-      </c>
-      <c r="K53" t="s">
-        <v>241</v>
-      </c>
-      <c r="L53" t="s">
-        <v>243</v>
-      </c>
-      <c r="M53" t="s">
-        <v>241</v>
-      </c>
-      <c r="N53" t="s">
-        <v>241</v>
-      </c>
-      <c r="O53" t="s">
-        <v>241</v>
-      </c>
-      <c r="P53" t="s">
+      <c r="J53" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="K53" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="L53" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="M53" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="N53" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="O53" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="P53" s="4" t="s">
         <v>241</v>
       </c>
     </row>
     <row r="54" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A54" s="5" t="s">
+      <c r="A54" s="7" t="s">
         <v>299</v>
       </c>
-      <c r="B54">
+      <c r="B54" s="4">
         <v>35</v>
       </c>
-      <c r="C54" t="s">
+      <c r="C54" s="4" t="s">
         <v>143</v>
       </c>
-      <c r="D54" s="6" t="s">
+      <c r="D54" s="9" t="s">
         <v>240</v>
       </c>
-      <c r="E54" s="7">
+      <c r="E54" s="8">
         <v>37911</v>
       </c>
-      <c r="F54">
-        <v>3</v>
-      </c>
-      <c r="G54">
+      <c r="F54" s="4">
+        <v>3</v>
+      </c>
+      <c r="G54" s="4">
         <v>1</v>
       </c>
-      <c r="H54">
+      <c r="H54" s="4">
         <v>1</v>
       </c>
-      <c r="I54">
+      <c r="I54" s="4">
         <v>280</v>
       </c>
-      <c r="J54" t="s">
-        <v>241</v>
-      </c>
-      <c r="K54" t="s">
-        <v>243</v>
-      </c>
-      <c r="L54" t="s">
-        <v>241</v>
-      </c>
-      <c r="M54" t="s">
-        <v>241</v>
-      </c>
-      <c r="N54" t="s">
-        <v>243</v>
-      </c>
-      <c r="O54" t="s">
-        <v>241</v>
-      </c>
-      <c r="P54" t="s">
+      <c r="J54" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="K54" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="L54" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="M54" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="N54" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="O54" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="P54" s="4" t="s">
         <v>243</v>
       </c>
     </row>
     <row r="55" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A55" s="5" t="s">
+      <c r="A55" s="7" t="s">
         <v>300</v>
       </c>
-      <c r="B55">
+      <c r="B55" s="4">
         <v>19</v>
       </c>
-      <c r="C55" t="s">
+      <c r="C55" s="4" t="s">
         <v>146</v>
       </c>
-      <c r="D55" s="6" t="s">
+      <c r="D55" s="9" t="s">
         <v>253</v>
       </c>
-      <c r="E55" s="7">
+      <c r="E55" s="8">
         <v>42927</v>
       </c>
-      <c r="F55">
-        <v>3</v>
-      </c>
-      <c r="G55">
+      <c r="F55" s="4">
+        <v>3</v>
+      </c>
+      <c r="G55" s="4">
         <v>2</v>
       </c>
-      <c r="H55">
+      <c r="H55" s="4">
         <v>1</v>
       </c>
-      <c r="I55">
+      <c r="I55" s="4">
         <v>68</v>
       </c>
-      <c r="J55" t="s">
-        <v>241</v>
-      </c>
-      <c r="K55" t="s">
-        <v>241</v>
-      </c>
-      <c r="L55" t="s">
-        <v>243</v>
-      </c>
-      <c r="M55" t="s">
-        <v>243</v>
-      </c>
-      <c r="N55" t="s">
-        <v>241</v>
-      </c>
-      <c r="O55" t="s">
-        <v>241</v>
-      </c>
-      <c r="P55" t="s">
+      <c r="J55" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="K55" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="L55" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="M55" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="N55" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="O55" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="P55" s="4" t="s">
         <v>241</v>
       </c>
     </row>
     <row r="56" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A56" s="5" t="s">
+      <c r="A56" s="7" t="s">
         <v>301</v>
       </c>
-      <c r="B56">
+      <c r="B56" s="4">
         <v>20</v>
       </c>
-      <c r="C56" t="s">
+      <c r="C56" s="4" t="s">
         <v>146</v>
       </c>
-      <c r="D56" s="6" t="s">
+      <c r="D56" s="9" t="s">
         <v>253</v>
       </c>
-      <c r="E56" s="7">
+      <c r="E56" s="8">
         <v>41560</v>
       </c>
-      <c r="F56">
-        <v>3</v>
-      </c>
-      <c r="G56">
+      <c r="F56" s="4">
+        <v>3</v>
+      </c>
+      <c r="G56" s="4">
         <v>1</v>
       </c>
-      <c r="H56">
+      <c r="H56" s="4">
         <v>1</v>
       </c>
-      <c r="I56">
+      <c r="I56" s="4">
         <v>100</v>
       </c>
-      <c r="J56" t="s">
-        <v>241</v>
-      </c>
-      <c r="K56" t="s">
-        <v>243</v>
-      </c>
-      <c r="L56" t="s">
-        <v>241</v>
-      </c>
-      <c r="M56" t="s">
-        <v>243</v>
-      </c>
-      <c r="N56" t="s">
-        <v>241</v>
-      </c>
-      <c r="O56" t="s">
-        <v>241</v>
-      </c>
-      <c r="P56" t="s">
+      <c r="J56" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="K56" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="L56" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="M56" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="N56" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="O56" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="P56" s="4" t="s">
         <v>241</v>
       </c>
     </row>
     <row r="57" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A57" s="5" t="s">
+      <c r="A57" s="7" t="s">
         <v>302</v>
       </c>
-      <c r="B57">
+      <c r="B57" s="4">
         <v>33</v>
       </c>
-      <c r="C57" t="s">
+      <c r="C57" s="4" t="s">
         <v>143</v>
       </c>
-      <c r="D57" s="6" t="s">
+      <c r="D57" s="9" t="s">
         <v>253</v>
       </c>
-      <c r="E57" s="7">
+      <c r="E57" s="8">
         <v>42886</v>
       </c>
-      <c r="F57">
-        <v>3</v>
-      </c>
-      <c r="G57">
+      <c r="F57" s="4">
+        <v>3</v>
+      </c>
+      <c r="G57" s="4">
         <v>1</v>
       </c>
-      <c r="H57">
+      <c r="H57" s="4">
         <v>1</v>
       </c>
-      <c r="I57">
+      <c r="I57" s="4">
         <v>100</v>
       </c>
-      <c r="J57" t="s">
-        <v>241</v>
-      </c>
-      <c r="K57" t="s">
-        <v>243</v>
-      </c>
-      <c r="L57" t="s">
-        <v>241</v>
-      </c>
-      <c r="M57" t="s">
+      <c r="J57" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="K57" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="L57" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="M57" s="4" t="s">
         <v>273</v>
       </c>
-      <c r="N57" t="s">
-        <v>243</v>
-      </c>
-      <c r="O57" t="s">
-        <v>243</v>
-      </c>
-      <c r="P57" t="s">
+      <c r="N57" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="O57" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="P57" s="4" t="s">
         <v>241</v>
       </c>
     </row>
     <row r="58" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A58" s="5" t="s">
+      <c r="A58" s="7" t="s">
         <v>303</v>
       </c>
-      <c r="B58">
+      <c r="B58" s="4">
         <v>23</v>
       </c>
-      <c r="C58" t="s">
+      <c r="C58" s="4" t="s">
         <v>143</v>
       </c>
-      <c r="D58" s="6" t="s">
+      <c r="D58" s="9" t="s">
         <v>253</v>
       </c>
-      <c r="E58" s="7">
+      <c r="E58" s="8">
         <v>39345</v>
       </c>
-      <c r="F58">
-        <v>3</v>
-      </c>
-      <c r="G58">
+      <c r="F58" s="4">
+        <v>3</v>
+      </c>
+      <c r="G58" s="4">
         <v>1</v>
       </c>
-      <c r="H58">
+      <c r="H58" s="4">
         <v>1</v>
       </c>
-      <c r="I58">
+      <c r="I58" s="4">
         <v>80</v>
       </c>
-      <c r="J58" t="s">
-        <v>241</v>
-      </c>
-      <c r="K58" t="s">
-        <v>241</v>
-      </c>
-      <c r="L58" t="s">
-        <v>243</v>
-      </c>
-      <c r="M58" t="s">
-        <v>241</v>
-      </c>
-      <c r="N58" t="s">
-        <v>243</v>
-      </c>
-      <c r="O58" t="s">
-        <v>243</v>
-      </c>
-      <c r="P58" t="s">
+      <c r="J58" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="K58" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="L58" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="M58" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="N58" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="O58" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="P58" s="4" t="s">
         <v>241</v>
       </c>
     </row>
     <row r="59" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A59" s="5" t="s">
+      <c r="A59" s="7" t="s">
         <v>304</v>
       </c>
-      <c r="B59">
+      <c r="B59" s="4">
         <v>50</v>
       </c>
-      <c r="C59" t="s">
+      <c r="C59" s="4" t="s">
         <v>146</v>
       </c>
-      <c r="D59" s="6" t="s">
+      <c r="D59" s="9" t="s">
         <v>240</v>
       </c>
-      <c r="E59" s="7">
+      <c r="E59" s="8">
         <v>39725</v>
       </c>
-      <c r="F59">
-        <v>3</v>
-      </c>
-      <c r="G59">
+      <c r="F59" s="4">
+        <v>3</v>
+      </c>
+      <c r="G59" s="4">
         <v>1</v>
       </c>
-      <c r="H59">
+      <c r="H59" s="4">
         <v>1</v>
       </c>
-      <c r="I59">
+      <c r="I59" s="4">
         <v>212</v>
       </c>
-      <c r="J59" t="s">
-        <v>241</v>
-      </c>
-      <c r="K59" t="s">
-        <v>243</v>
-      </c>
-      <c r="L59" t="s">
-        <v>241</v>
-      </c>
-      <c r="M59" t="s">
-        <v>243</v>
-      </c>
-      <c r="N59" t="s">
-        <v>243</v>
-      </c>
-      <c r="O59" t="s">
-        <v>243</v>
-      </c>
-      <c r="P59" t="s">
+      <c r="J59" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="K59" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="L59" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="M59" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="N59" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="O59" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="P59" s="4" t="s">
         <v>241</v>
       </c>
     </row>
     <row r="60" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A60" s="5" t="s">
+      <c r="A60" s="7" t="s">
         <v>305</v>
       </c>
-      <c r="B60">
+      <c r="B60" s="4">
         <v>37</v>
       </c>
-      <c r="C60" t="s">
+      <c r="C60" s="4" t="s">
         <v>143</v>
       </c>
-      <c r="D60" s="6" t="s">
+      <c r="D60" s="9" t="s">
         <v>240</v>
       </c>
-      <c r="E60" s="7">
+      <c r="E60" s="8">
         <v>41797</v>
       </c>
-      <c r="F60">
-        <v>3</v>
-      </c>
-      <c r="G60">
+      <c r="F60" s="4">
+        <v>3</v>
+      </c>
+      <c r="G60" s="4">
         <v>2</v>
       </c>
-      <c r="H60">
+      <c r="H60" s="4">
         <v>1</v>
       </c>
-      <c r="I60">
+      <c r="I60" s="4">
         <v>280</v>
       </c>
-      <c r="J60" t="s">
-        <v>241</v>
-      </c>
-      <c r="K60" t="s">
-        <v>243</v>
-      </c>
-      <c r="L60" t="s">
-        <v>241</v>
-      </c>
-      <c r="M60" t="s">
-        <v>241</v>
-      </c>
-      <c r="N60" t="s">
-        <v>243</v>
-      </c>
-      <c r="O60" t="s">
-        <v>241</v>
-      </c>
-      <c r="P60" t="s">
+      <c r="J60" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="K60" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="L60" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="M60" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="N60" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="O60" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="P60" s="4" t="s">
         <v>243</v>
       </c>
     </row>
     <row r="61" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A61" s="5" t="s">
+      <c r="A61" s="7" t="s">
         <v>306</v>
       </c>
-      <c r="B61">
+      <c r="B61" s="4">
         <v>48</v>
       </c>
-      <c r="C61" t="s">
+      <c r="C61" s="4" t="s">
         <v>143</v>
       </c>
-      <c r="D61" s="6" t="s">
+      <c r="D61" s="9" t="s">
         <v>246</v>
       </c>
-      <c r="E61" s="7">
+      <c r="E61" s="8">
         <v>42064</v>
       </c>
-      <c r="F61">
-        <v>3</v>
-      </c>
-      <c r="G61">
+      <c r="F61" s="4">
+        <v>3</v>
+      </c>
+      <c r="G61" s="4">
         <v>2</v>
       </c>
-      <c r="H61">
+      <c r="H61" s="4">
         <v>1</v>
       </c>
-      <c r="I61">
+      <c r="I61" s="4">
         <v>420</v>
       </c>
-      <c r="J61" t="s">
-        <v>241</v>
-      </c>
-      <c r="K61" t="s">
-        <v>243</v>
-      </c>
-      <c r="L61" t="s">
-        <v>241</v>
-      </c>
-      <c r="M61" t="s">
-        <v>241</v>
-      </c>
-      <c r="N61" t="s">
-        <v>243</v>
-      </c>
-      <c r="O61" t="s">
-        <v>241</v>
-      </c>
-      <c r="P61" t="s">
+      <c r="J61" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="K61" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="L61" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="M61" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="N61" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="O61" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="P61" s="4" t="s">
         <v>243</v>
       </c>
     </row>

--- a/office/data/实验数据.xlsx
+++ b/office/data/实验数据.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\glplaman.github.io\office\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E85A1D8-A8AD-4856-94AA-8B2D842E884B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F750E14E-A3C1-499F-9962-90EA4FAC56A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{2E5A61E7-CF82-4D7E-B994-D412ADB0B79D}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{2E5A61E7-CF82-4D7E-B994-D412ADB0B79D}"/>
   </bookViews>
   <sheets>
     <sheet name="通信录" sheetId="6" r:id="rId1"/>
@@ -22,7 +22,7 @@
     <sheet name="门店晚间收益" sheetId="8" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">工资收入!$A$1:$L$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">工资收入!$A$1:$M$11</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">门店晚间收益!$A$1:$P$61</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">学生成绩!$A$1:$K$16</definedName>
     <definedName name="_xlnm.Criteria" localSheetId="3">工资收入!$P$4:$Q$5</definedName>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="933" uniqueCount="308">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1084" uniqueCount="357">
   <si>
     <t>学号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1164,6 +1164,185 @@
   </si>
   <si>
     <t>出生日期</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>赵敏</t>
+  </si>
+  <si>
+    <t>副教授</t>
+  </si>
+  <si>
+    <t>孙强</t>
+  </si>
+  <si>
+    <t>周涛</t>
+  </si>
+  <si>
+    <t>讲师</t>
+  </si>
+  <si>
+    <t>郑凯</t>
+  </si>
+  <si>
+    <t>011</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>012</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>013</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>014</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>015</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>016</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>017</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>018</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>019</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>020</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>传媒学院</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>播音主持</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>人员类别</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>专职</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>兼职</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>吴芳芳</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>王丽丽</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>陈静</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>褚勇强</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>林霞</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>冯杰</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>助教</t>
+  </si>
+  <si>
+    <t>助教</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>刘洋</t>
+  </si>
+  <si>
+    <t>杨柳</t>
+  </si>
+  <si>
+    <t>陈晨</t>
+  </si>
+  <si>
+    <t>张悦</t>
+  </si>
+  <si>
+    <t>王博</t>
+  </si>
+  <si>
+    <t>李娜</t>
+  </si>
+  <si>
+    <t>赵刚</t>
+  </si>
+  <si>
+    <t>孙莉</t>
+  </si>
+  <si>
+    <t>周鹏</t>
+  </si>
+  <si>
+    <t>吴敏</t>
+  </si>
+  <si>
+    <t>021</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>022</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>023</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>024</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>025</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>026</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>027</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>028</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>029</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>030</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1171,7 +1350,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="181" formatCode="yyyy/mm/dd"/>
+  </numFmts>
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1236,6 +1418,12 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF222222"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -1271,7 +1459,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1306,6 +1494,12 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -2724,20 +2918,24 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CC66C260-99D9-44C3-B324-76C50FC519FC}">
-  <dimension ref="A1:Q11"/>
+  <dimension ref="A1:Q31"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="2" width="9.5" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.5" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.875" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.125" style="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="5.5" style="4" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="7.5" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="9.5" style="4" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="7.5" style="4" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="5.5" style="4" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9.5" style="4" bestFit="1" customWidth="1"/>
-    <col min="13" max="16384" width="9" style="4"/>
+    <col min="1" max="2" width="9" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.25" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.125" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="5.25" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.125" style="4" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="9" style="4" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="7.125" style="4" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="5.5" style="4" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9" style="4" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9" style="4"/>
+    <col min="15" max="15" width="9.5" style="4" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="41.625" style="4" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.2">
@@ -2751,30 +2949,33 @@
         <v>113</v>
       </c>
       <c r="D1" s="4" t="s">
+        <v>326</v>
+      </c>
+      <c r="E1" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="F1" s="4" t="s">
         <v>115</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="G1" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="H1" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="I1" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="J1" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="K1" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="K1" s="4" t="s">
+      <c r="L1" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="L1" s="4" t="s">
+      <c r="M1" s="4" t="s">
         <v>48</v>
       </c>
     </row>
@@ -2789,27 +2990,30 @@
         <v>117</v>
       </c>
       <c r="D2" s="4" t="s">
+        <v>327</v>
+      </c>
+      <c r="E2" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="E2" s="4">
+      <c r="F2" s="13">
         <v>21925</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="G2" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="H2" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="H2" s="4">
+      <c r="I2" s="4">
         <v>4700</v>
       </c>
-      <c r="I2" s="4">
+      <c r="J2" s="4">
         <v>1500</v>
       </c>
-      <c r="J2" s="4">
+      <c r="K2" s="4">
         <v>103</v>
       </c>
-      <c r="K2" s="4">
+      <c r="L2" s="4">
         <v>800</v>
       </c>
     </row>
@@ -2824,27 +3028,30 @@
         <v>117</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="E3" s="4">
+        <v>327</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>324</v>
+      </c>
+      <c r="F3" s="13">
         <v>25122</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="G3" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="G3" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="H3" s="4">
+      <c r="H3" s="4" t="s">
+        <v>336</v>
+      </c>
+      <c r="I3" s="4">
         <v>3200</v>
       </c>
-      <c r="I3" s="4">
+      <c r="J3" s="4">
         <v>1000</v>
       </c>
-      <c r="J3" s="4">
+      <c r="K3" s="4">
         <v>205</v>
       </c>
-      <c r="K3" s="4">
+      <c r="L3" s="4">
         <v>500</v>
       </c>
       <c r="P3" s="4" t="s">
@@ -2862,27 +3069,30 @@
         <v>117</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="E4" s="4">
+        <v>327</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>324</v>
+      </c>
+      <c r="F4" s="13">
         <v>20950</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="G4" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="G4" s="4" t="s">
+      <c r="H4" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="H4" s="4">
+      <c r="I4" s="4">
         <v>3400</v>
       </c>
-      <c r="I4" s="4">
+      <c r="J4" s="4">
         <v>1000</v>
       </c>
-      <c r="J4" s="4">
+      <c r="K4" s="4">
         <v>162</v>
       </c>
-      <c r="K4" s="4">
+      <c r="L4" s="4">
         <v>800</v>
       </c>
       <c r="P4" s="4" t="s">
@@ -2903,27 +3113,30 @@
         <v>117</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="E5" s="4">
+        <v>328</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>325</v>
+      </c>
+      <c r="F5" s="13">
         <v>22132</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="G5" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="G5" s="4" t="s">
+      <c r="H5" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="H5" s="4">
+      <c r="I5" s="4">
         <v>5000</v>
       </c>
-      <c r="I5" s="4">
+      <c r="J5" s="4">
         <v>2000</v>
       </c>
-      <c r="J5" s="4">
+      <c r="K5" s="4">
         <v>95.5</v>
       </c>
-      <c r="K5" s="4">
+      <c r="L5" s="4">
         <v>1000</v>
       </c>
       <c r="P5" s="4" t="s">
@@ -2944,27 +3157,30 @@
         <v>122</v>
       </c>
       <c r="D6" s="4" t="s">
+        <v>327</v>
+      </c>
+      <c r="E6" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="E6" s="4">
+      <c r="F6" s="13">
         <v>21220</v>
       </c>
-      <c r="F6" s="4" t="s">
+      <c r="G6" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="G6" s="4" t="s">
+      <c r="H6" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="H6" s="4">
+      <c r="I6" s="4">
         <v>4500</v>
       </c>
-      <c r="I6" s="4">
+      <c r="J6" s="4">
         <v>1500</v>
       </c>
-      <c r="J6" s="4">
+      <c r="K6" s="4">
         <v>100.5</v>
       </c>
-      <c r="K6" s="4">
+      <c r="L6" s="4">
         <v>1000</v>
       </c>
     </row>
@@ -2979,27 +3195,30 @@
         <v>122</v>
       </c>
       <c r="D7" s="4" t="s">
+        <v>328</v>
+      </c>
+      <c r="E7" s="4" t="s">
         <v>123</v>
       </c>
-      <c r="E7" s="4">
+      <c r="F7" s="13">
         <v>21248</v>
       </c>
-      <c r="F7" s="4" t="s">
+      <c r="G7" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="G7" s="4" t="s">
+      <c r="H7" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="H7" s="4">
+      <c r="I7" s="4">
         <v>3800</v>
       </c>
-      <c r="I7" s="4">
+      <c r="J7" s="4">
         <v>1000</v>
       </c>
-      <c r="J7" s="4">
+      <c r="K7" s="4">
         <v>150</v>
       </c>
-      <c r="K7" s="4">
+      <c r="L7" s="4">
         <v>800</v>
       </c>
     </row>
@@ -3014,27 +3233,30 @@
         <v>122</v>
       </c>
       <c r="D8" s="4" t="s">
+        <v>327</v>
+      </c>
+      <c r="E8" s="4" t="s">
         <v>123</v>
       </c>
-      <c r="E8" s="4">
+      <c r="F8" s="13">
         <v>22951</v>
       </c>
-      <c r="F8" s="4" t="s">
+      <c r="G8" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="G8" s="4" t="s">
+      <c r="H8" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="H8" s="4">
+      <c r="I8" s="4">
         <v>4300</v>
       </c>
-      <c r="I8" s="4">
+      <c r="J8" s="4">
         <v>1500</v>
       </c>
-      <c r="J8" s="4">
+      <c r="K8" s="4">
         <v>110</v>
       </c>
-      <c r="K8" s="4">
+      <c r="L8" s="4">
         <v>480</v>
       </c>
     </row>
@@ -3049,27 +3271,30 @@
         <v>117</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="E9" s="4">
+        <v>327</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>325</v>
+      </c>
+      <c r="F9" s="13">
         <v>20616</v>
       </c>
-      <c r="F9" s="4" t="s">
+      <c r="G9" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="G9" s="4" t="s">
+      <c r="H9" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="H9" s="4">
+      <c r="I9" s="4">
         <v>4500</v>
       </c>
-      <c r="I9" s="4">
+      <c r="J9" s="4">
         <v>1500</v>
       </c>
-      <c r="J9" s="4">
+      <c r="K9" s="4">
         <v>98.5</v>
       </c>
-      <c r="K9" s="4">
+      <c r="L9" s="4">
         <v>900</v>
       </c>
     </row>
@@ -3084,27 +3309,30 @@
         <v>117</v>
       </c>
       <c r="D10" s="4" t="s">
+        <v>327</v>
+      </c>
+      <c r="E10" s="4" t="s">
         <v>123</v>
       </c>
-      <c r="E10" s="4">
+      <c r="F10" s="13">
         <v>21956</v>
       </c>
-      <c r="F10" s="4" t="s">
+      <c r="G10" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="G10" s="4" t="s">
+      <c r="H10" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="H10" s="4">
+      <c r="I10" s="4">
         <v>4600</v>
       </c>
-      <c r="I10" s="4">
+      <c r="J10" s="4">
         <v>2000</v>
       </c>
-      <c r="J10" s="4">
+      <c r="K10" s="4">
         <v>154</v>
       </c>
-      <c r="K10" s="4">
+      <c r="L10" s="4">
         <v>600</v>
       </c>
     </row>
@@ -3119,28 +3347,791 @@
         <v>122</v>
       </c>
       <c r="D11" s="4" t="s">
+        <v>328</v>
+      </c>
+      <c r="E11" s="4" t="s">
         <v>123</v>
       </c>
-      <c r="E11" s="4">
+      <c r="F11" s="13">
         <v>25851</v>
       </c>
-      <c r="F11" s="4" t="s">
+      <c r="G11" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="G11" s="4" t="s">
+      <c r="H11" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="H11" s="4">
+      <c r="I11" s="4">
         <v>3700</v>
       </c>
-      <c r="I11" s="4">
+      <c r="J11" s="4">
         <v>1000</v>
       </c>
-      <c r="J11" s="4">
+      <c r="K11" s="4">
         <v>105</v>
       </c>
-      <c r="K11" s="4">
+      <c r="L11" s="4">
         <v>800</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" ht="17.25" x14ac:dyDescent="0.2">
+      <c r="A12" s="12" t="s">
+        <v>314</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>308</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>328</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="F12" s="13">
+        <v>32278</v>
+      </c>
+      <c r="G12" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="H12" s="4" t="s">
+        <v>309</v>
+      </c>
+      <c r="I12" s="4">
+        <v>4800</v>
+      </c>
+      <c r="J12" s="4">
+        <v>1500</v>
+      </c>
+      <c r="K12" s="4">
+        <v>110.5</v>
+      </c>
+      <c r="L12" s="4">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" ht="17.25" x14ac:dyDescent="0.2">
+      <c r="A13" s="12" t="s">
+        <v>315</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>310</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>327</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="F13" s="13">
+        <v>27718</v>
+      </c>
+      <c r="G13" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="H13" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="I13" s="4">
+        <v>5500</v>
+      </c>
+      <c r="J13" s="4">
+        <v>2000</v>
+      </c>
+      <c r="K13" s="4">
+        <v>160</v>
+      </c>
+      <c r="L13" s="4">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" ht="17.25" x14ac:dyDescent="0.2">
+      <c r="A14" s="12" t="s">
+        <v>316</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>311</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>327</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="F14" s="13">
+        <v>33671</v>
+      </c>
+      <c r="G14" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="H14" s="4" t="s">
+        <v>312</v>
+      </c>
+      <c r="I14" s="4">
+        <v>3500</v>
+      </c>
+      <c r="J14" s="4">
+        <v>1000</v>
+      </c>
+      <c r="K14" s="4">
+        <v>98</v>
+      </c>
+      <c r="L14" s="4">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" ht="17.25" x14ac:dyDescent="0.2">
+      <c r="A15" s="12" t="s">
+        <v>317</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>329</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>327</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="F15" s="13">
+        <v>31240</v>
+      </c>
+      <c r="G15" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="H15" s="4" t="s">
+        <v>309</v>
+      </c>
+      <c r="I15" s="4">
+        <v>4600</v>
+      </c>
+      <c r="J15" s="4">
+        <v>1500</v>
+      </c>
+      <c r="K15" s="4">
+        <v>105</v>
+      </c>
+      <c r="L15" s="4">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" ht="17.25" x14ac:dyDescent="0.2">
+      <c r="A16" s="12" t="s">
+        <v>318</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>313</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>327</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="F16" s="13">
+        <v>33141</v>
+      </c>
+      <c r="G16" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="H16" s="4" t="s">
+        <v>309</v>
+      </c>
+      <c r="I16" s="4">
+        <v>5000</v>
+      </c>
+      <c r="J16" s="4">
+        <v>1500</v>
+      </c>
+      <c r="K16" s="4">
+        <v>120</v>
+      </c>
+      <c r="L16" s="4">
+        <v>950</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" ht="17.25" x14ac:dyDescent="0.2">
+      <c r="A17" s="12" t="s">
+        <v>319</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>330</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>327</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="F17" s="13">
+        <v>30346</v>
+      </c>
+      <c r="G17" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="H17" s="4" t="s">
+        <v>312</v>
+      </c>
+      <c r="I17" s="4">
+        <v>3800</v>
+      </c>
+      <c r="J17" s="4">
+        <v>1000</v>
+      </c>
+      <c r="K17" s="4">
+        <v>95.5</v>
+      </c>
+      <c r="L17" s="4">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" ht="17.25" x14ac:dyDescent="0.2">
+      <c r="A18" s="12" t="s">
+        <v>320</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>334</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>327</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="F18" s="13">
+        <v>28659</v>
+      </c>
+      <c r="G18" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="H18" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="I18" s="4">
+        <v>5800</v>
+      </c>
+      <c r="J18" s="4">
+        <v>2000</v>
+      </c>
+      <c r="K18" s="4">
+        <v>170</v>
+      </c>
+      <c r="L18" s="4">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" ht="17.25" x14ac:dyDescent="0.2">
+      <c r="A19" s="12" t="s">
+        <v>321</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>331</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>328</v>
+      </c>
+      <c r="E19" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="F19" s="13">
+        <v>33577</v>
+      </c>
+      <c r="G19" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="H19" s="4" t="s">
+        <v>312</v>
+      </c>
+      <c r="I19" s="4">
+        <v>3400</v>
+      </c>
+      <c r="J19" s="4">
+        <v>1000</v>
+      </c>
+      <c r="K19" s="4">
+        <v>92</v>
+      </c>
+      <c r="L19" s="4">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" ht="17.25" x14ac:dyDescent="0.2">
+      <c r="A20" s="12" t="s">
+        <v>322</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>332</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>327</v>
+      </c>
+      <c r="E20" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="F20" s="13">
+        <v>31889</v>
+      </c>
+      <c r="G20" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="H20" s="4" t="s">
+        <v>309</v>
+      </c>
+      <c r="I20" s="4">
+        <v>4700</v>
+      </c>
+      <c r="J20" s="4">
+        <v>1500</v>
+      </c>
+      <c r="K20" s="4">
+        <v>115</v>
+      </c>
+      <c r="L20" s="4">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" ht="17.25" x14ac:dyDescent="0.2">
+      <c r="A21" s="12" t="s">
+        <v>323</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>333</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>328</v>
+      </c>
+      <c r="E21" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="F21" s="13">
+        <v>29443</v>
+      </c>
+      <c r="G21" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="H21" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="I21" s="4">
+        <v>5600</v>
+      </c>
+      <c r="J21" s="4">
+        <v>2000</v>
+      </c>
+      <c r="K21" s="4">
+        <v>165</v>
+      </c>
+      <c r="L21" s="4">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" ht="17.25" x14ac:dyDescent="0.2">
+      <c r="A22" s="12" t="s">
+        <v>347</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>337</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>327</v>
+      </c>
+      <c r="E22" s="4" t="s">
+        <v>325</v>
+      </c>
+      <c r="F22" s="13">
+        <v>35136</v>
+      </c>
+      <c r="G22" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="H22" s="4" t="s">
+        <v>335</v>
+      </c>
+      <c r="I22" s="4">
+        <v>2800</v>
+      </c>
+      <c r="J22" s="4">
+        <v>800</v>
+      </c>
+      <c r="K22" s="4">
+        <v>85</v>
+      </c>
+      <c r="L22" s="4">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" ht="17.25" x14ac:dyDescent="0.2">
+      <c r="A23" s="12" t="s">
+        <v>348</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>338</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>327</v>
+      </c>
+      <c r="E23" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="F23" s="13">
+        <v>35665</v>
+      </c>
+      <c r="G23" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="H23" s="4" t="s">
+        <v>335</v>
+      </c>
+      <c r="I23" s="4">
+        <v>2800</v>
+      </c>
+      <c r="J23" s="4">
+        <v>800</v>
+      </c>
+      <c r="K23" s="4">
+        <v>82.5</v>
+      </c>
+      <c r="L23" s="4">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" ht="17.25" x14ac:dyDescent="0.2">
+      <c r="A24" s="12" t="s">
+        <v>349</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>339</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>328</v>
+      </c>
+      <c r="E24" s="4" t="s">
+        <v>325</v>
+      </c>
+      <c r="F24" s="13">
+        <v>35800</v>
+      </c>
+      <c r="G24" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="H24" s="4" t="s">
+        <v>335</v>
+      </c>
+      <c r="I24" s="4">
+        <v>2600</v>
+      </c>
+      <c r="J24" s="4">
+        <v>800</v>
+      </c>
+      <c r="K24" s="4">
+        <v>78</v>
+      </c>
+      <c r="L24" s="4">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" ht="17.25" x14ac:dyDescent="0.2">
+      <c r="A25" s="12" t="s">
+        <v>350</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>340</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>327</v>
+      </c>
+      <c r="E25" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="F25" s="13">
+        <v>35399</v>
+      </c>
+      <c r="G25" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="H25" s="4" t="s">
+        <v>335</v>
+      </c>
+      <c r="I25" s="4">
+        <v>2800</v>
+      </c>
+      <c r="J25" s="4">
+        <v>800</v>
+      </c>
+      <c r="K25" s="4">
+        <v>88</v>
+      </c>
+      <c r="L25" s="4">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" ht="17.25" x14ac:dyDescent="0.2">
+      <c r="A26" s="12" t="s">
+        <v>351</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>341</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="D26" s="4" t="s">
+        <v>327</v>
+      </c>
+      <c r="E26" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="F26" s="13">
+        <v>35568</v>
+      </c>
+      <c r="G26" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="H26" s="4" t="s">
+        <v>335</v>
+      </c>
+      <c r="I26" s="4">
+        <v>2800</v>
+      </c>
+      <c r="J26" s="4">
+        <v>800</v>
+      </c>
+      <c r="K26" s="4">
+        <v>80</v>
+      </c>
+      <c r="L26" s="4">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" ht="17.25" x14ac:dyDescent="0.2">
+      <c r="A27" s="12" t="s">
+        <v>352</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>342</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="D27" s="4" t="s">
+        <v>327</v>
+      </c>
+      <c r="E27" s="4" t="s">
+        <v>324</v>
+      </c>
+      <c r="F27" s="13">
+        <v>36047</v>
+      </c>
+      <c r="G27" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="H27" s="4" t="s">
+        <v>335</v>
+      </c>
+      <c r="I27" s="4">
+        <v>2600</v>
+      </c>
+      <c r="J27" s="4">
+        <v>800</v>
+      </c>
+      <c r="K27" s="4">
+        <v>75</v>
+      </c>
+      <c r="L27" s="4">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" ht="17.25" x14ac:dyDescent="0.2">
+      <c r="A28" s="12" t="s">
+        <v>353</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>343</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>328</v>
+      </c>
+      <c r="E28" s="4" t="s">
+        <v>324</v>
+      </c>
+      <c r="F28" s="13">
+        <v>35273</v>
+      </c>
+      <c r="G28" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="H28" s="4" t="s">
+        <v>335</v>
+      </c>
+      <c r="I28" s="4">
+        <v>2800</v>
+      </c>
+      <c r="J28" s="4">
+        <v>800</v>
+      </c>
+      <c r="K28" s="4">
+        <v>83</v>
+      </c>
+      <c r="L28" s="4">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" ht="17.25" x14ac:dyDescent="0.2">
+      <c r="A29" s="12" t="s">
+        <v>354</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>344</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>327</v>
+      </c>
+      <c r="E29" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="F29" s="13">
+        <v>35475</v>
+      </c>
+      <c r="G29" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="H29" s="4" t="s">
+        <v>335</v>
+      </c>
+      <c r="I29" s="4">
+        <v>2800</v>
+      </c>
+      <c r="J29" s="4">
+        <v>800</v>
+      </c>
+      <c r="K29" s="4">
+        <v>86.5</v>
+      </c>
+      <c r="L29" s="4">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" ht="17.25" x14ac:dyDescent="0.2">
+      <c r="A30" s="12" t="s">
+        <v>355</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>345</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="D30" s="4" t="s">
+        <v>327</v>
+      </c>
+      <c r="E30" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="F30" s="13">
+        <v>35886</v>
+      </c>
+      <c r="G30" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="H30" s="4" t="s">
+        <v>335</v>
+      </c>
+      <c r="I30" s="4">
+        <v>2600</v>
+      </c>
+      <c r="J30" s="4">
+        <v>800</v>
+      </c>
+      <c r="K30" s="4">
+        <v>76</v>
+      </c>
+      <c r="L30" s="4">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" ht="17.25" x14ac:dyDescent="0.2">
+      <c r="A31" s="12" t="s">
+        <v>356</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>346</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="D31" s="4" t="s">
+        <v>327</v>
+      </c>
+      <c r="E31" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="F31" s="13">
+        <v>35348</v>
+      </c>
+      <c r="G31" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="H31" s="4" t="s">
+        <v>335</v>
+      </c>
+      <c r="I31" s="4">
+        <v>2800</v>
+      </c>
+      <c r="J31" s="4">
+        <v>800</v>
+      </c>
+      <c r="K31" s="4">
+        <v>84</v>
+      </c>
+      <c r="L31" s="4">
+        <v>500</v>
       </c>
     </row>
   </sheetData>

--- a/office/data/实验数据.xlsx
+++ b/office/data/实验数据.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\glplaman.github.io\office\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F750E14E-A3C1-499F-9962-90EA4FAC56A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4D7B592-D3AB-43C6-BE47-12252F3E0655}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{2E5A61E7-CF82-4D7E-B994-D412ADB0B79D}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="7" xr2:uid="{2E5A61E7-CF82-4D7E-B994-D412ADB0B79D}"/>
   </bookViews>
   <sheets>
     <sheet name="通信录" sheetId="6" r:id="rId1"/>
@@ -20,6 +20,7 @@
     <sheet name="高考成绩" sheetId="5" r:id="rId5"/>
     <sheet name="迷你图" sheetId="7" r:id="rId6"/>
     <sheet name="门店晚间收益" sheetId="8" r:id="rId7"/>
+    <sheet name="销售利润" sheetId="9" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">工资收入!$A$1:$M$11</definedName>
@@ -38,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1084" uniqueCount="357">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1087" uniqueCount="360">
   <si>
     <t>学号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1344,16 +1345,26 @@
   <si>
     <t>030</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>年份</t>
+  </si>
+  <si>
+    <t>销售金额</t>
+  </si>
+  <si>
+    <t>利润率</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="181" formatCode="yyyy/mm/dd"/>
+  <numFmts count="2">
+    <numFmt numFmtId="176" formatCode="yyyy/mm/dd"/>
+    <numFmt numFmtId="177" formatCode="_ [$¥-804]* #,##0.00_ ;_ [$¥-804]* \-#,##0.00_ ;_ [$¥-804]* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1424,6 +1435,15 @@
       <name val="Segoe UI"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -1459,7 +1479,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1499,7 +1519,19 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="181" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1518,6 +1550,1269 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="zh-CN"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="zh-CN" altLang="en-US"/>
+              <a:t>销售利润和金额</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="zh-CN"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="3.0492030492030493E-2"/>
+          <c:y val="0.19143383206023515"/>
+          <c:w val="0.93901593901593905"/>
+          <c:h val="0.61207634135075084"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>销售利润!$B$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>销售金额</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst>
+              <a:outerShdw blurRad="50800" dist="38100" dir="2700000" algn="tl" rotWithShape="0">
+                <a:prstClr val="black">
+                  <a:alpha val="40000"/>
+                </a:prstClr>
+              </a:outerShdw>
+            </a:effectLst>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:numFmt formatCode="0\.0,&quot;万&quot;" sourceLinked="0"/>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="accent2"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="zh-CN"/>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:numRef>
+              <c:f>销售利润!$A$2:$A$7</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>2014</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2015</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2016</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2017</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2018</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2019</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>销售利润!$B$2:$B$7</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>153000</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>213000</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>254000</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>374000</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>523000</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>622000</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-74A1-4BE9-958D-9ACED3E02EF9}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="31808160"/>
+        <c:axId val="31805280"/>
+      </c:barChart>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>销售利润!$C$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>利润率</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent6"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst>
+              <a:outerShdw blurRad="50800" dist="38100" dir="2700000" algn="tl" rotWithShape="0">
+                <a:prstClr val="black">
+                  <a:alpha val="40000"/>
+                </a:prstClr>
+              </a:outerShdw>
+            </a:effectLst>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="triangle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent6"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst>
+                <a:outerShdw blurRad="50800" dist="38100" dir="2700000" algn="tl" rotWithShape="0">
+                  <a:prstClr val="black">
+                    <a:alpha val="40000"/>
+                  </a:prstClr>
+                </a:outerShdw>
+              </a:effectLst>
+            </c:spPr>
+          </c:marker>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="accent6"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="zh-CN"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="t"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:numRef>
+              <c:f>销售利润!$A$2:$A$7</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>2014</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2015</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2016</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2017</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2018</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2019</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>销售利润!$C$2:$C$7</c:f>
+              <c:numCache>
+                <c:formatCode>0.00%</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>0.26650000000000001</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.3614</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.33119999999999999</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.42280000000000001</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.38140000000000002</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.43859999999999999</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-74A1-4BE9-958D-9ACED3E02EF9}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:marker val="1"/>
+        <c:smooth val="0"/>
+        <c:axId val="31892160"/>
+        <c:axId val="31887840"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="31808160"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="zh-CN"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="31805280"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="31805280"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="1000000"/>
+          <c:min val="100000"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:prstDash val="sysDash"/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="none"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="zh-CN"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="31808160"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="31887840"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="r"/>
+        <c:numFmt formatCode="0.00%" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="none"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="zh-CN"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="31892160"/>
+        <c:crosses val="max"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:catAx>
+        <c:axId val="31892160"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="1"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="31887840"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="zh-CN"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="zh-CN"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>531358</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>2722</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>234723</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>31297</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="图表 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1C7108C4-C99F-249C-1FF9-9CD92436E2BD}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -7678,4 +8973,99 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6A76E452-EA88-43E8-A640-F3FAF39616EE}">
+  <dimension ref="A1:F8"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="6" max="6" width="9.875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A1" s="15" t="s">
+        <v>357</v>
+      </c>
+      <c r="B1" s="15" t="s">
+        <v>358</v>
+      </c>
+      <c r="C1" s="15" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A2" s="14">
+        <v>2014</v>
+      </c>
+      <c r="B2" s="14">
+        <v>153000</v>
+      </c>
+      <c r="C2" s="16">
+        <v>0.26650000000000001</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A3" s="14">
+        <v>2015</v>
+      </c>
+      <c r="B3" s="14">
+        <v>213000</v>
+      </c>
+      <c r="C3" s="16">
+        <v>0.3614</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A4" s="14">
+        <v>2016</v>
+      </c>
+      <c r="B4" s="14">
+        <v>254000</v>
+      </c>
+      <c r="C4" s="16">
+        <v>0.33119999999999999</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A5" s="14">
+        <v>2017</v>
+      </c>
+      <c r="B5" s="14">
+        <v>374000</v>
+      </c>
+      <c r="C5" s="16">
+        <v>0.42280000000000001</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A6" s="14">
+        <v>2018</v>
+      </c>
+      <c r="B6" s="14">
+        <v>523000</v>
+      </c>
+      <c r="C6" s="16">
+        <v>0.38140000000000002</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A7" s="14">
+        <v>2019</v>
+      </c>
+      <c r="B7" s="14">
+        <v>622000</v>
+      </c>
+      <c r="C7" s="16">
+        <v>0.43859999999999999</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="F8" s="17"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>